--- a/Fase 2/Evidencias Proyecto/SIGMA_Pendientes_por_Sprint.xlsx
+++ b/Fase 2/Evidencias Proyecto/SIGMA_Pendientes_por_Sprint.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historias" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$1:$O$510</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Historias'!$B$5:$J$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$1:$O$455</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Historias'!$B$5:$J$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -679,16 +679,16 @@
         <v>514</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>509</v>
+        <v>454</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>405.5</v>
+        <v>353.2</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>310</v>
@@ -770,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O510"/>
+  <dimension ref="A1:O455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13653,7 +13653,7 @@
       </c>
       <c r="L192" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M192" s="8" t="inlineStr"/>
@@ -13716,7 +13716,7 @@
       </c>
       <c r="L193" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M193" s="8" t="inlineStr"/>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="L194" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M194" s="8" t="inlineStr"/>
@@ -13842,7 +13842,7 @@
       </c>
       <c r="L195" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M195" s="8" t="inlineStr"/>
@@ -13905,7 +13905,7 @@
       </c>
       <c r="L196" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M196" s="8" t="inlineStr"/>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="L197" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M197" s="8" t="inlineStr"/>
@@ -27039,17 +27039,17 @@
       </c>
       <c r="B398" s="8" t="inlineStr">
         <is>
-          <t>T-6059</t>
+          <t>T-6214</t>
         </is>
       </c>
       <c r="C398" s="8" t="inlineStr">
         <is>
-          <t>HU-177</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D398" s="8" t="inlineStr">
         <is>
-          <t>Registrar si la predicción se cumplió</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E398" s="8" t="inlineStr">
@@ -27069,7 +27069,7 @@
       </c>
       <c r="H398" s="9" t="inlineStr">
         <is>
-          <t>Modelo: revisar Prediccion — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
+          <t>Modelo: revisar Modelo_Monitoreo — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
         </is>
       </c>
       <c r="I398" s="8" t="inlineStr">
@@ -27078,16 +27078,16 @@
         </is>
       </c>
       <c r="J398" s="8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K398" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L398" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M398" s="8" t="inlineStr"/>
@@ -27102,17 +27102,17 @@
       </c>
       <c r="B399" s="8" t="inlineStr">
         <is>
-          <t>T-6060</t>
+          <t>T-6215</t>
         </is>
       </c>
       <c r="C399" s="8" t="inlineStr">
         <is>
-          <t>HU-177</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D399" s="8" t="inlineStr">
         <is>
-          <t>Registrar si la predicción se cumplió</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E399" s="8" t="inlineStr">
@@ -27132,7 +27132,7 @@
       </c>
       <c r="H399" s="9" t="inlineStr">
         <is>
-          <t>SP INS_PREDICCION_RESULTADO: alta transaccional con las validaciones de negocio de la historia. Devuelve el id creado por OUTPUT.</t>
+          <t>SP SEL_MODELO_MONITOREO: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
         </is>
       </c>
       <c r="I399" s="8" t="inlineStr">
@@ -27141,16 +27141,16 @@
         </is>
       </c>
       <c r="J399" s="8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K399" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L399" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M399" s="8" t="inlineStr"/>
@@ -27165,17 +27165,17 @@
       </c>
       <c r="B400" s="8" t="inlineStr">
         <is>
-          <t>T-6061</t>
+          <t>T-6216</t>
         </is>
       </c>
       <c r="C400" s="8" t="inlineStr">
         <is>
-          <t>HU-177</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D400" s="8" t="inlineStr">
         <is>
-          <t>Registrar si la predicción se cumplió</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E400" s="8" t="inlineStr">
@@ -27195,7 +27195,7 @@
       </c>
       <c r="H400" s="9" t="inlineStr">
         <is>
-          <t>SP SEL_PREDICCION_RESULTADO: consulta por id y por filtros, para la ficha y el listado.</t>
+          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Modelo_Monitoreo crezca.</t>
         </is>
       </c>
       <c r="I400" s="8" t="inlineStr">
@@ -27204,16 +27204,16 @@
         </is>
       </c>
       <c r="J400" s="8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K400" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L400" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M400" s="8" t="inlineStr"/>
@@ -27228,17 +27228,17 @@
       </c>
       <c r="B401" s="8" t="inlineStr">
         <is>
-          <t>T-6062</t>
+          <t>T-6217</t>
         </is>
       </c>
       <c r="C401" s="8" t="inlineStr">
         <is>
-          <t>HU-177</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D401" s="8" t="inlineStr">
         <is>
-          <t>Registrar si la predicción se cumplió</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E401" s="8" t="inlineStr">
@@ -27258,7 +27258,7 @@
       </c>
       <c r="H401" s="9" t="inlineStr">
         <is>
-          <t>SP UPD_PREDICCION_RESULTADO: corrección del registro mientras esté en un estado que lo permita.</t>
+          <t>Datos de prueba en Modelo_Monitoreo para poder ejercitar los criterios de aceptación.</t>
         </is>
       </c>
       <c r="I401" s="8" t="inlineStr">
@@ -27267,16 +27267,16 @@
         </is>
       </c>
       <c r="J401" s="8" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K401" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L401" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M401" s="8" t="inlineStr"/>
@@ -27291,17 +27291,17 @@
       </c>
       <c r="B402" s="8" t="inlineStr">
         <is>
-          <t>T-6063</t>
+          <t>T-6220</t>
         </is>
       </c>
       <c r="C402" s="8" t="inlineStr">
         <is>
-          <t>HU-177</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D402" s="8" t="inlineStr">
         <is>
-          <t>Registrar si la predicción se cumplió</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E402" s="8" t="inlineStr">
@@ -27321,25 +27321,25 @@
       </c>
       <c r="H402" s="9" t="inlineStr">
         <is>
-          <t>Datos de prueba en Prediccion para poder ejercitar los criterios de aceptación.</t>
+          <t>Pantalla ModeloMonitoreo.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
         </is>
       </c>
       <c r="I402" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="J402" s="8" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="K402" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L402" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M402" s="8" t="inlineStr"/>
@@ -27354,17 +27354,17 @@
       </c>
       <c r="B403" s="8" t="inlineStr">
         <is>
-          <t>T-6067</t>
+          <t>T-6221</t>
         </is>
       </c>
       <c r="C403" s="8" t="inlineStr">
         <is>
-          <t>HU-177</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D403" s="8" t="inlineStr">
         <is>
-          <t>Registrar si la predicción se cumplió</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E403" s="8" t="inlineStr">
@@ -27384,25 +27384,25 @@
       </c>
       <c r="H403" s="9" t="inlineStr">
         <is>
-          <t>Ficha PrediccionResultado.aspx: formulario de alta con sus validaciones.</t>
+          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
         </is>
       </c>
       <c r="I403" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="J403" s="8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K403" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L403" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M403" s="8" t="inlineStr"/>
@@ -27417,17 +27417,17 @@
       </c>
       <c r="B404" s="8" t="inlineStr">
         <is>
-          <t>T-6068</t>
+          <t>T-6222</t>
         </is>
       </c>
       <c r="C404" s="8" t="inlineStr">
         <is>
-          <t>HU-177</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D404" s="8" t="inlineStr">
         <is>
-          <t>Registrar si la predicción se cumplió</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E404" s="8" t="inlineStr">
@@ -27447,20 +27447,20 @@
       </c>
       <c r="H404" s="9" t="inlineStr">
         <is>
-          <t>Listado PrediccionResultados.aspx con el estado de cada registro.</t>
+          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
         </is>
       </c>
       <c r="I404" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="J404" s="8" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="K404" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L404" s="8" t="inlineStr">
@@ -27480,17 +27480,17 @@
       </c>
       <c r="B405" s="8" t="inlineStr">
         <is>
-          <t>T-6069</t>
+          <t>T-6223</t>
         </is>
       </c>
       <c r="C405" s="8" t="inlineStr">
         <is>
-          <t>HU-177</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D405" s="8" t="inlineStr">
         <is>
-          <t>Registrar si la predicción se cumplió</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E405" s="8" t="inlineStr">
@@ -27510,12 +27510,12 @@
       </c>
       <c r="H405" s="9" t="inlineStr">
         <is>
-          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
+          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
         </is>
       </c>
       <c r="I405" s="8" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="J405" s="8" t="n">
@@ -27523,7 +27523,7 @@
       </c>
       <c r="K405" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L405" s="8" t="inlineStr">
@@ -27543,17 +27543,17 @@
       </c>
       <c r="B406" s="8" t="inlineStr">
         <is>
-          <t>T-6070</t>
+          <t>T-6224</t>
         </is>
       </c>
       <c r="C406" s="8" t="inlineStr">
         <is>
-          <t>HU-177</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D406" s="8" t="inlineStr">
         <is>
-          <t>Registrar si la predicción se cumplió</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E406" s="8" t="inlineStr">
@@ -27573,16 +27573,16 @@
       </c>
       <c r="H406" s="9" t="inlineStr">
         <is>
-          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
+          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
         </is>
       </c>
       <c r="I406" s="8" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Validación</t>
         </is>
       </c>
       <c r="J406" s="8" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="K406" s="8" t="inlineStr">
         <is>
@@ -27606,22 +27606,22 @@
       </c>
       <c r="B407" s="8" t="inlineStr">
         <is>
-          <t>T-6071</t>
+          <t>T-6072</t>
         </is>
       </c>
       <c r="C407" s="8" t="inlineStr">
         <is>
-          <t>HU-177</t>
+          <t>HU-181</t>
         </is>
       </c>
       <c r="D407" s="8" t="inlineStr">
         <is>
-          <t>Registrar si la predicción se cumplió</t>
+          <t>Consultar el cumplimiento del plan de mantenimiento</t>
         </is>
       </c>
       <c r="E407" s="8" t="inlineStr">
         <is>
-          <t>EP-17</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F407" s="8" t="inlineStr">
@@ -27636,25 +27636,25 @@
       </c>
       <c r="H407" s="9" t="inlineStr">
         <is>
-          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
+          <t>Modelo: CREAR la tabla Indicador_Valor — todavía no existe. Columnas, PK, FK a sus padres y columna ind_uuid con índice UNIQUE para que la sincronización no duplique.</t>
         </is>
       </c>
       <c r="I407" s="8" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J407" s="8" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="K407" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L407" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M407" s="8" t="inlineStr"/>
@@ -27669,22 +27669,22 @@
       </c>
       <c r="B408" s="8" t="inlineStr">
         <is>
-          <t>T-6214</t>
+          <t>T-6073</t>
         </is>
       </c>
       <c r="C408" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-181</t>
         </is>
       </c>
       <c r="D408" s="8" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Consultar el cumplimiento del plan de mantenimiento</t>
         </is>
       </c>
       <c r="E408" s="8" t="inlineStr">
         <is>
-          <t>EP-17</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F408" s="8" t="inlineStr">
@@ -27699,7 +27699,7 @@
       </c>
       <c r="H408" s="9" t="inlineStr">
         <is>
-          <t>Modelo: revisar Modelo_Monitoreo — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
+          <t>SP SEL_INDICADOR_CUMPLIMIENTO: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
         </is>
       </c>
       <c r="I408" s="8" t="inlineStr">
@@ -27708,16 +27708,16 @@
         </is>
       </c>
       <c r="J408" s="8" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K408" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L408" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M408" s="8" t="inlineStr"/>
@@ -27732,22 +27732,22 @@
       </c>
       <c r="B409" s="8" t="inlineStr">
         <is>
-          <t>T-6215</t>
+          <t>T-6074</t>
         </is>
       </c>
       <c r="C409" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-181</t>
         </is>
       </c>
       <c r="D409" s="8" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Consultar el cumplimiento del plan de mantenimiento</t>
         </is>
       </c>
       <c r="E409" s="8" t="inlineStr">
         <is>
-          <t>EP-17</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F409" s="8" t="inlineStr">
@@ -27762,7 +27762,7 @@
       </c>
       <c r="H409" s="9" t="inlineStr">
         <is>
-          <t>SP SEL_MODELO_MONITOREO: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
+          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Indicador_Valor crezca.</t>
         </is>
       </c>
       <c r="I409" s="8" t="inlineStr">
@@ -27771,16 +27771,16 @@
         </is>
       </c>
       <c r="J409" s="8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K409" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L409" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M409" s="8" t="inlineStr"/>
@@ -27795,22 +27795,22 @@
       </c>
       <c r="B410" s="8" t="inlineStr">
         <is>
-          <t>T-6216</t>
+          <t>T-6075</t>
         </is>
       </c>
       <c r="C410" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-181</t>
         </is>
       </c>
       <c r="D410" s="8" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Consultar el cumplimiento del plan de mantenimiento</t>
         </is>
       </c>
       <c r="E410" s="8" t="inlineStr">
         <is>
-          <t>EP-17</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F410" s="8" t="inlineStr">
@@ -27825,7 +27825,7 @@
       </c>
       <c r="H410" s="9" t="inlineStr">
         <is>
-          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Modelo_Monitoreo crezca.</t>
+          <t>Datos de prueba en Indicador_Valor para poder ejercitar los criterios de aceptación.</t>
         </is>
       </c>
       <c r="I410" s="8" t="inlineStr">
@@ -27834,16 +27834,16 @@
         </is>
       </c>
       <c r="J410" s="8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K410" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L410" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M410" s="8" t="inlineStr"/>
@@ -27858,22 +27858,22 @@
       </c>
       <c r="B411" s="8" t="inlineStr">
         <is>
-          <t>T-6217</t>
+          <t>T-6078</t>
         </is>
       </c>
       <c r="C411" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-181</t>
         </is>
       </c>
       <c r="D411" s="8" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Consultar el cumplimiento del plan de mantenimiento</t>
         </is>
       </c>
       <c r="E411" s="8" t="inlineStr">
         <is>
-          <t>EP-17</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F411" s="8" t="inlineStr">
@@ -27888,25 +27888,25 @@
       </c>
       <c r="H411" s="9" t="inlineStr">
         <is>
-          <t>Datos de prueba en Modelo_Monitoreo para poder ejercitar los criterios de aceptación.</t>
+          <t>Pantalla IndicadorCumplimiento.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
         </is>
       </c>
       <c r="I411" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="J411" s="8" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="K411" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L411" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M411" s="8" t="inlineStr"/>
@@ -27921,22 +27921,22 @@
       </c>
       <c r="B412" s="8" t="inlineStr">
         <is>
-          <t>T-6220</t>
+          <t>T-6079</t>
         </is>
       </c>
       <c r="C412" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-181</t>
         </is>
       </c>
       <c r="D412" s="8" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Consultar el cumplimiento del plan de mantenimiento</t>
         </is>
       </c>
       <c r="E412" s="8" t="inlineStr">
         <is>
-          <t>EP-17</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F412" s="8" t="inlineStr">
@@ -27951,25 +27951,25 @@
       </c>
       <c r="H412" s="9" t="inlineStr">
         <is>
-          <t>Pantalla ModeloMonitoreo.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
+          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
         </is>
       </c>
       <c r="I412" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="J412" s="8" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="K412" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L412" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M412" s="8" t="inlineStr"/>
@@ -27984,22 +27984,22 @@
       </c>
       <c r="B413" s="8" t="inlineStr">
         <is>
-          <t>T-6221</t>
+          <t>T-6080</t>
         </is>
       </c>
       <c r="C413" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-181</t>
         </is>
       </c>
       <c r="D413" s="8" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Consultar el cumplimiento del plan de mantenimiento</t>
         </is>
       </c>
       <c r="E413" s="8" t="inlineStr">
         <is>
-          <t>EP-17</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F413" s="8" t="inlineStr">
@@ -28014,12 +28014,12 @@
       </c>
       <c r="H413" s="9" t="inlineStr">
         <is>
-          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
+          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
         </is>
       </c>
       <c r="I413" s="8" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="J413" s="8" t="n">
@@ -28027,7 +28027,7 @@
       </c>
       <c r="K413" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L413" s="8" t="inlineStr">
@@ -28047,22 +28047,22 @@
       </c>
       <c r="B414" s="8" t="inlineStr">
         <is>
-          <t>T-6222</t>
+          <t>T-6081</t>
         </is>
       </c>
       <c r="C414" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-181</t>
         </is>
       </c>
       <c r="D414" s="8" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Consultar el cumplimiento del plan de mantenimiento</t>
         </is>
       </c>
       <c r="E414" s="8" t="inlineStr">
         <is>
-          <t>EP-17</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F414" s="8" t="inlineStr">
@@ -28077,16 +28077,16 @@
       </c>
       <c r="H414" s="9" t="inlineStr">
         <is>
-          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
+          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
         </is>
       </c>
       <c r="I414" s="8" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="J414" s="8" t="n">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="K414" s="8" t="inlineStr">
         <is>
@@ -28110,22 +28110,22 @@
       </c>
       <c r="B415" s="8" t="inlineStr">
         <is>
-          <t>T-6223</t>
+          <t>T-6116</t>
         </is>
       </c>
       <c r="C415" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-184</t>
         </is>
       </c>
       <c r="D415" s="8" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Consultar la bandeja de alertas</t>
         </is>
       </c>
       <c r="E415" s="8" t="inlineStr">
         <is>
-          <t>EP-17</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F415" s="8" t="inlineStr">
@@ -28135,21 +28135,21 @@
       </c>
       <c r="G415" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Web y App</t>
         </is>
       </c>
       <c r="H415" s="9" t="inlineStr">
         <is>
-          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
+          <t>Modelo: revisar Alerta — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
         </is>
       </c>
       <c r="I415" s="8" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J415" s="8" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K415" s="8" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
       </c>
       <c r="L415" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M415" s="8" t="inlineStr"/>
@@ -28173,22 +28173,22 @@
       </c>
       <c r="B416" s="8" t="inlineStr">
         <is>
-          <t>T-6224</t>
+          <t>T-6117</t>
         </is>
       </c>
       <c r="C416" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-184</t>
         </is>
       </c>
       <c r="D416" s="8" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Consultar la bandeja de alertas</t>
         </is>
       </c>
       <c r="E416" s="8" t="inlineStr">
         <is>
-          <t>EP-17</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F416" s="8" t="inlineStr">
@@ -28198,30 +28198,30 @@
       </c>
       <c r="G416" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Web y App</t>
         </is>
       </c>
       <c r="H416" s="9" t="inlineStr">
         <is>
-          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
+          <t>SP SEL_ALERTA: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
         </is>
       </c>
       <c r="I416" s="8" t="inlineStr">
         <is>
-          <t>Validación</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J416" s="8" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="K416" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L416" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M416" s="8" t="inlineStr"/>
@@ -28236,17 +28236,17 @@
       </c>
       <c r="B417" s="8" t="inlineStr">
         <is>
-          <t>T-6035</t>
+          <t>T-6118</t>
         </is>
       </c>
       <c r="C417" s="8" t="inlineStr">
         <is>
-          <t>HU-180</t>
+          <t>HU-184</t>
         </is>
       </c>
       <c r="D417" s="8" t="inlineStr">
         <is>
-          <t>Consultar el tablero de indicadores</t>
+          <t>Consultar la bandeja de alertas</t>
         </is>
       </c>
       <c r="E417" s="8" t="inlineStr">
@@ -28261,12 +28261,12 @@
       </c>
       <c r="G417" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Web y App</t>
         </is>
       </c>
       <c r="H417" s="9" t="inlineStr">
         <is>
-          <t>Modelo: CREAR la tabla Indicador_Valor — todavía no existe. Columnas, PK, FK a sus padres y columna ind_uuid con índice UNIQUE para que la sincronización no duplique.</t>
+          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Alerta crezca.</t>
         </is>
       </c>
       <c r="I417" s="8" t="inlineStr">
@@ -28275,7 +28275,7 @@
         </is>
       </c>
       <c r="J417" s="8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K417" s="8" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
       </c>
       <c r="L417" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M417" s="8" t="inlineStr"/>
@@ -28299,17 +28299,17 @@
       </c>
       <c r="B418" s="8" t="inlineStr">
         <is>
-          <t>T-6036</t>
+          <t>T-6119</t>
         </is>
       </c>
       <c r="C418" s="8" t="inlineStr">
         <is>
-          <t>HU-180</t>
+          <t>HU-184</t>
         </is>
       </c>
       <c r="D418" s="8" t="inlineStr">
         <is>
-          <t>Consultar el tablero de indicadores</t>
+          <t>Consultar la bandeja de alertas</t>
         </is>
       </c>
       <c r="E418" s="8" t="inlineStr">
@@ -28324,12 +28324,12 @@
       </c>
       <c r="G418" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Web y App</t>
         </is>
       </c>
       <c r="H418" s="9" t="inlineStr">
         <is>
-          <t>SP SEL_INDICADOR_TABLERO: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
+          <t>Datos de prueba en Alerta para poder ejercitar los criterios de aceptación.</t>
         </is>
       </c>
       <c r="I418" s="8" t="inlineStr">
@@ -28338,7 +28338,7 @@
         </is>
       </c>
       <c r="J418" s="8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K418" s="8" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
       </c>
       <c r="L418" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M418" s="8" t="inlineStr"/>
@@ -28362,17 +28362,17 @@
       </c>
       <c r="B419" s="8" t="inlineStr">
         <is>
-          <t>T-6037</t>
+          <t>T-6120</t>
         </is>
       </c>
       <c r="C419" s="8" t="inlineStr">
         <is>
-          <t>HU-180</t>
+          <t>HU-184</t>
         </is>
       </c>
       <c r="D419" s="8" t="inlineStr">
         <is>
-          <t>Consultar el tablero de indicadores</t>
+          <t>Consultar la bandeja de alertas</t>
         </is>
       </c>
       <c r="E419" s="8" t="inlineStr">
@@ -28387,25 +28387,25 @@
       </c>
       <c r="G419" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Web y App</t>
         </is>
       </c>
       <c r="H419" s="9" t="inlineStr">
         <is>
-          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Indicador_Valor crezca.</t>
+          <t>GET /api/alertas — consulta con filtros y paginación.</t>
         </is>
       </c>
       <c r="I419" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>API</t>
         </is>
       </c>
       <c r="J419" s="8" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K419" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L419" s="8" t="inlineStr">
@@ -28425,17 +28425,17 @@
       </c>
       <c r="B420" s="8" t="inlineStr">
         <is>
-          <t>T-6038</t>
+          <t>T-6121</t>
         </is>
       </c>
       <c r="C420" s="8" t="inlineStr">
         <is>
-          <t>HU-180</t>
+          <t>HU-184</t>
         </is>
       </c>
       <c r="D420" s="8" t="inlineStr">
         <is>
-          <t>Consultar el tablero de indicadores</t>
+          <t>Consultar la bandeja de alertas</t>
         </is>
       </c>
       <c r="E420" s="8" t="inlineStr">
@@ -28450,17 +28450,17 @@
       </c>
       <c r="G420" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Web y App</t>
         </is>
       </c>
       <c r="H420" s="9" t="inlineStr">
         <is>
-          <t>Datos de prueba en Indicador_Valor para poder ejercitar los criterios de aceptación.</t>
+          <t>Caché corta de la respuesta cuando el dato no cambia por petición.</t>
         </is>
       </c>
       <c r="I420" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>API</t>
         </is>
       </c>
       <c r="J420" s="8" t="n">
@@ -28468,7 +28468,7 @@
       </c>
       <c r="K420" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L420" s="8" t="inlineStr">
@@ -28488,17 +28488,17 @@
       </c>
       <c r="B421" s="8" t="inlineStr">
         <is>
-          <t>T-6041</t>
+          <t>T-6122</t>
         </is>
       </c>
       <c r="C421" s="8" t="inlineStr">
         <is>
-          <t>HU-180</t>
+          <t>HU-184</t>
         </is>
       </c>
       <c r="D421" s="8" t="inlineStr">
         <is>
-          <t>Consultar el tablero de indicadores</t>
+          <t>Consultar la bandeja de alertas</t>
         </is>
       </c>
       <c r="E421" s="8" t="inlineStr">
@@ -28513,21 +28513,21 @@
       </c>
       <c r="G421" s="8" t="inlineStr">
         <is>
+          <t>Web y App</t>
+        </is>
+      </c>
+      <c r="H421" s="9" t="inlineStr">
+        <is>
+          <t>Pantalla Alerta.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
+        </is>
+      </c>
+      <c r="I421" s="8" t="inlineStr">
+        <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H421" s="9" t="inlineStr">
-        <is>
-          <t>Pantalla IndicadorTablero.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
-        </is>
-      </c>
-      <c r="I421" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
       <c r="J421" s="8" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="K421" s="8" t="inlineStr">
         <is>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="L421" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M421" s="8" t="inlineStr"/>
@@ -28551,17 +28551,17 @@
       </c>
       <c r="B422" s="8" t="inlineStr">
         <is>
-          <t>T-6042</t>
+          <t>T-6123</t>
         </is>
       </c>
       <c r="C422" s="8" t="inlineStr">
         <is>
-          <t>HU-180</t>
+          <t>HU-184</t>
         </is>
       </c>
       <c r="D422" s="8" t="inlineStr">
         <is>
-          <t>Consultar el tablero de indicadores</t>
+          <t>Consultar la bandeja de alertas</t>
         </is>
       </c>
       <c r="E422" s="8" t="inlineStr">
@@ -28576,21 +28576,21 @@
       </c>
       <c r="G422" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Web y App</t>
         </is>
       </c>
       <c r="H422" s="9" t="inlineStr">
         <is>
-          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
+          <t>Consumo del endpoint desde la app cuando corresponda.</t>
         </is>
       </c>
       <c r="I422" s="8" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Móvil</t>
         </is>
       </c>
       <c r="J422" s="8" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K422" s="8" t="inlineStr">
         <is>
@@ -28614,17 +28614,17 @@
       </c>
       <c r="B423" s="8" t="inlineStr">
         <is>
-          <t>T-6043</t>
+          <t>T-6124</t>
         </is>
       </c>
       <c r="C423" s="8" t="inlineStr">
         <is>
-          <t>HU-180</t>
+          <t>HU-184</t>
         </is>
       </c>
       <c r="D423" s="8" t="inlineStr">
         <is>
-          <t>Consultar el tablero de indicadores</t>
+          <t>Consultar la bandeja de alertas</t>
         </is>
       </c>
       <c r="E423" s="8" t="inlineStr">
@@ -28639,30 +28639,30 @@
       </c>
       <c r="G423" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Web y App</t>
         </is>
       </c>
       <c r="H423" s="9" t="inlineStr">
         <is>
-          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
+          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
         </is>
       </c>
       <c r="I423" s="8" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="J423" s="8" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="K423" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L423" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M423" s="8" t="inlineStr"/>
@@ -28677,17 +28677,17 @@
       </c>
       <c r="B424" s="8" t="inlineStr">
         <is>
-          <t>T-6044</t>
+          <t>T-6125</t>
         </is>
       </c>
       <c r="C424" s="8" t="inlineStr">
         <is>
-          <t>HU-180</t>
+          <t>HU-184</t>
         </is>
       </c>
       <c r="D424" s="8" t="inlineStr">
         <is>
-          <t>Consultar el tablero de indicadores</t>
+          <t>Consultar la bandeja de alertas</t>
         </is>
       </c>
       <c r="E424" s="8" t="inlineStr">
@@ -28702,21 +28702,21 @@
       </c>
       <c r="G424" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Web y App</t>
         </is>
       </c>
       <c r="H424" s="9" t="inlineStr">
         <is>
-          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
+          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
         </is>
       </c>
       <c r="I424" s="8" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="J424" s="8" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K424" s="8" t="inlineStr">
         <is>
@@ -28740,17 +28740,17 @@
       </c>
       <c r="B425" s="8" t="inlineStr">
         <is>
-          <t>T-6045</t>
+          <t>T-6126</t>
         </is>
       </c>
       <c r="C425" s="8" t="inlineStr">
         <is>
-          <t>HU-180</t>
+          <t>HU-184</t>
         </is>
       </c>
       <c r="D425" s="8" t="inlineStr">
         <is>
-          <t>Consultar el tablero de indicadores</t>
+          <t>Consultar la bandeja de alertas</t>
         </is>
       </c>
       <c r="E425" s="8" t="inlineStr">
@@ -28765,17 +28765,17 @@
       </c>
       <c r="G425" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Web y App</t>
         </is>
       </c>
       <c r="H425" s="9" t="inlineStr">
         <is>
-          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
+          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
         </is>
       </c>
       <c r="I425" s="8" t="inlineStr">
         <is>
-          <t>Validación</t>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="J425" s="8" t="n">
@@ -28803,17 +28803,17 @@
       </c>
       <c r="B426" s="8" t="inlineStr">
         <is>
-          <t>T-6072</t>
+          <t>T-6192</t>
         </is>
       </c>
       <c r="C426" s="8" t="inlineStr">
         <is>
-          <t>HU-181</t>
+          <t>HU-185</t>
         </is>
       </c>
       <c r="D426" s="8" t="inlineStr">
         <is>
-          <t>Consultar el cumplimiento del plan de mantenimiento</t>
+          <t>Exportar e imprimir reportes</t>
         </is>
       </c>
       <c r="E426" s="8" t="inlineStr">
@@ -28846,7 +28846,7 @@
       </c>
       <c r="K426" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L426" s="8" t="inlineStr">
@@ -28866,17 +28866,17 @@
       </c>
       <c r="B427" s="8" t="inlineStr">
         <is>
-          <t>T-6073</t>
+          <t>T-6193</t>
         </is>
       </c>
       <c r="C427" s="8" t="inlineStr">
         <is>
-          <t>HU-181</t>
+          <t>HU-185</t>
         </is>
       </c>
       <c r="D427" s="8" t="inlineStr">
         <is>
-          <t>Consultar el cumplimiento del plan de mantenimiento</t>
+          <t>Exportar e imprimir reportes</t>
         </is>
       </c>
       <c r="E427" s="8" t="inlineStr">
@@ -28896,7 +28896,7 @@
       </c>
       <c r="H427" s="9" t="inlineStr">
         <is>
-          <t>SP SEL_INDICADOR_CUMPLIMIENTO: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
+          <t>SP INDICADOR_EXPORTAR: el proceso completo dentro de una transacción, con SET XACT_ABORT ON para que un error no deje datos a medias.</t>
         </is>
       </c>
       <c r="I427" s="8" t="inlineStr">
@@ -28905,11 +28905,11 @@
         </is>
       </c>
       <c r="J427" s="8" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="K427" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L427" s="8" t="inlineStr">
@@ -28929,17 +28929,17 @@
       </c>
       <c r="B428" s="8" t="inlineStr">
         <is>
-          <t>T-6074</t>
+          <t>T-6194</t>
         </is>
       </c>
       <c r="C428" s="8" t="inlineStr">
         <is>
-          <t>HU-181</t>
+          <t>HU-185</t>
         </is>
       </c>
       <c r="D428" s="8" t="inlineStr">
         <is>
-          <t>Consultar el cumplimiento del plan de mantenimiento</t>
+          <t>Exportar e imprimir reportes</t>
         </is>
       </c>
       <c r="E428" s="8" t="inlineStr">
@@ -28959,7 +28959,7 @@
       </c>
       <c r="H428" s="9" t="inlineStr">
         <is>
-          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Indicador_Valor crezca.</t>
+          <t>Reglas de negocio de la historia en el SP, no en la pantalla: la API y la web tienen que obtener el mismo resultado.</t>
         </is>
       </c>
       <c r="I428" s="8" t="inlineStr">
@@ -28972,7 +28972,7 @@
       </c>
       <c r="K428" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L428" s="8" t="inlineStr">
@@ -28992,17 +28992,17 @@
       </c>
       <c r="B429" s="8" t="inlineStr">
         <is>
-          <t>T-6075</t>
+          <t>T-6195</t>
         </is>
       </c>
       <c r="C429" s="8" t="inlineStr">
         <is>
-          <t>HU-181</t>
+          <t>HU-185</t>
         </is>
       </c>
       <c r="D429" s="8" t="inlineStr">
         <is>
-          <t>Consultar el cumplimiento del plan de mantenimiento</t>
+          <t>Exportar e imprimir reportes</t>
         </is>
       </c>
       <c r="E429" s="8" t="inlineStr">
@@ -29022,7 +29022,7 @@
       </c>
       <c r="H429" s="9" t="inlineStr">
         <is>
-          <t>Datos de prueba en Indicador_Valor para poder ejercitar los criterios de aceptación.</t>
+          <t>SP SEL_INDICADOR_EXPORTAR: consultar el resultado del proceso.</t>
         </is>
       </c>
       <c r="I429" s="8" t="inlineStr">
@@ -29035,7 +29035,7 @@
       </c>
       <c r="K429" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L429" s="8" t="inlineStr">
@@ -29055,17 +29055,17 @@
       </c>
       <c r="B430" s="8" t="inlineStr">
         <is>
-          <t>T-6078</t>
+          <t>T-6196</t>
         </is>
       </c>
       <c r="C430" s="8" t="inlineStr">
         <is>
-          <t>HU-181</t>
+          <t>HU-185</t>
         </is>
       </c>
       <c r="D430" s="8" t="inlineStr">
         <is>
-          <t>Consultar el cumplimiento del plan de mantenimiento</t>
+          <t>Exportar e imprimir reportes</t>
         </is>
       </c>
       <c r="E430" s="8" t="inlineStr">
@@ -29085,20 +29085,20 @@
       </c>
       <c r="H430" s="9" t="inlineStr">
         <is>
-          <t>Pantalla IndicadorCumplimiento.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
+          <t>Datos de prueba en Indicador_Valor para poder ejercitar los criterios de aceptación.</t>
         </is>
       </c>
       <c r="I430" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J430" s="8" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="K430" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L430" s="8" t="inlineStr">
@@ -29118,17 +29118,17 @@
       </c>
       <c r="B431" s="8" t="inlineStr">
         <is>
-          <t>T-6079</t>
+          <t>T-6199</t>
         </is>
       </c>
       <c r="C431" s="8" t="inlineStr">
         <is>
-          <t>HU-181</t>
+          <t>HU-185</t>
         </is>
       </c>
       <c r="D431" s="8" t="inlineStr">
         <is>
-          <t>Consultar el cumplimiento del plan de mantenimiento</t>
+          <t>Exportar e imprimir reportes</t>
         </is>
       </c>
       <c r="E431" s="8" t="inlineStr">
@@ -29148,20 +29148,20 @@
       </c>
       <c r="H431" s="9" t="inlineStr">
         <is>
-          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
+          <t>Pantalla IndicadorExportar.aspx: disparar el proceso, mostrar el resultado y dejar constancia de quién lo ejecutó.</t>
         </is>
       </c>
       <c r="I431" s="8" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="J431" s="8" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="K431" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L431" s="8" t="inlineStr">
@@ -29181,17 +29181,17 @@
       </c>
       <c r="B432" s="8" t="inlineStr">
         <is>
-          <t>T-6080</t>
+          <t>T-6200</t>
         </is>
       </c>
       <c r="C432" s="8" t="inlineStr">
         <is>
-          <t>HU-181</t>
+          <t>HU-185</t>
         </is>
       </c>
       <c r="D432" s="8" t="inlineStr">
         <is>
-          <t>Consultar el cumplimiento del plan de mantenimiento</t>
+          <t>Exportar e imprimir reportes</t>
         </is>
       </c>
       <c r="E432" s="8" t="inlineStr">
@@ -29211,25 +29211,25 @@
       </c>
       <c r="H432" s="9" t="inlineStr">
         <is>
-          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
+          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
         </is>
       </c>
       <c r="I432" s="8" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="J432" s="8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K432" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L432" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M432" s="8" t="inlineStr"/>
@@ -29244,17 +29244,17 @@
       </c>
       <c r="B433" s="8" t="inlineStr">
         <is>
-          <t>T-6081</t>
+          <t>T-6201</t>
         </is>
       </c>
       <c r="C433" s="8" t="inlineStr">
         <is>
-          <t>HU-181</t>
+          <t>HU-185</t>
         </is>
       </c>
       <c r="D433" s="8" t="inlineStr">
         <is>
-          <t>Consultar el cumplimiento del plan de mantenimiento</t>
+          <t>Exportar e imprimir reportes</t>
         </is>
       </c>
       <c r="E433" s="8" t="inlineStr">
@@ -29274,16 +29274,16 @@
       </c>
       <c r="H433" s="9" t="inlineStr">
         <is>
-          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
+          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
         </is>
       </c>
       <c r="I433" s="8" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="J433" s="8" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="K433" s="8" t="inlineStr">
         <is>
@@ -29307,17 +29307,17 @@
       </c>
       <c r="B434" s="8" t="inlineStr">
         <is>
-          <t>T-6082</t>
+          <t>T-6202</t>
         </is>
       </c>
       <c r="C434" s="8" t="inlineStr">
         <is>
-          <t>HU-182</t>
+          <t>HU-185</t>
         </is>
       </c>
       <c r="D434" s="8" t="inlineStr">
         <is>
-          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
+          <t>Exportar e imprimir reportes</t>
         </is>
       </c>
       <c r="E434" s="8" t="inlineStr">
@@ -29337,20 +29337,20 @@
       </c>
       <c r="H434" s="9" t="inlineStr">
         <is>
-          <t>Modelo: CREAR la tabla Indicador_Valor — todavía no existe. Columnas, PK, FK a sus padres y columna ind_uuid con índice UNIQUE para que la sincronización no duplique.</t>
+          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
         </is>
       </c>
       <c r="I434" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="J434" s="8" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K434" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L434" s="8" t="inlineStr">
@@ -29370,50 +29370,50 @@
       </c>
       <c r="B435" s="8" t="inlineStr">
         <is>
-          <t>T-6083</t>
+          <t>T-2142</t>
         </is>
       </c>
       <c r="C435" s="8" t="inlineStr">
         <is>
-          <t>HU-182</t>
+          <t>HU-193</t>
         </is>
       </c>
       <c r="D435" s="8" t="inlineStr">
         <is>
-          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
+          <t>Bloquear el acceso por suscripción vencida</t>
         </is>
       </c>
       <c r="E435" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-19</t>
         </is>
       </c>
       <c r="F435" s="8" t="inlineStr">
         <is>
-          <t>Sprint 6</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="G435" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Web y App</t>
         </is>
       </c>
       <c r="H435" s="9" t="inlineStr">
         <is>
-          <t>SP SEL_INDICADOR_DISPONIBILIDAD: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
+          <t>Consumo del endpoint desde la app cuando corresponda.</t>
         </is>
       </c>
       <c r="I435" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Móvil</t>
         </is>
       </c>
       <c r="J435" s="8" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K435" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L435" s="8" t="inlineStr">
@@ -29421,7 +29421,11 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="M435" s="8" t="inlineStr"/>
+      <c r="M435" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
       <c r="N435" s="8" t="inlineStr"/>
       <c r="O435" s="8" t="inlineStr"/>
     </row>
@@ -29433,22 +29437,22 @@
       </c>
       <c r="B436" s="8" t="inlineStr">
         <is>
-          <t>T-6084</t>
+          <t>T-6127</t>
         </is>
       </c>
       <c r="C436" s="8" t="inlineStr">
         <is>
-          <t>HU-182</t>
+          <t>HU-201</t>
         </is>
       </c>
       <c r="D436" s="8" t="inlineStr">
         <is>
-          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
+          <t>Resolver las celdas ambiguas de una importación</t>
         </is>
       </c>
       <c r="E436" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F436" s="8" t="inlineStr">
@@ -29463,7 +29467,7 @@
       </c>
       <c r="H436" s="9" t="inlineStr">
         <is>
-          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Indicador_Valor crezca.</t>
+          <t>Modelo: revisar Importacion_Carga_Celda — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
         </is>
       </c>
       <c r="I436" s="8" t="inlineStr">
@@ -29481,7 +29485,7 @@
       </c>
       <c r="L436" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M436" s="8" t="inlineStr"/>
@@ -29496,22 +29500,22 @@
       </c>
       <c r="B437" s="8" t="inlineStr">
         <is>
-          <t>T-6085</t>
+          <t>T-6128</t>
         </is>
       </c>
       <c r="C437" s="8" t="inlineStr">
         <is>
-          <t>HU-182</t>
+          <t>HU-201</t>
         </is>
       </c>
       <c r="D437" s="8" t="inlineStr">
         <is>
-          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
+          <t>Resolver las celdas ambiguas de una importación</t>
         </is>
       </c>
       <c r="E437" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F437" s="8" t="inlineStr">
@@ -29526,7 +29530,7 @@
       </c>
       <c r="H437" s="9" t="inlineStr">
         <is>
-          <t>Datos de prueba en Indicador_Valor para poder ejercitar los criterios de aceptación.</t>
+          <t>SP IMPORTACION_CELDA: el proceso completo dentro de una transacción, con SET XACT_ABORT ON para que un error no deje datos a medias.</t>
         </is>
       </c>
       <c r="I437" s="8" t="inlineStr">
@@ -29544,7 +29548,7 @@
       </c>
       <c r="L437" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M437" s="8" t="inlineStr"/>
@@ -29559,22 +29563,22 @@
       </c>
       <c r="B438" s="8" t="inlineStr">
         <is>
-          <t>T-6088</t>
+          <t>T-6129</t>
         </is>
       </c>
       <c r="C438" s="8" t="inlineStr">
         <is>
-          <t>HU-182</t>
+          <t>HU-201</t>
         </is>
       </c>
       <c r="D438" s="8" t="inlineStr">
         <is>
-          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
+          <t>Resolver las celdas ambiguas de una importación</t>
         </is>
       </c>
       <c r="E438" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F438" s="8" t="inlineStr">
@@ -29589,25 +29593,25 @@
       </c>
       <c r="H438" s="9" t="inlineStr">
         <is>
-          <t>Pantalla IndicadorDisponibilidad.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
+          <t>Reglas de negocio de la historia en el SP, no en la pantalla: la API y la web tienen que obtener el mismo resultado.</t>
         </is>
       </c>
       <c r="I438" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J438" s="8" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="K438" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L438" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M438" s="8" t="inlineStr"/>
@@ -29622,22 +29626,22 @@
       </c>
       <c r="B439" s="8" t="inlineStr">
         <is>
-          <t>T-6089</t>
+          <t>T-6130</t>
         </is>
       </c>
       <c r="C439" s="8" t="inlineStr">
         <is>
-          <t>HU-182</t>
+          <t>HU-201</t>
         </is>
       </c>
       <c r="D439" s="8" t="inlineStr">
         <is>
-          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
+          <t>Resolver las celdas ambiguas de una importación</t>
         </is>
       </c>
       <c r="E439" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F439" s="8" t="inlineStr">
@@ -29652,25 +29656,25 @@
       </c>
       <c r="H439" s="9" t="inlineStr">
         <is>
-          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
+          <t>SP SEL_IMPORTACION_CELDA: consultar el resultado del proceso.</t>
         </is>
       </c>
       <c r="I439" s="8" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J439" s="8" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K439" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L439" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M439" s="8" t="inlineStr"/>
@@ -29685,22 +29689,22 @@
       </c>
       <c r="B440" s="8" t="inlineStr">
         <is>
-          <t>T-6090</t>
+          <t>T-6131</t>
         </is>
       </c>
       <c r="C440" s="8" t="inlineStr">
         <is>
-          <t>HU-182</t>
+          <t>HU-201</t>
         </is>
       </c>
       <c r="D440" s="8" t="inlineStr">
         <is>
-          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
+          <t>Resolver las celdas ambiguas de una importación</t>
         </is>
       </c>
       <c r="E440" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F440" s="8" t="inlineStr">
@@ -29715,25 +29719,25 @@
       </c>
       <c r="H440" s="9" t="inlineStr">
         <is>
-          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
+          <t>Datos de prueba en Importacion_Carga_Celda para poder ejercitar los criterios de aceptación.</t>
         </is>
       </c>
       <c r="I440" s="8" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J440" s="8" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="K440" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L440" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M440" s="8" t="inlineStr"/>
@@ -29748,22 +29752,22 @@
       </c>
       <c r="B441" s="8" t="inlineStr">
         <is>
-          <t>T-6091</t>
+          <t>T-6134</t>
         </is>
       </c>
       <c r="C441" s="8" t="inlineStr">
         <is>
-          <t>HU-182</t>
+          <t>HU-201</t>
         </is>
       </c>
       <c r="D441" s="8" t="inlineStr">
         <is>
-          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
+          <t>Resolver las celdas ambiguas de una importación</t>
         </is>
       </c>
       <c r="E441" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F441" s="8" t="inlineStr">
@@ -29778,25 +29782,25 @@
       </c>
       <c r="H441" s="9" t="inlineStr">
         <is>
-          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
+          <t>Pantalla ImportacionCelda.aspx: disparar el proceso, mostrar el resultado y dejar constancia de quién lo ejecutó.</t>
         </is>
       </c>
       <c r="I441" s="8" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="J441" s="8" t="n">
-        <v>0.5</v>
+        <v>2.25</v>
       </c>
       <c r="K441" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L441" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M441" s="8" t="inlineStr"/>
@@ -29811,22 +29815,22 @@
       </c>
       <c r="B442" s="8" t="inlineStr">
         <is>
-          <t>T-6092</t>
+          <t>T-6135</t>
         </is>
       </c>
       <c r="C442" s="8" t="inlineStr">
         <is>
-          <t>HU-182</t>
+          <t>HU-201</t>
         </is>
       </c>
       <c r="D442" s="8" t="inlineStr">
         <is>
-          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
+          <t>Resolver las celdas ambiguas de una importación</t>
         </is>
       </c>
       <c r="E442" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F442" s="8" t="inlineStr">
@@ -29841,25 +29845,25 @@
       </c>
       <c r="H442" s="9" t="inlineStr">
         <is>
-          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
+          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
         </is>
       </c>
       <c r="I442" s="8" t="inlineStr">
         <is>
-          <t>Validación</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="J442" s="8" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="K442" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L442" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M442" s="8" t="inlineStr"/>
@@ -29874,22 +29878,22 @@
       </c>
       <c r="B443" s="8" t="inlineStr">
         <is>
-          <t>T-6093</t>
+          <t>T-6136</t>
         </is>
       </c>
       <c r="C443" s="8" t="inlineStr">
         <is>
-          <t>HU-183</t>
+          <t>HU-201</t>
         </is>
       </c>
       <c r="D443" s="8" t="inlineStr">
         <is>
-          <t>Consultar los costos de mantenimiento</t>
+          <t>Resolver las celdas ambiguas de una importación</t>
         </is>
       </c>
       <c r="E443" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F443" s="8" t="inlineStr">
@@ -29904,16 +29908,16 @@
       </c>
       <c r="H443" s="9" t="inlineStr">
         <is>
-          <t>Modelo: CREAR la tabla Indicador_Valor — todavía no existe. Columnas, PK, FK a sus padres y columna ind_uuid con índice UNIQUE para que la sincronización no duplique.</t>
+          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
         </is>
       </c>
       <c r="I443" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="J443" s="8" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="K443" s="8" t="inlineStr">
         <is>
@@ -29937,22 +29941,22 @@
       </c>
       <c r="B444" s="8" t="inlineStr">
         <is>
-          <t>T-6094</t>
+          <t>T-6137</t>
         </is>
       </c>
       <c r="C444" s="8" t="inlineStr">
         <is>
-          <t>HU-183</t>
+          <t>HU-201</t>
         </is>
       </c>
       <c r="D444" s="8" t="inlineStr">
         <is>
-          <t>Consultar los costos de mantenimiento</t>
+          <t>Resolver las celdas ambiguas de una importación</t>
         </is>
       </c>
       <c r="E444" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F444" s="8" t="inlineStr">
@@ -29967,20 +29971,20 @@
       </c>
       <c r="H444" s="9" t="inlineStr">
         <is>
-          <t>SP SEL_INDICADOR_COSTO: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
+          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
         </is>
       </c>
       <c r="I444" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="J444" s="8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K444" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L444" s="8" t="inlineStr">
@@ -30000,22 +30004,22 @@
       </c>
       <c r="B445" s="8" t="inlineStr">
         <is>
-          <t>T-6095</t>
+          <t>T-6138</t>
         </is>
       </c>
       <c r="C445" s="8" t="inlineStr">
         <is>
-          <t>HU-183</t>
+          <t>HU-201</t>
         </is>
       </c>
       <c r="D445" s="8" t="inlineStr">
         <is>
-          <t>Consultar los costos de mantenimiento</t>
+          <t>Resolver las celdas ambiguas de una importación</t>
         </is>
       </c>
       <c r="E445" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F445" s="8" t="inlineStr">
@@ -30030,20 +30034,20 @@
       </c>
       <c r="H445" s="9" t="inlineStr">
         <is>
-          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Indicador_Valor crezca.</t>
+          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
         </is>
       </c>
       <c r="I445" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Validación</t>
         </is>
       </c>
       <c r="J445" s="8" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K445" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L445" s="8" t="inlineStr">
@@ -30063,22 +30067,22 @@
       </c>
       <c r="B446" s="8" t="inlineStr">
         <is>
-          <t>T-6096</t>
+          <t>T-6139</t>
         </is>
       </c>
       <c r="C446" s="8" t="inlineStr">
         <is>
-          <t>HU-183</t>
+          <t>HU-202</t>
         </is>
       </c>
       <c r="D446" s="8" t="inlineStr">
         <is>
-          <t>Consultar los costos de mantenimiento</t>
+          <t>Importar el plan anual desde una planilla</t>
         </is>
       </c>
       <c r="E446" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F446" s="8" t="inlineStr">
@@ -30093,7 +30097,7 @@
       </c>
       <c r="H446" s="9" t="inlineStr">
         <is>
-          <t>Datos de prueba en Indicador_Valor para poder ejercitar los criterios de aceptación.</t>
+          <t>Modelo: revisar Importacion_Carga — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
         </is>
       </c>
       <c r="I446" s="8" t="inlineStr">
@@ -30102,7 +30106,7 @@
         </is>
       </c>
       <c r="J446" s="8" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="K446" s="8" t="inlineStr">
         <is>
@@ -30111,7 +30115,7 @@
       </c>
       <c r="L446" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M446" s="8" t="inlineStr"/>
@@ -30126,22 +30130,22 @@
       </c>
       <c r="B447" s="8" t="inlineStr">
         <is>
-          <t>T-6099</t>
+          <t>T-6140</t>
         </is>
       </c>
       <c r="C447" s="8" t="inlineStr">
         <is>
-          <t>HU-183</t>
+          <t>HU-202</t>
         </is>
       </c>
       <c r="D447" s="8" t="inlineStr">
         <is>
-          <t>Consultar los costos de mantenimiento</t>
+          <t>Importar el plan anual desde una planilla</t>
         </is>
       </c>
       <c r="E447" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F447" s="8" t="inlineStr">
@@ -30156,25 +30160,25 @@
       </c>
       <c r="H447" s="9" t="inlineStr">
         <is>
-          <t>Pantalla IndicadorCosto.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
+          <t>SP IMPORTACION_PLAN: el proceso completo dentro de una transacción, con SET XACT_ABORT ON para que un error no deje datos a medias.</t>
         </is>
       </c>
       <c r="I447" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J447" s="8" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="K447" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L447" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M447" s="8" t="inlineStr"/>
@@ -30189,22 +30193,22 @@
       </c>
       <c r="B448" s="8" t="inlineStr">
         <is>
-          <t>T-6100</t>
+          <t>T-6141</t>
         </is>
       </c>
       <c r="C448" s="8" t="inlineStr">
         <is>
-          <t>HU-183</t>
+          <t>HU-202</t>
         </is>
       </c>
       <c r="D448" s="8" t="inlineStr">
         <is>
-          <t>Consultar los costos de mantenimiento</t>
+          <t>Importar el plan anual desde una planilla</t>
         </is>
       </c>
       <c r="E448" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F448" s="8" t="inlineStr">
@@ -30219,25 +30223,25 @@
       </c>
       <c r="H448" s="9" t="inlineStr">
         <is>
-          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
+          <t>Reglas de negocio de la historia en el SP, no en la pantalla: la API y la web tienen que obtener el mismo resultado.</t>
         </is>
       </c>
       <c r="I448" s="8" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J448" s="8" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="K448" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L448" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M448" s="8" t="inlineStr"/>
@@ -30252,22 +30256,22 @@
       </c>
       <c r="B449" s="8" t="inlineStr">
         <is>
-          <t>T-6101</t>
+          <t>T-6142</t>
         </is>
       </c>
       <c r="C449" s="8" t="inlineStr">
         <is>
-          <t>HU-183</t>
+          <t>HU-202</t>
         </is>
       </c>
       <c r="D449" s="8" t="inlineStr">
         <is>
-          <t>Consultar los costos de mantenimiento</t>
+          <t>Importar el plan anual desde una planilla</t>
         </is>
       </c>
       <c r="E449" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F449" s="8" t="inlineStr">
@@ -30282,12 +30286,12 @@
       </c>
       <c r="H449" s="9" t="inlineStr">
         <is>
-          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
+          <t>SP SEL_IMPORTACION_PLAN: consultar el resultado del proceso.</t>
         </is>
       </c>
       <c r="I449" s="8" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J449" s="8" t="n">
@@ -30300,7 +30304,7 @@
       </c>
       <c r="L449" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M449" s="8" t="inlineStr"/>
@@ -30315,22 +30319,22 @@
       </c>
       <c r="B450" s="8" t="inlineStr">
         <is>
-          <t>T-6102</t>
+          <t>T-6143</t>
         </is>
       </c>
       <c r="C450" s="8" t="inlineStr">
         <is>
-          <t>HU-183</t>
+          <t>HU-202</t>
         </is>
       </c>
       <c r="D450" s="8" t="inlineStr">
         <is>
-          <t>Consultar los costos de mantenimiento</t>
+          <t>Importar el plan anual desde una planilla</t>
         </is>
       </c>
       <c r="E450" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F450" s="8" t="inlineStr">
@@ -30345,25 +30349,25 @@
       </c>
       <c r="H450" s="9" t="inlineStr">
         <is>
-          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
+          <t>Datos de prueba en Importacion_Carga para poder ejercitar los criterios de aceptación.</t>
         </is>
       </c>
       <c r="I450" s="8" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J450" s="8" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="K450" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L450" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M450" s="8" t="inlineStr"/>
@@ -30378,22 +30382,22 @@
       </c>
       <c r="B451" s="8" t="inlineStr">
         <is>
-          <t>T-6103</t>
+          <t>T-6146</t>
         </is>
       </c>
       <c r="C451" s="8" t="inlineStr">
         <is>
-          <t>HU-183</t>
+          <t>HU-202</t>
         </is>
       </c>
       <c r="D451" s="8" t="inlineStr">
         <is>
-          <t>Consultar los costos de mantenimiento</t>
+          <t>Importar el plan anual desde una planilla</t>
         </is>
       </c>
       <c r="E451" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F451" s="8" t="inlineStr">
@@ -30408,25 +30412,25 @@
       </c>
       <c r="H451" s="9" t="inlineStr">
         <is>
-          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
+          <t>Pantalla ImportacionPlan.aspx: disparar el proceso, mostrar el resultado y dejar constancia de quién lo ejecutó.</t>
         </is>
       </c>
       <c r="I451" s="8" t="inlineStr">
         <is>
-          <t>Validación</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="J451" s="8" t="n">
-        <v>0.25</v>
+        <v>4</v>
       </c>
       <c r="K451" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L451" s="8" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="M451" s="8" t="inlineStr"/>
@@ -30441,22 +30445,22 @@
       </c>
       <c r="B452" s="8" t="inlineStr">
         <is>
-          <t>T-6116</t>
+          <t>T-6147</t>
         </is>
       </c>
       <c r="C452" s="8" t="inlineStr">
         <is>
-          <t>HU-184</t>
+          <t>HU-202</t>
         </is>
       </c>
       <c r="D452" s="8" t="inlineStr">
         <is>
-          <t>Consultar la bandeja de alertas</t>
+          <t>Importar el plan anual desde una planilla</t>
         </is>
       </c>
       <c r="E452" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F452" s="8" t="inlineStr">
@@ -30466,25 +30470,25 @@
       </c>
       <c r="G452" s="8" t="inlineStr">
         <is>
-          <t>Web y App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H452" s="9" t="inlineStr">
         <is>
-          <t>Modelo: revisar Alerta — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
+          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
         </is>
       </c>
       <c r="I452" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="J452" s="8" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="K452" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L452" s="8" t="inlineStr">
@@ -30504,22 +30508,22 @@
       </c>
       <c r="B453" s="8" t="inlineStr">
         <is>
-          <t>T-6117</t>
+          <t>T-6148</t>
         </is>
       </c>
       <c r="C453" s="8" t="inlineStr">
         <is>
-          <t>HU-184</t>
+          <t>HU-202</t>
         </is>
       </c>
       <c r="D453" s="8" t="inlineStr">
         <is>
-          <t>Consultar la bandeja de alertas</t>
+          <t>Importar el plan anual desde una planilla</t>
         </is>
       </c>
       <c r="E453" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F453" s="8" t="inlineStr">
@@ -30529,30 +30533,30 @@
       </c>
       <c r="G453" s="8" t="inlineStr">
         <is>
-          <t>Web y App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H453" s="9" t="inlineStr">
         <is>
-          <t>SP SEL_ALERTA: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
+          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
         </is>
       </c>
       <c r="I453" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="J453" s="8" t="n">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
       <c r="K453" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L453" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M453" s="8" t="inlineStr"/>
@@ -30567,22 +30571,22 @@
       </c>
       <c r="B454" s="8" t="inlineStr">
         <is>
-          <t>T-6118</t>
+          <t>T-6149</t>
         </is>
       </c>
       <c r="C454" s="8" t="inlineStr">
         <is>
-          <t>HU-184</t>
+          <t>HU-202</t>
         </is>
       </c>
       <c r="D454" s="8" t="inlineStr">
         <is>
-          <t>Consultar la bandeja de alertas</t>
+          <t>Importar el plan anual desde una planilla</t>
         </is>
       </c>
       <c r="E454" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F454" s="8" t="inlineStr">
@@ -30592,30 +30596,30 @@
       </c>
       <c r="G454" s="8" t="inlineStr">
         <is>
-          <t>Web y App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H454" s="9" t="inlineStr">
         <is>
-          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Alerta crezca.</t>
+          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
         </is>
       </c>
       <c r="I454" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="J454" s="8" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K454" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L454" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M454" s="8" t="inlineStr"/>
@@ -30630,22 +30634,22 @@
       </c>
       <c r="B455" s="8" t="inlineStr">
         <is>
-          <t>T-6119</t>
+          <t>T-6150</t>
         </is>
       </c>
       <c r="C455" s="8" t="inlineStr">
         <is>
-          <t>HU-184</t>
+          <t>HU-202</t>
         </is>
       </c>
       <c r="D455" s="8" t="inlineStr">
         <is>
-          <t>Consultar la bandeja de alertas</t>
+          <t>Importar el plan anual desde una planilla</t>
         </is>
       </c>
       <c r="E455" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F455" s="8" t="inlineStr">
@@ -30655,17 +30659,17 @@
       </c>
       <c r="G455" s="8" t="inlineStr">
         <is>
-          <t>Web y App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H455" s="9" t="inlineStr">
         <is>
-          <t>Datos de prueba en Alerta para poder ejercitar los criterios de aceptación.</t>
+          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
         </is>
       </c>
       <c r="I455" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Validación</t>
         </is>
       </c>
       <c r="J455" s="8" t="n">
@@ -30678,3484 +30682,15 @@
       </c>
       <c r="L455" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M455" s="8" t="inlineStr"/>
       <c r="N455" s="8" t="inlineStr"/>
       <c r="O455" s="8" t="inlineStr"/>
     </row>
-    <row r="456">
-      <c r="A456" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B456" s="8" t="inlineStr">
-        <is>
-          <t>T-6120</t>
-        </is>
-      </c>
-      <c r="C456" s="8" t="inlineStr">
-        <is>
-          <t>HU-184</t>
-        </is>
-      </c>
-      <c r="D456" s="8" t="inlineStr">
-        <is>
-          <t>Consultar la bandeja de alertas</t>
-        </is>
-      </c>
-      <c r="E456" s="8" t="inlineStr">
-        <is>
-          <t>EP-18</t>
-        </is>
-      </c>
-      <c r="F456" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G456" s="8" t="inlineStr">
-        <is>
-          <t>Web y App</t>
-        </is>
-      </c>
-      <c r="H456" s="9" t="inlineStr">
-        <is>
-          <t>GET /api/alertas — consulta con filtros y paginación.</t>
-        </is>
-      </c>
-      <c r="I456" s="8" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="J456" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K456" s="8" t="inlineStr">
-        <is>
-          <t>Emilio Fuentes</t>
-        </is>
-      </c>
-      <c r="L456" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M456" s="8" t="inlineStr"/>
-      <c r="N456" s="8" t="inlineStr"/>
-      <c r="O456" s="8" t="inlineStr"/>
-    </row>
-    <row r="457">
-      <c r="A457" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B457" s="8" t="inlineStr">
-        <is>
-          <t>T-6121</t>
-        </is>
-      </c>
-      <c r="C457" s="8" t="inlineStr">
-        <is>
-          <t>HU-184</t>
-        </is>
-      </c>
-      <c r="D457" s="8" t="inlineStr">
-        <is>
-          <t>Consultar la bandeja de alertas</t>
-        </is>
-      </c>
-      <c r="E457" s="8" t="inlineStr">
-        <is>
-          <t>EP-18</t>
-        </is>
-      </c>
-      <c r="F457" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G457" s="8" t="inlineStr">
-        <is>
-          <t>Web y App</t>
-        </is>
-      </c>
-      <c r="H457" s="9" t="inlineStr">
-        <is>
-          <t>Caché corta de la respuesta cuando el dato no cambia por petición.</t>
-        </is>
-      </c>
-      <c r="I457" s="8" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="J457" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K457" s="8" t="inlineStr">
-        <is>
-          <t>Bryan Chávez</t>
-        </is>
-      </c>
-      <c r="L457" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M457" s="8" t="inlineStr"/>
-      <c r="N457" s="8" t="inlineStr"/>
-      <c r="O457" s="8" t="inlineStr"/>
-    </row>
-    <row r="458">
-      <c r="A458" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B458" s="8" t="inlineStr">
-        <is>
-          <t>T-6122</t>
-        </is>
-      </c>
-      <c r="C458" s="8" t="inlineStr">
-        <is>
-          <t>HU-184</t>
-        </is>
-      </c>
-      <c r="D458" s="8" t="inlineStr">
-        <is>
-          <t>Consultar la bandeja de alertas</t>
-        </is>
-      </c>
-      <c r="E458" s="8" t="inlineStr">
-        <is>
-          <t>EP-18</t>
-        </is>
-      </c>
-      <c r="F458" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G458" s="8" t="inlineStr">
-        <is>
-          <t>Web y App</t>
-        </is>
-      </c>
-      <c r="H458" s="9" t="inlineStr">
-        <is>
-          <t>Pantalla Alerta.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
-        </is>
-      </c>
-      <c r="I458" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="J458" s="8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K458" s="8" t="inlineStr">
-        <is>
-          <t>Emilio Fuentes</t>
-        </is>
-      </c>
-      <c r="L458" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M458" s="8" t="inlineStr"/>
-      <c r="N458" s="8" t="inlineStr"/>
-      <c r="O458" s="8" t="inlineStr"/>
-    </row>
-    <row r="459">
-      <c r="A459" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B459" s="8" t="inlineStr">
-        <is>
-          <t>T-6123</t>
-        </is>
-      </c>
-      <c r="C459" s="8" t="inlineStr">
-        <is>
-          <t>HU-184</t>
-        </is>
-      </c>
-      <c r="D459" s="8" t="inlineStr">
-        <is>
-          <t>Consultar la bandeja de alertas</t>
-        </is>
-      </c>
-      <c r="E459" s="8" t="inlineStr">
-        <is>
-          <t>EP-18</t>
-        </is>
-      </c>
-      <c r="F459" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G459" s="8" t="inlineStr">
-        <is>
-          <t>Web y App</t>
-        </is>
-      </c>
-      <c r="H459" s="9" t="inlineStr">
-        <is>
-          <t>Consumo del endpoint desde la app cuando corresponda.</t>
-        </is>
-      </c>
-      <c r="I459" s="8" t="inlineStr">
-        <is>
-          <t>Móvil</t>
-        </is>
-      </c>
-      <c r="J459" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K459" s="8" t="inlineStr">
-        <is>
-          <t>Emilio Fuentes</t>
-        </is>
-      </c>
-      <c r="L459" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M459" s="8" t="inlineStr"/>
-      <c r="N459" s="8" t="inlineStr"/>
-      <c r="O459" s="8" t="inlineStr"/>
-    </row>
-    <row r="460">
-      <c r="A460" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B460" s="8" t="inlineStr">
-        <is>
-          <t>T-6124</t>
-        </is>
-      </c>
-      <c r="C460" s="8" t="inlineStr">
-        <is>
-          <t>HU-184</t>
-        </is>
-      </c>
-      <c r="D460" s="8" t="inlineStr">
-        <is>
-          <t>Consultar la bandeja de alertas</t>
-        </is>
-      </c>
-      <c r="E460" s="8" t="inlineStr">
-        <is>
-          <t>EP-18</t>
-        </is>
-      </c>
-      <c r="F460" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G460" s="8" t="inlineStr">
-        <is>
-          <t>Web y App</t>
-        </is>
-      </c>
-      <c r="H460" s="9" t="inlineStr">
-        <is>
-          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
-        </is>
-      </c>
-      <c r="I460" s="8" t="inlineStr">
-        <is>
-          <t>Seguridad</t>
-        </is>
-      </c>
-      <c r="J460" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K460" s="8" t="inlineStr">
-        <is>
-          <t>Bryan Chávez</t>
-        </is>
-      </c>
-      <c r="L460" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M460" s="8" t="inlineStr"/>
-      <c r="N460" s="8" t="inlineStr"/>
-      <c r="O460" s="8" t="inlineStr"/>
-    </row>
-    <row r="461">
-      <c r="A461" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B461" s="8" t="inlineStr">
-        <is>
-          <t>T-6125</t>
-        </is>
-      </c>
-      <c r="C461" s="8" t="inlineStr">
-        <is>
-          <t>HU-184</t>
-        </is>
-      </c>
-      <c r="D461" s="8" t="inlineStr">
-        <is>
-          <t>Consultar la bandeja de alertas</t>
-        </is>
-      </c>
-      <c r="E461" s="8" t="inlineStr">
-        <is>
-          <t>EP-18</t>
-        </is>
-      </c>
-      <c r="F461" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G461" s="8" t="inlineStr">
-        <is>
-          <t>Web y App</t>
-        </is>
-      </c>
-      <c r="H461" s="9" t="inlineStr">
-        <is>
-          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="I461" s="8" t="inlineStr">
-        <is>
-          <t>Pruebas</t>
-        </is>
-      </c>
-      <c r="J461" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K461" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L461" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M461" s="8" t="inlineStr"/>
-      <c r="N461" s="8" t="inlineStr"/>
-      <c r="O461" s="8" t="inlineStr"/>
-    </row>
-    <row r="462">
-      <c r="A462" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B462" s="8" t="inlineStr">
-        <is>
-          <t>T-6126</t>
-        </is>
-      </c>
-      <c r="C462" s="8" t="inlineStr">
-        <is>
-          <t>HU-184</t>
-        </is>
-      </c>
-      <c r="D462" s="8" t="inlineStr">
-        <is>
-          <t>Consultar la bandeja de alertas</t>
-        </is>
-      </c>
-      <c r="E462" s="8" t="inlineStr">
-        <is>
-          <t>EP-18</t>
-        </is>
-      </c>
-      <c r="F462" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G462" s="8" t="inlineStr">
-        <is>
-          <t>Web y App</t>
-        </is>
-      </c>
-      <c r="H462" s="9" t="inlineStr">
-        <is>
-          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
-        </is>
-      </c>
-      <c r="I462" s="8" t="inlineStr">
-        <is>
-          <t>Documentación</t>
-        </is>
-      </c>
-      <c r="J462" s="8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K462" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L462" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M462" s="8" t="inlineStr"/>
-      <c r="N462" s="8" t="inlineStr"/>
-      <c r="O462" s="8" t="inlineStr"/>
-    </row>
-    <row r="463">
-      <c r="A463" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B463" s="8" t="inlineStr">
-        <is>
-          <t>T-6192</t>
-        </is>
-      </c>
-      <c r="C463" s="8" t="inlineStr">
-        <is>
-          <t>HU-185</t>
-        </is>
-      </c>
-      <c r="D463" s="8" t="inlineStr">
-        <is>
-          <t>Exportar e imprimir reportes</t>
-        </is>
-      </c>
-      <c r="E463" s="8" t="inlineStr">
-        <is>
-          <t>EP-18</t>
-        </is>
-      </c>
-      <c r="F463" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G463" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H463" s="9" t="inlineStr">
-        <is>
-          <t>Modelo: CREAR la tabla Indicador_Valor — todavía no existe. Columnas, PK, FK a sus padres y columna ind_uuid con índice UNIQUE para que la sincronización no duplique.</t>
-        </is>
-      </c>
-      <c r="I463" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J463" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K463" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L463" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M463" s="8" t="inlineStr"/>
-      <c r="N463" s="8" t="inlineStr"/>
-      <c r="O463" s="8" t="inlineStr"/>
-    </row>
-    <row r="464">
-      <c r="A464" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B464" s="8" t="inlineStr">
-        <is>
-          <t>T-6193</t>
-        </is>
-      </c>
-      <c r="C464" s="8" t="inlineStr">
-        <is>
-          <t>HU-185</t>
-        </is>
-      </c>
-      <c r="D464" s="8" t="inlineStr">
-        <is>
-          <t>Exportar e imprimir reportes</t>
-        </is>
-      </c>
-      <c r="E464" s="8" t="inlineStr">
-        <is>
-          <t>EP-18</t>
-        </is>
-      </c>
-      <c r="F464" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G464" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H464" s="9" t="inlineStr">
-        <is>
-          <t>SP INDICADOR_EXPORTAR: el proceso completo dentro de una transacción, con SET XACT_ABORT ON para que un error no deje datos a medias.</t>
-        </is>
-      </c>
-      <c r="I464" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J464" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K464" s="8" t="inlineStr">
-        <is>
-          <t>Bryan Chávez</t>
-        </is>
-      </c>
-      <c r="L464" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M464" s="8" t="inlineStr"/>
-      <c r="N464" s="8" t="inlineStr"/>
-      <c r="O464" s="8" t="inlineStr"/>
-    </row>
-    <row r="465">
-      <c r="A465" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B465" s="8" t="inlineStr">
-        <is>
-          <t>T-6194</t>
-        </is>
-      </c>
-      <c r="C465" s="8" t="inlineStr">
-        <is>
-          <t>HU-185</t>
-        </is>
-      </c>
-      <c r="D465" s="8" t="inlineStr">
-        <is>
-          <t>Exportar e imprimir reportes</t>
-        </is>
-      </c>
-      <c r="E465" s="8" t="inlineStr">
-        <is>
-          <t>EP-18</t>
-        </is>
-      </c>
-      <c r="F465" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G465" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H465" s="9" t="inlineStr">
-        <is>
-          <t>Reglas de negocio de la historia en el SP, no en la pantalla: la API y la web tienen que obtener el mismo resultado.</t>
-        </is>
-      </c>
-      <c r="I465" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J465" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K465" s="8" t="inlineStr">
-        <is>
-          <t>Emilio Fuentes</t>
-        </is>
-      </c>
-      <c r="L465" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M465" s="8" t="inlineStr"/>
-      <c r="N465" s="8" t="inlineStr"/>
-      <c r="O465" s="8" t="inlineStr"/>
-    </row>
-    <row r="466">
-      <c r="A466" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B466" s="8" t="inlineStr">
-        <is>
-          <t>T-6195</t>
-        </is>
-      </c>
-      <c r="C466" s="8" t="inlineStr">
-        <is>
-          <t>HU-185</t>
-        </is>
-      </c>
-      <c r="D466" s="8" t="inlineStr">
-        <is>
-          <t>Exportar e imprimir reportes</t>
-        </is>
-      </c>
-      <c r="E466" s="8" t="inlineStr">
-        <is>
-          <t>EP-18</t>
-        </is>
-      </c>
-      <c r="F466" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G466" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H466" s="9" t="inlineStr">
-        <is>
-          <t>SP SEL_INDICADOR_EXPORTAR: consultar el resultado del proceso.</t>
-        </is>
-      </c>
-      <c r="I466" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J466" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K466" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L466" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M466" s="8" t="inlineStr"/>
-      <c r="N466" s="8" t="inlineStr"/>
-      <c r="O466" s="8" t="inlineStr"/>
-    </row>
-    <row r="467">
-      <c r="A467" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B467" s="8" t="inlineStr">
-        <is>
-          <t>T-6196</t>
-        </is>
-      </c>
-      <c r="C467" s="8" t="inlineStr">
-        <is>
-          <t>HU-185</t>
-        </is>
-      </c>
-      <c r="D467" s="8" t="inlineStr">
-        <is>
-          <t>Exportar e imprimir reportes</t>
-        </is>
-      </c>
-      <c r="E467" s="8" t="inlineStr">
-        <is>
-          <t>EP-18</t>
-        </is>
-      </c>
-      <c r="F467" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G467" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H467" s="9" t="inlineStr">
-        <is>
-          <t>Datos de prueba en Indicador_Valor para poder ejercitar los criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="I467" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J467" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K467" s="8" t="inlineStr">
-        <is>
-          <t>Bryan Chávez</t>
-        </is>
-      </c>
-      <c r="L467" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M467" s="8" t="inlineStr"/>
-      <c r="N467" s="8" t="inlineStr"/>
-      <c r="O467" s="8" t="inlineStr"/>
-    </row>
-    <row r="468">
-      <c r="A468" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B468" s="8" t="inlineStr">
-        <is>
-          <t>T-6199</t>
-        </is>
-      </c>
-      <c r="C468" s="8" t="inlineStr">
-        <is>
-          <t>HU-185</t>
-        </is>
-      </c>
-      <c r="D468" s="8" t="inlineStr">
-        <is>
-          <t>Exportar e imprimir reportes</t>
-        </is>
-      </c>
-      <c r="E468" s="8" t="inlineStr">
-        <is>
-          <t>EP-18</t>
-        </is>
-      </c>
-      <c r="F468" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G468" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H468" s="9" t="inlineStr">
-        <is>
-          <t>Pantalla IndicadorExportar.aspx: disparar el proceso, mostrar el resultado y dejar constancia de quién lo ejecutó.</t>
-        </is>
-      </c>
-      <c r="I468" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="J468" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K468" s="8" t="inlineStr">
-        <is>
-          <t>Emilio Fuentes</t>
-        </is>
-      </c>
-      <c r="L468" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M468" s="8" t="inlineStr"/>
-      <c r="N468" s="8" t="inlineStr"/>
-      <c r="O468" s="8" t="inlineStr"/>
-    </row>
-    <row r="469">
-      <c r="A469" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B469" s="8" t="inlineStr">
-        <is>
-          <t>T-6200</t>
-        </is>
-      </c>
-      <c r="C469" s="8" t="inlineStr">
-        <is>
-          <t>HU-185</t>
-        </is>
-      </c>
-      <c r="D469" s="8" t="inlineStr">
-        <is>
-          <t>Exportar e imprimir reportes</t>
-        </is>
-      </c>
-      <c r="E469" s="8" t="inlineStr">
-        <is>
-          <t>EP-18</t>
-        </is>
-      </c>
-      <c r="F469" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G469" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H469" s="9" t="inlineStr">
-        <is>
-          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
-        </is>
-      </c>
-      <c r="I469" s="8" t="inlineStr">
-        <is>
-          <t>Seguridad</t>
-        </is>
-      </c>
-      <c r="J469" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K469" s="8" t="inlineStr">
-        <is>
-          <t>Bryan Chávez</t>
-        </is>
-      </c>
-      <c r="L469" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M469" s="8" t="inlineStr"/>
-      <c r="N469" s="8" t="inlineStr"/>
-      <c r="O469" s="8" t="inlineStr"/>
-    </row>
-    <row r="470">
-      <c r="A470" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B470" s="8" t="inlineStr">
-        <is>
-          <t>T-6201</t>
-        </is>
-      </c>
-      <c r="C470" s="8" t="inlineStr">
-        <is>
-          <t>HU-185</t>
-        </is>
-      </c>
-      <c r="D470" s="8" t="inlineStr">
-        <is>
-          <t>Exportar e imprimir reportes</t>
-        </is>
-      </c>
-      <c r="E470" s="8" t="inlineStr">
-        <is>
-          <t>EP-18</t>
-        </is>
-      </c>
-      <c r="F470" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G470" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H470" s="9" t="inlineStr">
-        <is>
-          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="I470" s="8" t="inlineStr">
-        <is>
-          <t>Pruebas</t>
-        </is>
-      </c>
-      <c r="J470" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K470" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L470" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M470" s="8" t="inlineStr"/>
-      <c r="N470" s="8" t="inlineStr"/>
-      <c r="O470" s="8" t="inlineStr"/>
-    </row>
-    <row r="471">
-      <c r="A471" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B471" s="8" t="inlineStr">
-        <is>
-          <t>T-6202</t>
-        </is>
-      </c>
-      <c r="C471" s="8" t="inlineStr">
-        <is>
-          <t>HU-185</t>
-        </is>
-      </c>
-      <c r="D471" s="8" t="inlineStr">
-        <is>
-          <t>Exportar e imprimir reportes</t>
-        </is>
-      </c>
-      <c r="E471" s="8" t="inlineStr">
-        <is>
-          <t>EP-18</t>
-        </is>
-      </c>
-      <c r="F471" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G471" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H471" s="9" t="inlineStr">
-        <is>
-          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
-        </is>
-      </c>
-      <c r="I471" s="8" t="inlineStr">
-        <is>
-          <t>Documentación</t>
-        </is>
-      </c>
-      <c r="J471" s="8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K471" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L471" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M471" s="8" t="inlineStr"/>
-      <c r="N471" s="8" t="inlineStr"/>
-      <c r="O471" s="8" t="inlineStr"/>
-    </row>
-    <row r="472">
-      <c r="A472" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B472" s="8" t="inlineStr">
-        <is>
-          <t>T-2142</t>
-        </is>
-      </c>
-      <c r="C472" s="8" t="inlineStr">
-        <is>
-          <t>HU-193</t>
-        </is>
-      </c>
-      <c r="D472" s="8" t="inlineStr">
-        <is>
-          <t>Bloquear el acceso por suscripción vencida</t>
-        </is>
-      </c>
-      <c r="E472" s="8" t="inlineStr">
-        <is>
-          <t>EP-19</t>
-        </is>
-      </c>
-      <c r="F472" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 2</t>
-        </is>
-      </c>
-      <c r="G472" s="8" t="inlineStr">
-        <is>
-          <t>Web y App</t>
-        </is>
-      </c>
-      <c r="H472" s="9" t="inlineStr">
-        <is>
-          <t>Consumo del endpoint desde la app cuando corresponda.</t>
-        </is>
-      </c>
-      <c r="I472" s="8" t="inlineStr">
-        <is>
-          <t>Móvil</t>
-        </is>
-      </c>
-      <c r="J472" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K472" s="8" t="inlineStr">
-        <is>
-          <t>Emilio Fuentes</t>
-        </is>
-      </c>
-      <c r="L472" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M472" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="N472" s="8" t="inlineStr"/>
-      <c r="O472" s="8" t="inlineStr"/>
-    </row>
-    <row r="473">
-      <c r="A473" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B473" s="8" t="inlineStr">
-        <is>
-          <t>T-6104</t>
-        </is>
-      </c>
-      <c r="C473" s="8" t="inlineStr">
-        <is>
-          <t>HU-200</t>
-        </is>
-      </c>
-      <c r="D473" s="8" t="inlineStr">
-        <is>
-          <t>Importar activos desde una planilla</t>
-        </is>
-      </c>
-      <c r="E473" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F473" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G473" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H473" s="9" t="inlineStr">
-        <is>
-          <t>Modelo: revisar Importacion_Carga — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
-        </is>
-      </c>
-      <c r="I473" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J473" s="8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K473" s="8" t="inlineStr">
-        <is>
-          <t>Bryan Chávez</t>
-        </is>
-      </c>
-      <c r="L473" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M473" s="8" t="inlineStr"/>
-      <c r="N473" s="8" t="inlineStr"/>
-      <c r="O473" s="8" t="inlineStr"/>
-    </row>
-    <row r="474">
-      <c r="A474" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B474" s="8" t="inlineStr">
-        <is>
-          <t>T-6105</t>
-        </is>
-      </c>
-      <c r="C474" s="8" t="inlineStr">
-        <is>
-          <t>HU-200</t>
-        </is>
-      </c>
-      <c r="D474" s="8" t="inlineStr">
-        <is>
-          <t>Importar activos desde una planilla</t>
-        </is>
-      </c>
-      <c r="E474" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F474" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G474" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H474" s="9" t="inlineStr">
-        <is>
-          <t>SP IMPORTACION_ACTIVO: el proceso completo dentro de una transacción, con SET XACT_ABORT ON para que un error no deje datos a medias.</t>
-        </is>
-      </c>
-      <c r="I474" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J474" s="8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K474" s="8" t="inlineStr">
-        <is>
-          <t>Emilio Fuentes</t>
-        </is>
-      </c>
-      <c r="L474" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M474" s="8" t="inlineStr"/>
-      <c r="N474" s="8" t="inlineStr"/>
-      <c r="O474" s="8" t="inlineStr"/>
-    </row>
-    <row r="475">
-      <c r="A475" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B475" s="8" t="inlineStr">
-        <is>
-          <t>T-6106</t>
-        </is>
-      </c>
-      <c r="C475" s="8" t="inlineStr">
-        <is>
-          <t>HU-200</t>
-        </is>
-      </c>
-      <c r="D475" s="8" t="inlineStr">
-        <is>
-          <t>Importar activos desde una planilla</t>
-        </is>
-      </c>
-      <c r="E475" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F475" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G475" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H475" s="9" t="inlineStr">
-        <is>
-          <t>Reglas de negocio de la historia en el SP, no en la pantalla: la API y la web tienen que obtener el mismo resultado.</t>
-        </is>
-      </c>
-      <c r="I475" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J475" s="8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K475" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L475" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M475" s="8" t="inlineStr"/>
-      <c r="N475" s="8" t="inlineStr"/>
-      <c r="O475" s="8" t="inlineStr"/>
-    </row>
-    <row r="476">
-      <c r="A476" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B476" s="8" t="inlineStr">
-        <is>
-          <t>T-6107</t>
-        </is>
-      </c>
-      <c r="C476" s="8" t="inlineStr">
-        <is>
-          <t>HU-200</t>
-        </is>
-      </c>
-      <c r="D476" s="8" t="inlineStr">
-        <is>
-          <t>Importar activos desde una planilla</t>
-        </is>
-      </c>
-      <c r="E476" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F476" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G476" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H476" s="9" t="inlineStr">
-        <is>
-          <t>SP SEL_IMPORTACION_ACTIVO: consultar el resultado del proceso.</t>
-        </is>
-      </c>
-      <c r="I476" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J476" s="8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K476" s="8" t="inlineStr">
-        <is>
-          <t>Bryan Chávez</t>
-        </is>
-      </c>
-      <c r="L476" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M476" s="8" t="inlineStr"/>
-      <c r="N476" s="8" t="inlineStr"/>
-      <c r="O476" s="8" t="inlineStr"/>
-    </row>
-    <row r="477">
-      <c r="A477" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B477" s="8" t="inlineStr">
-        <is>
-          <t>T-6108</t>
-        </is>
-      </c>
-      <c r="C477" s="8" t="inlineStr">
-        <is>
-          <t>HU-200</t>
-        </is>
-      </c>
-      <c r="D477" s="8" t="inlineStr">
-        <is>
-          <t>Importar activos desde una planilla</t>
-        </is>
-      </c>
-      <c r="E477" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F477" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G477" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H477" s="9" t="inlineStr">
-        <is>
-          <t>Datos de prueba en Importacion_Carga para poder ejercitar los criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="I477" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J477" s="8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K477" s="8" t="inlineStr">
-        <is>
-          <t>Emilio Fuentes</t>
-        </is>
-      </c>
-      <c r="L477" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M477" s="8" t="inlineStr"/>
-      <c r="N477" s="8" t="inlineStr"/>
-      <c r="O477" s="8" t="inlineStr"/>
-    </row>
-    <row r="478">
-      <c r="A478" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B478" s="8" t="inlineStr">
-        <is>
-          <t>T-6111</t>
-        </is>
-      </c>
-      <c r="C478" s="8" t="inlineStr">
-        <is>
-          <t>HU-200</t>
-        </is>
-      </c>
-      <c r="D478" s="8" t="inlineStr">
-        <is>
-          <t>Importar activos desde una planilla</t>
-        </is>
-      </c>
-      <c r="E478" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F478" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G478" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H478" s="9" t="inlineStr">
-        <is>
-          <t>Pantalla ImportacionActivo.aspx: disparar el proceso, mostrar el resultado y dejar constancia de quién lo ejecutó.</t>
-        </is>
-      </c>
-      <c r="I478" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="J478" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K478" s="8" t="inlineStr">
-        <is>
-          <t>Bryan Chávez</t>
-        </is>
-      </c>
-      <c r="L478" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M478" s="8" t="inlineStr"/>
-      <c r="N478" s="8" t="inlineStr"/>
-      <c r="O478" s="8" t="inlineStr"/>
-    </row>
-    <row r="479">
-      <c r="A479" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B479" s="8" t="inlineStr">
-        <is>
-          <t>T-6112</t>
-        </is>
-      </c>
-      <c r="C479" s="8" t="inlineStr">
-        <is>
-          <t>HU-200</t>
-        </is>
-      </c>
-      <c r="D479" s="8" t="inlineStr">
-        <is>
-          <t>Importar activos desde una planilla</t>
-        </is>
-      </c>
-      <c r="E479" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F479" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G479" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H479" s="9" t="inlineStr">
-        <is>
-          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
-        </is>
-      </c>
-      <c r="I479" s="8" t="inlineStr">
-        <is>
-          <t>Seguridad</t>
-        </is>
-      </c>
-      <c r="J479" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K479" s="8" t="inlineStr">
-        <is>
-          <t>Emilio Fuentes</t>
-        </is>
-      </c>
-      <c r="L479" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M479" s="8" t="inlineStr"/>
-      <c r="N479" s="8" t="inlineStr"/>
-      <c r="O479" s="8" t="inlineStr"/>
-    </row>
-    <row r="480">
-      <c r="A480" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B480" s="8" t="inlineStr">
-        <is>
-          <t>T-6113</t>
-        </is>
-      </c>
-      <c r="C480" s="8" t="inlineStr">
-        <is>
-          <t>HU-200</t>
-        </is>
-      </c>
-      <c r="D480" s="8" t="inlineStr">
-        <is>
-          <t>Importar activos desde una planilla</t>
-        </is>
-      </c>
-      <c r="E480" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F480" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G480" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H480" s="9" t="inlineStr">
-        <is>
-          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="I480" s="8" t="inlineStr">
-        <is>
-          <t>Pruebas</t>
-        </is>
-      </c>
-      <c r="J480" s="8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="K480" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L480" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M480" s="8" t="inlineStr"/>
-      <c r="N480" s="8" t="inlineStr"/>
-      <c r="O480" s="8" t="inlineStr"/>
-    </row>
-    <row r="481">
-      <c r="A481" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B481" s="8" t="inlineStr">
-        <is>
-          <t>T-6114</t>
-        </is>
-      </c>
-      <c r="C481" s="8" t="inlineStr">
-        <is>
-          <t>HU-200</t>
-        </is>
-      </c>
-      <c r="D481" s="8" t="inlineStr">
-        <is>
-          <t>Importar activos desde una planilla</t>
-        </is>
-      </c>
-      <c r="E481" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F481" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G481" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H481" s="9" t="inlineStr">
-        <is>
-          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
-        </is>
-      </c>
-      <c r="I481" s="8" t="inlineStr">
-        <is>
-          <t>Documentación</t>
-        </is>
-      </c>
-      <c r="J481" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K481" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L481" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M481" s="8" t="inlineStr"/>
-      <c r="N481" s="8" t="inlineStr"/>
-      <c r="O481" s="8" t="inlineStr"/>
-    </row>
-    <row r="482">
-      <c r="A482" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B482" s="8" t="inlineStr">
-        <is>
-          <t>T-6115</t>
-        </is>
-      </c>
-      <c r="C482" s="8" t="inlineStr">
-        <is>
-          <t>HU-200</t>
-        </is>
-      </c>
-      <c r="D482" s="8" t="inlineStr">
-        <is>
-          <t>Importar activos desde una planilla</t>
-        </is>
-      </c>
-      <c r="E482" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F482" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G482" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H482" s="9" t="inlineStr">
-        <is>
-          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
-        </is>
-      </c>
-      <c r="I482" s="8" t="inlineStr">
-        <is>
-          <t>Validación</t>
-        </is>
-      </c>
-      <c r="J482" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K482" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L482" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M482" s="8" t="inlineStr"/>
-      <c r="N482" s="8" t="inlineStr"/>
-      <c r="O482" s="8" t="inlineStr"/>
-    </row>
-    <row r="483">
-      <c r="A483" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B483" s="8" t="inlineStr">
-        <is>
-          <t>T-6127</t>
-        </is>
-      </c>
-      <c r="C483" s="8" t="inlineStr">
-        <is>
-          <t>HU-201</t>
-        </is>
-      </c>
-      <c r="D483" s="8" t="inlineStr">
-        <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
-        </is>
-      </c>
-      <c r="E483" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F483" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G483" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H483" s="9" t="inlineStr">
-        <is>
-          <t>Modelo: revisar Importacion_Carga_Celda — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
-        </is>
-      </c>
-      <c r="I483" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J483" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K483" s="8" t="inlineStr">
-        <is>
-          <t>Bryan Chávez</t>
-        </is>
-      </c>
-      <c r="L483" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M483" s="8" t="inlineStr"/>
-      <c r="N483" s="8" t="inlineStr"/>
-      <c r="O483" s="8" t="inlineStr"/>
-    </row>
-    <row r="484">
-      <c r="A484" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B484" s="8" t="inlineStr">
-        <is>
-          <t>T-6128</t>
-        </is>
-      </c>
-      <c r="C484" s="8" t="inlineStr">
-        <is>
-          <t>HU-201</t>
-        </is>
-      </c>
-      <c r="D484" s="8" t="inlineStr">
-        <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
-        </is>
-      </c>
-      <c r="E484" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F484" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G484" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H484" s="9" t="inlineStr">
-        <is>
-          <t>SP IMPORTACION_CELDA: el proceso completo dentro de una transacción, con SET XACT_ABORT ON para que un error no deje datos a medias.</t>
-        </is>
-      </c>
-      <c r="I484" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J484" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K484" s="8" t="inlineStr">
-        <is>
-          <t>Emilio Fuentes</t>
-        </is>
-      </c>
-      <c r="L484" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M484" s="8" t="inlineStr"/>
-      <c r="N484" s="8" t="inlineStr"/>
-      <c r="O484" s="8" t="inlineStr"/>
-    </row>
-    <row r="485">
-      <c r="A485" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B485" s="8" t="inlineStr">
-        <is>
-          <t>T-6129</t>
-        </is>
-      </c>
-      <c r="C485" s="8" t="inlineStr">
-        <is>
-          <t>HU-201</t>
-        </is>
-      </c>
-      <c r="D485" s="8" t="inlineStr">
-        <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
-        </is>
-      </c>
-      <c r="E485" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F485" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G485" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H485" s="9" t="inlineStr">
-        <is>
-          <t>Reglas de negocio de la historia en el SP, no en la pantalla: la API y la web tienen que obtener el mismo resultado.</t>
-        </is>
-      </c>
-      <c r="I485" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J485" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K485" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L485" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M485" s="8" t="inlineStr"/>
-      <c r="N485" s="8" t="inlineStr"/>
-      <c r="O485" s="8" t="inlineStr"/>
-    </row>
-    <row r="486">
-      <c r="A486" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B486" s="8" t="inlineStr">
-        <is>
-          <t>T-6130</t>
-        </is>
-      </c>
-      <c r="C486" s="8" t="inlineStr">
-        <is>
-          <t>HU-201</t>
-        </is>
-      </c>
-      <c r="D486" s="8" t="inlineStr">
-        <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
-        </is>
-      </c>
-      <c r="E486" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F486" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G486" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H486" s="9" t="inlineStr">
-        <is>
-          <t>SP SEL_IMPORTACION_CELDA: consultar el resultado del proceso.</t>
-        </is>
-      </c>
-      <c r="I486" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J486" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K486" s="8" t="inlineStr">
-        <is>
-          <t>Bryan Chávez</t>
-        </is>
-      </c>
-      <c r="L486" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M486" s="8" t="inlineStr"/>
-      <c r="N486" s="8" t="inlineStr"/>
-      <c r="O486" s="8" t="inlineStr"/>
-    </row>
-    <row r="487">
-      <c r="A487" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B487" s="8" t="inlineStr">
-        <is>
-          <t>T-6131</t>
-        </is>
-      </c>
-      <c r="C487" s="8" t="inlineStr">
-        <is>
-          <t>HU-201</t>
-        </is>
-      </c>
-      <c r="D487" s="8" t="inlineStr">
-        <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
-        </is>
-      </c>
-      <c r="E487" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F487" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G487" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H487" s="9" t="inlineStr">
-        <is>
-          <t>Datos de prueba en Importacion_Carga_Celda para poder ejercitar los criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="I487" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J487" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K487" s="8" t="inlineStr">
-        <is>
-          <t>Emilio Fuentes</t>
-        </is>
-      </c>
-      <c r="L487" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M487" s="8" t="inlineStr"/>
-      <c r="N487" s="8" t="inlineStr"/>
-      <c r="O487" s="8" t="inlineStr"/>
-    </row>
-    <row r="488">
-      <c r="A488" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B488" s="8" t="inlineStr">
-        <is>
-          <t>T-6134</t>
-        </is>
-      </c>
-      <c r="C488" s="8" t="inlineStr">
-        <is>
-          <t>HU-201</t>
-        </is>
-      </c>
-      <c r="D488" s="8" t="inlineStr">
-        <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
-        </is>
-      </c>
-      <c r="E488" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F488" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G488" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H488" s="9" t="inlineStr">
-        <is>
-          <t>Pantalla ImportacionCelda.aspx: disparar el proceso, mostrar el resultado y dejar constancia de quién lo ejecutó.</t>
-        </is>
-      </c>
-      <c r="I488" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="J488" s="8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="K488" s="8" t="inlineStr">
-        <is>
-          <t>Bryan Chávez</t>
-        </is>
-      </c>
-      <c r="L488" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M488" s="8" t="inlineStr"/>
-      <c r="N488" s="8" t="inlineStr"/>
-      <c r="O488" s="8" t="inlineStr"/>
-    </row>
-    <row r="489">
-      <c r="A489" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B489" s="8" t="inlineStr">
-        <is>
-          <t>T-6135</t>
-        </is>
-      </c>
-      <c r="C489" s="8" t="inlineStr">
-        <is>
-          <t>HU-201</t>
-        </is>
-      </c>
-      <c r="D489" s="8" t="inlineStr">
-        <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
-        </is>
-      </c>
-      <c r="E489" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F489" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G489" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H489" s="9" t="inlineStr">
-        <is>
-          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
-        </is>
-      </c>
-      <c r="I489" s="8" t="inlineStr">
-        <is>
-          <t>Seguridad</t>
-        </is>
-      </c>
-      <c r="J489" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K489" s="8" t="inlineStr">
-        <is>
-          <t>Emilio Fuentes</t>
-        </is>
-      </c>
-      <c r="L489" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M489" s="8" t="inlineStr"/>
-      <c r="N489" s="8" t="inlineStr"/>
-      <c r="O489" s="8" t="inlineStr"/>
-    </row>
-    <row r="490">
-      <c r="A490" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B490" s="8" t="inlineStr">
-        <is>
-          <t>T-6136</t>
-        </is>
-      </c>
-      <c r="C490" s="8" t="inlineStr">
-        <is>
-          <t>HU-201</t>
-        </is>
-      </c>
-      <c r="D490" s="8" t="inlineStr">
-        <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
-        </is>
-      </c>
-      <c r="E490" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F490" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G490" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H490" s="9" t="inlineStr">
-        <is>
-          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="I490" s="8" t="inlineStr">
-        <is>
-          <t>Pruebas</t>
-        </is>
-      </c>
-      <c r="J490" s="8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K490" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L490" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M490" s="8" t="inlineStr"/>
-      <c r="N490" s="8" t="inlineStr"/>
-      <c r="O490" s="8" t="inlineStr"/>
-    </row>
-    <row r="491">
-      <c r="A491" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B491" s="8" t="inlineStr">
-        <is>
-          <t>T-6137</t>
-        </is>
-      </c>
-      <c r="C491" s="8" t="inlineStr">
-        <is>
-          <t>HU-201</t>
-        </is>
-      </c>
-      <c r="D491" s="8" t="inlineStr">
-        <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
-        </is>
-      </c>
-      <c r="E491" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F491" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G491" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H491" s="9" t="inlineStr">
-        <is>
-          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
-        </is>
-      </c>
-      <c r="I491" s="8" t="inlineStr">
-        <is>
-          <t>Documentación</t>
-        </is>
-      </c>
-      <c r="J491" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K491" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L491" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M491" s="8" t="inlineStr"/>
-      <c r="N491" s="8" t="inlineStr"/>
-      <c r="O491" s="8" t="inlineStr"/>
-    </row>
-    <row r="492">
-      <c r="A492" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B492" s="8" t="inlineStr">
-        <is>
-          <t>T-6138</t>
-        </is>
-      </c>
-      <c r="C492" s="8" t="inlineStr">
-        <is>
-          <t>HU-201</t>
-        </is>
-      </c>
-      <c r="D492" s="8" t="inlineStr">
-        <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
-        </is>
-      </c>
-      <c r="E492" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F492" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G492" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H492" s="9" t="inlineStr">
-        <is>
-          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
-        </is>
-      </c>
-      <c r="I492" s="8" t="inlineStr">
-        <is>
-          <t>Validación</t>
-        </is>
-      </c>
-      <c r="J492" s="8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K492" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L492" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M492" s="8" t="inlineStr"/>
-      <c r="N492" s="8" t="inlineStr"/>
-      <c r="O492" s="8" t="inlineStr"/>
-    </row>
-    <row r="493">
-      <c r="A493" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B493" s="8" t="inlineStr">
-        <is>
-          <t>T-6139</t>
-        </is>
-      </c>
-      <c r="C493" s="8" t="inlineStr">
-        <is>
-          <t>HU-202</t>
-        </is>
-      </c>
-      <c r="D493" s="8" t="inlineStr">
-        <is>
-          <t>Importar el plan anual desde una planilla</t>
-        </is>
-      </c>
-      <c r="E493" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F493" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G493" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H493" s="9" t="inlineStr">
-        <is>
-          <t>Modelo: revisar Importacion_Carga — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
-        </is>
-      </c>
-      <c r="I493" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J493" s="8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K493" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L493" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M493" s="8" t="inlineStr"/>
-      <c r="N493" s="8" t="inlineStr"/>
-      <c r="O493" s="8" t="inlineStr"/>
-    </row>
-    <row r="494">
-      <c r="A494" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B494" s="8" t="inlineStr">
-        <is>
-          <t>T-6140</t>
-        </is>
-      </c>
-      <c r="C494" s="8" t="inlineStr">
-        <is>
-          <t>HU-202</t>
-        </is>
-      </c>
-      <c r="D494" s="8" t="inlineStr">
-        <is>
-          <t>Importar el plan anual desde una planilla</t>
-        </is>
-      </c>
-      <c r="E494" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F494" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G494" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H494" s="9" t="inlineStr">
-        <is>
-          <t>SP IMPORTACION_PLAN: el proceso completo dentro de una transacción, con SET XACT_ABORT ON para que un error no deje datos a medias.</t>
-        </is>
-      </c>
-      <c r="I494" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J494" s="8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K494" s="8" t="inlineStr">
-        <is>
-          <t>Bryan Chávez</t>
-        </is>
-      </c>
-      <c r="L494" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M494" s="8" t="inlineStr"/>
-      <c r="N494" s="8" t="inlineStr"/>
-      <c r="O494" s="8" t="inlineStr"/>
-    </row>
-    <row r="495">
-      <c r="A495" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B495" s="8" t="inlineStr">
-        <is>
-          <t>T-6141</t>
-        </is>
-      </c>
-      <c r="C495" s="8" t="inlineStr">
-        <is>
-          <t>HU-202</t>
-        </is>
-      </c>
-      <c r="D495" s="8" t="inlineStr">
-        <is>
-          <t>Importar el plan anual desde una planilla</t>
-        </is>
-      </c>
-      <c r="E495" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F495" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G495" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H495" s="9" t="inlineStr">
-        <is>
-          <t>Reglas de negocio de la historia en el SP, no en la pantalla: la API y la web tienen que obtener el mismo resultado.</t>
-        </is>
-      </c>
-      <c r="I495" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J495" s="8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K495" s="8" t="inlineStr">
-        <is>
-          <t>Emilio Fuentes</t>
-        </is>
-      </c>
-      <c r="L495" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M495" s="8" t="inlineStr"/>
-      <c r="N495" s="8" t="inlineStr"/>
-      <c r="O495" s="8" t="inlineStr"/>
-    </row>
-    <row r="496">
-      <c r="A496" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B496" s="8" t="inlineStr">
-        <is>
-          <t>T-6142</t>
-        </is>
-      </c>
-      <c r="C496" s="8" t="inlineStr">
-        <is>
-          <t>HU-202</t>
-        </is>
-      </c>
-      <c r="D496" s="8" t="inlineStr">
-        <is>
-          <t>Importar el plan anual desde una planilla</t>
-        </is>
-      </c>
-      <c r="E496" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F496" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G496" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H496" s="9" t="inlineStr">
-        <is>
-          <t>SP SEL_IMPORTACION_PLAN: consultar el resultado del proceso.</t>
-        </is>
-      </c>
-      <c r="I496" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J496" s="8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K496" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L496" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M496" s="8" t="inlineStr"/>
-      <c r="N496" s="8" t="inlineStr"/>
-      <c r="O496" s="8" t="inlineStr"/>
-    </row>
-    <row r="497">
-      <c r="A497" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B497" s="8" t="inlineStr">
-        <is>
-          <t>T-6143</t>
-        </is>
-      </c>
-      <c r="C497" s="8" t="inlineStr">
-        <is>
-          <t>HU-202</t>
-        </is>
-      </c>
-      <c r="D497" s="8" t="inlineStr">
-        <is>
-          <t>Importar el plan anual desde una planilla</t>
-        </is>
-      </c>
-      <c r="E497" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F497" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G497" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H497" s="9" t="inlineStr">
-        <is>
-          <t>Datos de prueba en Importacion_Carga para poder ejercitar los criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="I497" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J497" s="8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K497" s="8" t="inlineStr">
-        <is>
-          <t>Bryan Chávez</t>
-        </is>
-      </c>
-      <c r="L497" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M497" s="8" t="inlineStr"/>
-      <c r="N497" s="8" t="inlineStr"/>
-      <c r="O497" s="8" t="inlineStr"/>
-    </row>
-    <row r="498">
-      <c r="A498" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B498" s="8" t="inlineStr">
-        <is>
-          <t>T-6146</t>
-        </is>
-      </c>
-      <c r="C498" s="8" t="inlineStr">
-        <is>
-          <t>HU-202</t>
-        </is>
-      </c>
-      <c r="D498" s="8" t="inlineStr">
-        <is>
-          <t>Importar el plan anual desde una planilla</t>
-        </is>
-      </c>
-      <c r="E498" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F498" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G498" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H498" s="9" t="inlineStr">
-        <is>
-          <t>Pantalla ImportacionPlan.aspx: disparar el proceso, mostrar el resultado y dejar constancia de quién lo ejecutó.</t>
-        </is>
-      </c>
-      <c r="I498" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="J498" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K498" s="8" t="inlineStr">
-        <is>
-          <t>Emilio Fuentes</t>
-        </is>
-      </c>
-      <c r="L498" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M498" s="8" t="inlineStr"/>
-      <c r="N498" s="8" t="inlineStr"/>
-      <c r="O498" s="8" t="inlineStr"/>
-    </row>
-    <row r="499">
-      <c r="A499" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B499" s="8" t="inlineStr">
-        <is>
-          <t>T-6147</t>
-        </is>
-      </c>
-      <c r="C499" s="8" t="inlineStr">
-        <is>
-          <t>HU-202</t>
-        </is>
-      </c>
-      <c r="D499" s="8" t="inlineStr">
-        <is>
-          <t>Importar el plan anual desde una planilla</t>
-        </is>
-      </c>
-      <c r="E499" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F499" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G499" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H499" s="9" t="inlineStr">
-        <is>
-          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
-        </is>
-      </c>
-      <c r="I499" s="8" t="inlineStr">
-        <is>
-          <t>Seguridad</t>
-        </is>
-      </c>
-      <c r="J499" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K499" s="8" t="inlineStr">
-        <is>
-          <t>Bryan Chávez</t>
-        </is>
-      </c>
-      <c r="L499" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M499" s="8" t="inlineStr"/>
-      <c r="N499" s="8" t="inlineStr"/>
-      <c r="O499" s="8" t="inlineStr"/>
-    </row>
-    <row r="500">
-      <c r="A500" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B500" s="8" t="inlineStr">
-        <is>
-          <t>T-6148</t>
-        </is>
-      </c>
-      <c r="C500" s="8" t="inlineStr">
-        <is>
-          <t>HU-202</t>
-        </is>
-      </c>
-      <c r="D500" s="8" t="inlineStr">
-        <is>
-          <t>Importar el plan anual desde una planilla</t>
-        </is>
-      </c>
-      <c r="E500" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F500" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G500" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H500" s="9" t="inlineStr">
-        <is>
-          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="I500" s="8" t="inlineStr">
-        <is>
-          <t>Pruebas</t>
-        </is>
-      </c>
-      <c r="J500" s="8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="K500" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L500" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M500" s="8" t="inlineStr"/>
-      <c r="N500" s="8" t="inlineStr"/>
-      <c r="O500" s="8" t="inlineStr"/>
-    </row>
-    <row r="501">
-      <c r="A501" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B501" s="8" t="inlineStr">
-        <is>
-          <t>T-6149</t>
-        </is>
-      </c>
-      <c r="C501" s="8" t="inlineStr">
-        <is>
-          <t>HU-202</t>
-        </is>
-      </c>
-      <c r="D501" s="8" t="inlineStr">
-        <is>
-          <t>Importar el plan anual desde una planilla</t>
-        </is>
-      </c>
-      <c r="E501" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F501" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G501" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H501" s="9" t="inlineStr">
-        <is>
-          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
-        </is>
-      </c>
-      <c r="I501" s="8" t="inlineStr">
-        <is>
-          <t>Documentación</t>
-        </is>
-      </c>
-      <c r="J501" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K501" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L501" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M501" s="8" t="inlineStr"/>
-      <c r="N501" s="8" t="inlineStr"/>
-      <c r="O501" s="8" t="inlineStr"/>
-    </row>
-    <row r="502">
-      <c r="A502" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B502" s="8" t="inlineStr">
-        <is>
-          <t>T-6150</t>
-        </is>
-      </c>
-      <c r="C502" s="8" t="inlineStr">
-        <is>
-          <t>HU-202</t>
-        </is>
-      </c>
-      <c r="D502" s="8" t="inlineStr">
-        <is>
-          <t>Importar el plan anual desde una planilla</t>
-        </is>
-      </c>
-      <c r="E502" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F502" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G502" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H502" s="9" t="inlineStr">
-        <is>
-          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
-        </is>
-      </c>
-      <c r="I502" s="8" t="inlineStr">
-        <is>
-          <t>Validación</t>
-        </is>
-      </c>
-      <c r="J502" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K502" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L502" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M502" s="8" t="inlineStr"/>
-      <c r="N502" s="8" t="inlineStr"/>
-      <c r="O502" s="8" t="inlineStr"/>
-    </row>
-    <row r="503">
-      <c r="A503" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B503" s="8" t="inlineStr">
-        <is>
-          <t>T-6225</t>
-        </is>
-      </c>
-      <c r="C503" s="8" t="inlineStr">
-        <is>
-          <t>HU-203</t>
-        </is>
-      </c>
-      <c r="D503" s="8" t="inlineStr">
-        <is>
-          <t>Consultar el historial de importaciones</t>
-        </is>
-      </c>
-      <c r="E503" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F503" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G503" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H503" s="9" t="inlineStr">
-        <is>
-          <t>Modelo: revisar Importacion_Carga — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
-        </is>
-      </c>
-      <c r="I503" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J503" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K503" s="8" t="inlineStr">
-        <is>
-          <t>Bryan Chávez</t>
-        </is>
-      </c>
-      <c r="L503" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M503" s="8" t="inlineStr"/>
-      <c r="N503" s="8" t="inlineStr"/>
-      <c r="O503" s="8" t="inlineStr"/>
-    </row>
-    <row r="504">
-      <c r="A504" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B504" s="8" t="inlineStr">
-        <is>
-          <t>T-6226</t>
-        </is>
-      </c>
-      <c r="C504" s="8" t="inlineStr">
-        <is>
-          <t>HU-203</t>
-        </is>
-      </c>
-      <c r="D504" s="8" t="inlineStr">
-        <is>
-          <t>Consultar el historial de importaciones</t>
-        </is>
-      </c>
-      <c r="E504" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F504" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G504" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H504" s="9" t="inlineStr">
-        <is>
-          <t>SP SEL_IMPORTACION_HISTORIAL: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
-        </is>
-      </c>
-      <c r="I504" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J504" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K504" s="8" t="inlineStr">
-        <is>
-          <t>Emilio Fuentes</t>
-        </is>
-      </c>
-      <c r="L504" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M504" s="8" t="inlineStr"/>
-      <c r="N504" s="8" t="inlineStr"/>
-      <c r="O504" s="8" t="inlineStr"/>
-    </row>
-    <row r="505">
-      <c r="A505" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B505" s="8" t="inlineStr">
-        <is>
-          <t>T-6227</t>
-        </is>
-      </c>
-      <c r="C505" s="8" t="inlineStr">
-        <is>
-          <t>HU-203</t>
-        </is>
-      </c>
-      <c r="D505" s="8" t="inlineStr">
-        <is>
-          <t>Consultar el historial de importaciones</t>
-        </is>
-      </c>
-      <c r="E505" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F505" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G505" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H505" s="9" t="inlineStr">
-        <is>
-          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Importacion_Carga crezca.</t>
-        </is>
-      </c>
-      <c r="I505" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J505" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K505" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L505" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M505" s="8" t="inlineStr"/>
-      <c r="N505" s="8" t="inlineStr"/>
-      <c r="O505" s="8" t="inlineStr"/>
-    </row>
-    <row r="506">
-      <c r="A506" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B506" s="8" t="inlineStr">
-        <is>
-          <t>T-6228</t>
-        </is>
-      </c>
-      <c r="C506" s="8" t="inlineStr">
-        <is>
-          <t>HU-203</t>
-        </is>
-      </c>
-      <c r="D506" s="8" t="inlineStr">
-        <is>
-          <t>Consultar el historial de importaciones</t>
-        </is>
-      </c>
-      <c r="E506" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F506" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G506" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H506" s="9" t="inlineStr">
-        <is>
-          <t>Datos de prueba en Importacion_Carga para poder ejercitar los criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="I506" s="8" t="inlineStr">
-        <is>
-          <t>Base de datos</t>
-        </is>
-      </c>
-      <c r="J506" s="8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K506" s="8" t="inlineStr">
-        <is>
-          <t>Bryan Chávez</t>
-        </is>
-      </c>
-      <c r="L506" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M506" s="8" t="inlineStr"/>
-      <c r="N506" s="8" t="inlineStr"/>
-      <c r="O506" s="8" t="inlineStr"/>
-    </row>
-    <row r="507">
-      <c r="A507" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B507" s="8" t="inlineStr">
-        <is>
-          <t>T-6231</t>
-        </is>
-      </c>
-      <c r="C507" s="8" t="inlineStr">
-        <is>
-          <t>HU-203</t>
-        </is>
-      </c>
-      <c r="D507" s="8" t="inlineStr">
-        <is>
-          <t>Consultar el historial de importaciones</t>
-        </is>
-      </c>
-      <c r="E507" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F507" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G507" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H507" s="9" t="inlineStr">
-        <is>
-          <t>Pantalla ImportacionHistorial.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
-        </is>
-      </c>
-      <c r="I507" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="J507" s="8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K507" s="8" t="inlineStr">
-        <is>
-          <t>Bryan Chávez</t>
-        </is>
-      </c>
-      <c r="L507" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M507" s="8" t="inlineStr"/>
-      <c r="N507" s="8" t="inlineStr"/>
-      <c r="O507" s="8" t="inlineStr"/>
-    </row>
-    <row r="508">
-      <c r="A508" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B508" s="8" t="inlineStr">
-        <is>
-          <t>T-6232</t>
-        </is>
-      </c>
-      <c r="C508" s="8" t="inlineStr">
-        <is>
-          <t>HU-203</t>
-        </is>
-      </c>
-      <c r="D508" s="8" t="inlineStr">
-        <is>
-          <t>Consultar el historial de importaciones</t>
-        </is>
-      </c>
-      <c r="E508" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F508" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G508" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H508" s="9" t="inlineStr">
-        <is>
-          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
-        </is>
-      </c>
-      <c r="I508" s="8" t="inlineStr">
-        <is>
-          <t>Seguridad</t>
-        </is>
-      </c>
-      <c r="J508" s="8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K508" s="8" t="inlineStr">
-        <is>
-          <t>Emilio Fuentes</t>
-        </is>
-      </c>
-      <c r="L508" s="8" t="inlineStr">
-        <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="M508" s="8" t="inlineStr"/>
-      <c r="N508" s="8" t="inlineStr"/>
-      <c r="O508" s="8" t="inlineStr"/>
-    </row>
-    <row r="509">
-      <c r="A509" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B509" s="8" t="inlineStr">
-        <is>
-          <t>T-6233</t>
-        </is>
-      </c>
-      <c r="C509" s="8" t="inlineStr">
-        <is>
-          <t>HU-203</t>
-        </is>
-      </c>
-      <c r="D509" s="8" t="inlineStr">
-        <is>
-          <t>Consultar el historial de importaciones</t>
-        </is>
-      </c>
-      <c r="E509" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F509" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G509" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H509" s="9" t="inlineStr">
-        <is>
-          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
-        </is>
-      </c>
-      <c r="I509" s="8" t="inlineStr">
-        <is>
-          <t>Pruebas</t>
-        </is>
-      </c>
-      <c r="J509" s="8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K509" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L509" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M509" s="8" t="inlineStr"/>
-      <c r="N509" s="8" t="inlineStr"/>
-      <c r="O509" s="8" t="inlineStr"/>
-    </row>
-    <row r="510">
-      <c r="A510" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B510" s="8" t="inlineStr">
-        <is>
-          <t>T-6234</t>
-        </is>
-      </c>
-      <c r="C510" s="8" t="inlineStr">
-        <is>
-          <t>HU-203</t>
-        </is>
-      </c>
-      <c r="D510" s="8" t="inlineStr">
-        <is>
-          <t>Consultar el historial de importaciones</t>
-        </is>
-      </c>
-      <c r="E510" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F510" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G510" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="H510" s="9" t="inlineStr">
-        <is>
-          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
-        </is>
-      </c>
-      <c r="I510" s="8" t="inlineStr">
-        <is>
-          <t>Documentación</t>
-        </is>
-      </c>
-      <c r="J510" s="8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K510" s="8" t="inlineStr">
-        <is>
-          <t>Catalina Pescio</t>
-        </is>
-      </c>
-      <c r="L510" s="8" t="inlineStr">
-        <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="M510" s="8" t="inlineStr"/>
-      <c r="N510" s="8" t="inlineStr"/>
-      <c r="O510" s="8" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O510"/>
+  <autoFilter ref="A1:O455"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34247,7 +30782,7 @@
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="n">
-        <v>188.5</v>
+        <v>172.8</v>
       </c>
       <c r="I6" s="6">
         <f>SUM(C6:H6)</f>
@@ -34266,7 +30801,7 @@
       <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="n">
-        <v>100</v>
+        <v>82.2</v>
       </c>
       <c r="I7" s="6">
         <f>SUM(C7:H7)</f>
@@ -34285,7 +30820,7 @@
       <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="n">
-        <v>117</v>
+        <v>98.2</v>
       </c>
       <c r="I8" s="6">
         <f>SUM(C8:H8)</f>
@@ -34303,7 +30838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J75"/>
+  <dimension ref="B2:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="2" max="2"/>
@@ -36764,12 +33299,12 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>HU-177</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Registrar si la predicción se cumplió</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -36783,17 +33318,17 @@
         </is>
       </c>
       <c r="G64" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I64" s="8" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>Base de datos (5) · Web (2) · Seguridad (1) · Pruebas (1) · Documentación (1)</t>
+          <t>Base de datos (4) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1) · Validación (1)</t>
         </is>
       </c>
     </row>
@@ -36805,17 +33340,17 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-181</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Consultar el cumplimiento del plan de mantenimiento</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>EP-17</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
@@ -36824,17 +33359,17 @@
         </is>
       </c>
       <c r="G65" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H65" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="H65" s="8" t="n">
-        <v>9</v>
-      </c>
       <c r="I65" s="8" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="J65" s="9" t="inlineStr">
         <is>
-          <t>Base de datos (4) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1) · Validación (1)</t>
+          <t>Base de datos (4) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1)</t>
         </is>
       </c>
     </row>
@@ -36846,12 +33381,12 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>HU-180</t>
+          <t>HU-184</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Consultar el tablero de indicadores</t>
+          <t>Consultar la bandeja de alertas</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
@@ -36861,21 +33396,21 @@
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Web y App</t>
         </is>
       </c>
       <c r="G66" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I66" s="8" t="n">
-        <v>9.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>Base de datos (4) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1) · Validación (1)</t>
+          <t>Base de datos (4) · API (2) · Web (1) · Móvil (1) · Seguridad (1) · Pruebas (1) · Documentación (1)</t>
         </is>
       </c>
     </row>
@@ -36887,12 +33422,12 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>HU-181</t>
+          <t>HU-185</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Consultar el cumplimiento del plan de mantenimiento</t>
+          <t>Exportar e imprimir reportes</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -36909,14 +33444,14 @@
         <v>5</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I67" s="8" t="n">
         <v>5.8</v>
       </c>
       <c r="J67" s="9" t="inlineStr">
         <is>
-          <t>Base de datos (4) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1)</t>
+          <t>Base de datos (5) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1)</t>
         </is>
       </c>
     </row>
@@ -36928,17 +33463,17 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>HU-182</t>
+          <t>HU-201</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
+          <t>Resolver las celdas ambiguas de una importación</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
@@ -36950,14 +33485,14 @@
         <v>8</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I68" s="8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>Base de datos (4) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1) · Validación (1)</t>
+          <t>Base de datos (5) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1) · Validación (1)</t>
         </is>
       </c>
     </row>
@@ -36969,17 +33504,17 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>HU-183</t>
+          <t>HU-202</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Consultar los costos de mantenimiento</t>
+          <t>Importar el plan anual desde una planilla</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-20</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -36988,268 +33523,22 @@
         </is>
       </c>
       <c r="G69" s="8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I69" s="8" t="n">
-        <v>9.199999999999999</v>
+        <v>15.2</v>
       </c>
       <c r="J69" s="9" t="inlineStr">
         <is>
-          <t>Base de datos (4) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1) · Validación (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr">
-        <is>
-          <t>HU-184</t>
-        </is>
-      </c>
-      <c r="D70" s="9" t="inlineStr">
-        <is>
-          <t>Consultar la bandeja de alertas</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>EP-18</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>Web y App</t>
-        </is>
-      </c>
-      <c r="G70" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H70" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="I70" s="8" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J70" s="9" t="inlineStr">
-        <is>
-          <t>Base de datos (4) · API (2) · Web (1) · Móvil (1) · Seguridad (1) · Pruebas (1) · Documentación (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="C71" s="8" t="inlineStr">
-        <is>
-          <t>HU-185</t>
-        </is>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>Exportar e imprimir reportes</t>
-        </is>
-      </c>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>EP-18</t>
-        </is>
-      </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="H71" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="I71" s="8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J71" s="9" t="inlineStr">
-        <is>
-          <t>Base de datos (5) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>HU-200</t>
-        </is>
-      </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>Importar activos desde una planilla</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="G72" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="H72" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="I72" s="8" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="J72" s="9" t="inlineStr">
-        <is>
           <t>Base de datos (5) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1) · Validación (1)</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>HU-201</t>
-        </is>
-      </c>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="H73" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="I73" s="8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J73" s="9" t="inlineStr">
-        <is>
-          <t>Base de datos (5) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1) · Validación (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="inlineStr">
-        <is>
-          <t>HU-202</t>
-        </is>
-      </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>Importar el plan anual desde una planilla</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="G74" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="H74" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="I74" s="8" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="J74" s="9" t="inlineStr">
-        <is>
-          <t>Base de datos (5) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1) · Validación (1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>HU-203</t>
-        </is>
-      </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>Consultar el historial de importaciones</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>EP-20</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="G75" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H75" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="I75" s="8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J75" s="9" t="inlineStr">
-        <is>
-          <t>Base de datos (4) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="B5:J75"/>
+  <autoFilter ref="B5:J69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Fase 2/Evidencias Proyecto/SIGMA_Pendientes_por_Sprint.xlsx
+++ b/Fase 2/Evidencias Proyecto/SIGMA_Pendientes_por_Sprint.xlsx
@@ -1119,7 +1119,7 @@
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L9" s="8" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L17" s="8" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L21" s="8" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L25" s="8" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L29" s="8" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L31" s="8" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L33" s="8" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L36" s="8" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L37" s="8" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L40" s="8" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L42" s="8" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L43" s="8" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L44" s="8" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L47" s="8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L48" s="8" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="K50" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L50" s="8" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L52" s="8" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L53" s="8" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="K54" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L54" s="8" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="K55" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L55" s="8" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L56" s="8" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="K57" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L57" s="8" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="K58" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L58" s="8" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="K59" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L59" s="8" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="K60" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L60" s="8" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="K61" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L61" s="8" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="K62" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L62" s="8" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="K63" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L63" s="8" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="K64" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L64" s="8" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="K65" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L65" s="8" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="K66" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L66" s="8" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="K67" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L67" s="8" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="K68" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L68" s="8" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="K69" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L69" s="8" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="K70" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L70" s="8" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="K71" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L71" s="8" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="K72" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L72" s="8" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="K73" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L73" s="8" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="K74" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L74" s="8" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="K150" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L150" s="8" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="K152" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L152" s="8" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="K153" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L153" s="8" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="K156" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L156" s="8" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="K159" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L159" s="8" t="inlineStr">
@@ -11504,7 +11504,7 @@
       </c>
       <c r="K160" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L160" s="8" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="K161" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L161" s="8" t="inlineStr">
@@ -12442,7 +12442,7 @@
       </c>
       <c r="K174" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L174" s="8" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="K175" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L175" s="8" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="K176" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L176" s="8" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="K188" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L188" s="8" t="inlineStr">
@@ -13447,7 +13447,7 @@
       </c>
       <c r="K189" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L189" s="8" t="inlineStr">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="K190" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L190" s="8" t="inlineStr">
@@ -13581,7 +13581,7 @@
       </c>
       <c r="K191" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L191" s="8" t="inlineStr">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="K192" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L192" s="8" t="inlineStr">
@@ -13774,7 +13774,7 @@
       </c>
       <c r="K194" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L194" s="8" t="inlineStr">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="K195" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L195" s="8" t="inlineStr">
@@ -13900,7 +13900,7 @@
       </c>
       <c r="K196" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L196" s="8" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="K197" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L197" s="8" t="inlineStr">
@@ -14215,7 +14215,7 @@
       </c>
       <c r="K201" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L201" s="8" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="K206" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L206" s="8" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="K209" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L209" s="8" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="K210" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L210" s="8" t="inlineStr">
@@ -14885,7 +14885,7 @@
       </c>
       <c r="K211" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L211" s="8" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="K212" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L212" s="8" t="inlineStr">
@@ -15019,7 +15019,7 @@
       </c>
       <c r="K213" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L213" s="8" t="inlineStr">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="K215" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L215" s="8" t="inlineStr">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="K218" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L218" s="8" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="K221" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L221" s="8" t="inlineStr">
@@ -15622,7 +15622,7 @@
       </c>
       <c r="K222" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L222" s="8" t="inlineStr">
@@ -15689,7 +15689,7 @@
       </c>
       <c r="K223" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L223" s="8" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="K225" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L225" s="8" t="inlineStr">
@@ -15890,7 +15890,7 @@
       </c>
       <c r="K226" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L226" s="8" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="K229" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L229" s="8" t="inlineStr">
@@ -16292,7 +16292,7 @@
       </c>
       <c r="K232" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L232" s="8" t="inlineStr">
@@ -16493,7 +16493,7 @@
       </c>
       <c r="K235" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L235" s="8" t="inlineStr">
@@ -16560,7 +16560,7 @@
       </c>
       <c r="K236" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L236" s="8" t="inlineStr">
@@ -16627,7 +16627,7 @@
       </c>
       <c r="K237" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L237" s="8" t="inlineStr">
@@ -16694,7 +16694,7 @@
       </c>
       <c r="K238" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L238" s="8" t="inlineStr">
@@ -16828,7 +16828,7 @@
       </c>
       <c r="K240" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L240" s="8" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="K241" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L241" s="8" t="inlineStr">
@@ -17029,7 +17029,7 @@
       </c>
       <c r="K243" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L243" s="8" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="K244" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L244" s="8" t="inlineStr">
@@ -17163,7 +17163,7 @@
       </c>
       <c r="K245" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L245" s="8" t="inlineStr">
@@ -17230,7 +17230,7 @@
       </c>
       <c r="K246" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L246" s="8" t="inlineStr">
@@ -17565,7 +17565,7 @@
       </c>
       <c r="K251" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L251" s="8" t="inlineStr">
@@ -17632,7 +17632,7 @@
       </c>
       <c r="K252" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L252" s="8" t="inlineStr">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="K254" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L254" s="8" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="K256" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L256" s="8" t="inlineStr">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="K258" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L258" s="8" t="inlineStr">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="K261" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L261" s="8" t="inlineStr">
@@ -18302,7 +18302,7 @@
       </c>
       <c r="K262" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L262" s="8" t="inlineStr">
@@ -18369,7 +18369,7 @@
       </c>
       <c r="K263" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L263" s="8" t="inlineStr">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="K264" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L264" s="8" t="inlineStr">
@@ -18570,7 +18570,7 @@
       </c>
       <c r="K266" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L266" s="8" t="inlineStr">
@@ -18637,7 +18637,7 @@
       </c>
       <c r="K267" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L267" s="8" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="K268" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L268" s="8" t="inlineStr">
@@ -18771,7 +18771,7 @@
       </c>
       <c r="K269" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L269" s="8" t="inlineStr">
@@ -18838,7 +18838,7 @@
       </c>
       <c r="K270" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L270" s="8" t="inlineStr">
@@ -18905,7 +18905,7 @@
       </c>
       <c r="K271" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L271" s="8" t="inlineStr">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="K272" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L272" s="8" t="inlineStr">
@@ -19039,7 +19039,7 @@
       </c>
       <c r="K273" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L273" s="8" t="inlineStr">
@@ -19307,7 +19307,7 @@
       </c>
       <c r="K277" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L277" s="8" t="inlineStr">
@@ -19374,7 +19374,7 @@
       </c>
       <c r="K278" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L278" s="8" t="inlineStr">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="K280" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L280" s="8" t="inlineStr">
@@ -19575,7 +19575,7 @@
       </c>
       <c r="K281" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L281" s="8" t="inlineStr">
@@ -19709,7 +19709,7 @@
       </c>
       <c r="K283" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L283" s="8" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="K284" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L284" s="8" t="inlineStr">
@@ -19843,7 +19843,7 @@
       </c>
       <c r="K285" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L285" s="8" t="inlineStr">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="K286" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L286" s="8" t="inlineStr">
@@ -20714,7 +20714,7 @@
       </c>
       <c r="K298" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L298" s="8" t="inlineStr">
@@ -20781,7 +20781,7 @@
       </c>
       <c r="K299" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L299" s="8" t="inlineStr">
@@ -20848,7 +20848,7 @@
       </c>
       <c r="K300" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L300" s="8" t="inlineStr">
@@ -20915,7 +20915,7 @@
       </c>
       <c r="K301" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L301" s="8" t="inlineStr">
@@ -20982,7 +20982,7 @@
       </c>
       <c r="K302" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L302" s="8" t="inlineStr">
@@ -21116,7 +21116,7 @@
       </c>
       <c r="K304" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L304" s="8" t="inlineStr">
@@ -21250,7 +21250,7 @@
       </c>
       <c r="K306" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L306" s="8" t="inlineStr">
@@ -21384,7 +21384,7 @@
       </c>
       <c r="K308" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L308" s="8" t="inlineStr">
@@ -21518,7 +21518,7 @@
       </c>
       <c r="K310" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L310" s="8" t="inlineStr">
@@ -21585,7 +21585,7 @@
       </c>
       <c r="K311" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L311" s="8" t="inlineStr">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="K312" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L312" s="8" t="inlineStr">
@@ -21719,7 +21719,7 @@
       </c>
       <c r="K313" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L313" s="8" t="inlineStr">
@@ -21916,7 +21916,7 @@
       </c>
       <c r="K316" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L316" s="8" t="inlineStr">
@@ -21979,7 +21979,7 @@
       </c>
       <c r="K317" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L317" s="8" t="inlineStr">
@@ -22105,7 +22105,7 @@
       </c>
       <c r="K319" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L319" s="8" t="inlineStr">
@@ -22168,7 +22168,7 @@
       </c>
       <c r="K320" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L320" s="8" t="inlineStr">
@@ -22231,7 +22231,7 @@
       </c>
       <c r="K321" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L321" s="8" t="inlineStr">
@@ -22357,7 +22357,7 @@
       </c>
       <c r="K323" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L323" s="8" t="inlineStr">
@@ -22483,7 +22483,7 @@
       </c>
       <c r="K325" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L325" s="8" t="inlineStr">
@@ -22546,7 +22546,7 @@
       </c>
       <c r="K326" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L326" s="8" t="inlineStr">
@@ -22609,7 +22609,7 @@
       </c>
       <c r="K327" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L327" s="8" t="inlineStr">
@@ -22672,7 +22672,7 @@
       </c>
       <c r="K328" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L328" s="8" t="inlineStr">
@@ -22798,7 +22798,7 @@
       </c>
       <c r="K330" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L330" s="8" t="inlineStr">
@@ -22861,7 +22861,7 @@
       </c>
       <c r="K331" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L331" s="8" t="inlineStr">
@@ -22987,7 +22987,7 @@
       </c>
       <c r="K333" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L333" s="8" t="inlineStr">
@@ -23113,7 +23113,7 @@
       </c>
       <c r="K335" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L335" s="8" t="inlineStr">
@@ -23176,7 +23176,7 @@
       </c>
       <c r="K336" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L336" s="8" t="inlineStr">
@@ -23239,7 +23239,7 @@
       </c>
       <c r="K337" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L337" s="8" t="inlineStr">
@@ -23365,7 +23365,7 @@
       </c>
       <c r="K339" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L339" s="8" t="inlineStr">
@@ -23428,7 +23428,7 @@
       </c>
       <c r="K340" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L340" s="8" t="inlineStr">
@@ -23554,7 +23554,7 @@
       </c>
       <c r="K342" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L342" s="8" t="inlineStr">
@@ -23680,7 +23680,7 @@
       </c>
       <c r="K344" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L344" s="8" t="inlineStr">
@@ -23743,7 +23743,7 @@
       </c>
       <c r="K345" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L345" s="8" t="inlineStr">
@@ -23806,7 +23806,7 @@
       </c>
       <c r="K346" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L346" s="8" t="inlineStr">
@@ -23869,7 +23869,7 @@
       </c>
       <c r="K347" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L347" s="8" t="inlineStr">
@@ -23932,7 +23932,7 @@
       </c>
       <c r="K348" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L348" s="8" t="inlineStr">
@@ -23995,7 +23995,7 @@
       </c>
       <c r="K349" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L349" s="8" t="inlineStr">
@@ -24058,7 +24058,7 @@
       </c>
       <c r="K350" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L350" s="8" t="inlineStr">
@@ -24121,7 +24121,7 @@
       </c>
       <c r="K351" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L351" s="8" t="inlineStr">
@@ -24184,7 +24184,7 @@
       </c>
       <c r="K352" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L352" s="8" t="inlineStr">
@@ -24247,7 +24247,7 @@
       </c>
       <c r="K353" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L353" s="8" t="inlineStr">
@@ -24373,7 +24373,7 @@
       </c>
       <c r="K355" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L355" s="8" t="inlineStr">
@@ -24436,7 +24436,7 @@
       </c>
       <c r="K356" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L356" s="8" t="inlineStr">
@@ -24499,7 +24499,7 @@
       </c>
       <c r="K357" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L357" s="8" t="inlineStr">
@@ -24625,7 +24625,7 @@
       </c>
       <c r="K359" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L359" s="8" t="inlineStr">
@@ -24688,7 +24688,7 @@
       </c>
       <c r="K360" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L360" s="8" t="inlineStr">
@@ -24751,7 +24751,7 @@
       </c>
       <c r="K361" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L361" s="8" t="inlineStr">
@@ -24814,7 +24814,7 @@
       </c>
       <c r="K362" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L362" s="8" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="K363" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L363" s="8" t="inlineStr">
@@ -24940,7 +24940,7 @@
       </c>
       <c r="K364" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L364" s="8" t="inlineStr">
@@ -25003,7 +25003,7 @@
       </c>
       <c r="K365" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L365" s="8" t="inlineStr">
@@ -25066,7 +25066,7 @@
       </c>
       <c r="K366" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L366" s="8" t="inlineStr">
@@ -25192,7 +25192,7 @@
       </c>
       <c r="K368" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L368" s="8" t="inlineStr">
@@ -25255,7 +25255,7 @@
       </c>
       <c r="K369" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L369" s="8" t="inlineStr">
@@ -25318,7 +25318,7 @@
       </c>
       <c r="K370" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L370" s="8" t="inlineStr">
@@ -25444,7 +25444,7 @@
       </c>
       <c r="K372" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L372" s="8" t="inlineStr">
@@ -25507,7 +25507,7 @@
       </c>
       <c r="K373" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L373" s="8" t="inlineStr">
@@ -25570,7 +25570,7 @@
       </c>
       <c r="K374" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L374" s="8" t="inlineStr">
@@ -25633,7 +25633,7 @@
       </c>
       <c r="K375" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L375" s="8" t="inlineStr">
@@ -25696,7 +25696,7 @@
       </c>
       <c r="K376" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L376" s="8" t="inlineStr">
@@ -25759,7 +25759,7 @@
       </c>
       <c r="K377" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L377" s="8" t="inlineStr">
@@ -25822,7 +25822,7 @@
       </c>
       <c r="K378" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L378" s="8" t="inlineStr">
@@ -25948,7 +25948,7 @@
       </c>
       <c r="K380" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L380" s="8" t="inlineStr">
@@ -26011,7 +26011,7 @@
       </c>
       <c r="K381" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L381" s="8" t="inlineStr">
@@ -26074,7 +26074,7 @@
       </c>
       <c r="K382" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L382" s="8" t="inlineStr">
@@ -26200,7 +26200,7 @@
       </c>
       <c r="K384" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L384" s="8" t="inlineStr">
@@ -26326,7 +26326,7 @@
       </c>
       <c r="K386" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L386" s="8" t="inlineStr">
@@ -26389,7 +26389,7 @@
       </c>
       <c r="K387" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L387" s="8" t="inlineStr">
@@ -26452,7 +26452,7 @@
       </c>
       <c r="K388" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L388" s="8" t="inlineStr">
@@ -26578,7 +26578,7 @@
       </c>
       <c r="K390" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L390" s="8" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="K391" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L391" s="8" t="inlineStr">
@@ -26767,7 +26767,7 @@
       </c>
       <c r="K393" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L393" s="8" t="inlineStr">
@@ -26956,7 +26956,7 @@
       </c>
       <c r="K396" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L396" s="8" t="inlineStr">
@@ -27019,7 +27019,7 @@
       </c>
       <c r="K397" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L397" s="8" t="inlineStr">
@@ -27082,7 +27082,7 @@
       </c>
       <c r="K398" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L398" s="8" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="K399" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L399" s="8" t="inlineStr">
@@ -27271,7 +27271,7 @@
       </c>
       <c r="K401" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L401" s="8" t="inlineStr">
@@ -27397,7 +27397,7 @@
       </c>
       <c r="K403" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L403" s="8" t="inlineStr">
@@ -27460,7 +27460,7 @@
       </c>
       <c r="K404" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L404" s="8" t="inlineStr">
@@ -27523,7 +27523,7 @@
       </c>
       <c r="K405" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L405" s="8" t="inlineStr">
@@ -27586,7 +27586,7 @@
       </c>
       <c r="K406" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L406" s="8" t="inlineStr">
@@ -27649,7 +27649,7 @@
       </c>
       <c r="K407" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L407" s="8" t="inlineStr">
@@ -27712,7 +27712,7 @@
       </c>
       <c r="K408" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L408" s="8" t="inlineStr">
@@ -27838,7 +27838,7 @@
       </c>
       <c r="K410" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L410" s="8" t="inlineStr">
@@ -27901,7 +27901,7 @@
       </c>
       <c r="K411" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L411" s="8" t="inlineStr">
@@ -27964,7 +27964,7 @@
       </c>
       <c r="K412" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L412" s="8" t="inlineStr">
@@ -28216,7 +28216,7 @@
       </c>
       <c r="K416" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L416" s="8" t="inlineStr">
@@ -28279,7 +28279,7 @@
       </c>
       <c r="K417" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L417" s="8" t="inlineStr">
@@ -28405,7 +28405,7 @@
       </c>
       <c r="K419" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L419" s="8" t="inlineStr">
@@ -28468,7 +28468,7 @@
       </c>
       <c r="K420" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L420" s="8" t="inlineStr">
@@ -28531,7 +28531,7 @@
       </c>
       <c r="K421" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L421" s="8" t="inlineStr">
@@ -28594,7 +28594,7 @@
       </c>
       <c r="K422" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L422" s="8" t="inlineStr">
@@ -28657,7 +28657,7 @@
       </c>
       <c r="K423" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L423" s="8" t="inlineStr">
@@ -28909,7 +28909,7 @@
       </c>
       <c r="K427" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L427" s="8" t="inlineStr">
@@ -28972,7 +28972,7 @@
       </c>
       <c r="K428" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L428" s="8" t="inlineStr">
@@ -29098,7 +29098,7 @@
       </c>
       <c r="K430" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L430" s="8" t="inlineStr">
@@ -29161,7 +29161,7 @@
       </c>
       <c r="K431" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L431" s="8" t="inlineStr">
@@ -29224,7 +29224,7 @@
       </c>
       <c r="K432" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L432" s="8" t="inlineStr">
@@ -29413,7 +29413,7 @@
       </c>
       <c r="K435" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L435" s="8" t="inlineStr">
@@ -29480,7 +29480,7 @@
       </c>
       <c r="K436" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L436" s="8" t="inlineStr">
@@ -29543,7 +29543,7 @@
       </c>
       <c r="K437" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L437" s="8" t="inlineStr">
@@ -29669,7 +29669,7 @@
       </c>
       <c r="K439" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L439" s="8" t="inlineStr">
@@ -29732,7 +29732,7 @@
       </c>
       <c r="K440" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L440" s="8" t="inlineStr">
@@ -29795,7 +29795,7 @@
       </c>
       <c r="K441" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L441" s="8" t="inlineStr">
@@ -29858,7 +29858,7 @@
       </c>
       <c r="K442" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L442" s="8" t="inlineStr">
@@ -30173,7 +30173,7 @@
       </c>
       <c r="K447" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L447" s="8" t="inlineStr">
@@ -30236,7 +30236,7 @@
       </c>
       <c r="K448" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L448" s="8" t="inlineStr">
@@ -30362,7 +30362,7 @@
       </c>
       <c r="K450" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L450" s="8" t="inlineStr">
@@ -30425,7 +30425,7 @@
       </c>
       <c r="K451" s="8" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L451" s="8" t="inlineStr">
@@ -30488,7 +30488,7 @@
       </c>
       <c r="K452" s="8" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="L452" s="8" t="inlineStr">
@@ -30782,7 +30782,7 @@
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="n">
-        <v>172.8</v>
+        <v>117.8</v>
       </c>
       <c r="I6" s="6">
         <f>SUM(C6:H6)</f>
@@ -30801,7 +30801,7 @@
       <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="n">
-        <v>82.2</v>
+        <v>117</v>
       </c>
       <c r="I7" s="6">
         <f>SUM(C7:H7)</f>
@@ -30820,7 +30820,7 @@
       <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="n">
-        <v>98.2</v>
+        <v>118.5</v>
       </c>
       <c r="I8" s="6">
         <f>SUM(C8:H8)</f>

--- a/Fase 2/Evidencias Proyecto/SIGMA_Pendientes_por_Sprint.xlsx
+++ b/Fase 2/Evidencias Proyecto/SIGMA_Pendientes_por_Sprint.xlsx
@@ -13,8 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historias" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$1:$O$455</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Historias'!$B$5:$J$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$1:$O$510</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Historias'!$B$5:$J$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -679,16 +679,16 @@
         <v>514</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>454</v>
+        <v>509</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>353.2</v>
+        <v>405.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>310</v>
@@ -770,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O455"/>
+  <dimension ref="A1:O510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -13653,7 +13653,7 @@
       </c>
       <c r="L192" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M192" s="8" t="inlineStr"/>
@@ -13716,7 +13716,7 @@
       </c>
       <c r="L193" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M193" s="8" t="inlineStr"/>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="L194" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M194" s="8" t="inlineStr"/>
@@ -13842,7 +13842,7 @@
       </c>
       <c r="L195" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M195" s="8" t="inlineStr"/>
@@ -13905,7 +13905,7 @@
       </c>
       <c r="L196" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M196" s="8" t="inlineStr"/>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="L197" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M197" s="8" t="inlineStr"/>
@@ -21984,7 +21984,7 @@
       </c>
       <c r="L317" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M317" s="8" t="inlineStr"/>
@@ -22362,7 +22362,7 @@
       </c>
       <c r="L323" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M323" s="8" t="inlineStr"/>
@@ -22677,7 +22677,7 @@
       </c>
       <c r="L328" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M328" s="8" t="inlineStr"/>
@@ -22866,7 +22866,7 @@
       </c>
       <c r="L331" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M331" s="8" t="inlineStr"/>
@@ -22992,7 +22992,7 @@
       </c>
       <c r="L333" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M333" s="8" t="inlineStr"/>
@@ -23433,7 +23433,7 @@
       </c>
       <c r="L340" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M340" s="8" t="inlineStr"/>
@@ -23685,7 +23685,7 @@
       </c>
       <c r="L344" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M344" s="8" t="inlineStr"/>
@@ -24252,7 +24252,7 @@
       </c>
       <c r="L353" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M353" s="8" t="inlineStr"/>
@@ -24315,7 +24315,7 @@
       </c>
       <c r="L354" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M354" s="8" t="inlineStr"/>
@@ -24378,7 +24378,7 @@
       </c>
       <c r="L355" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M355" s="8" t="inlineStr"/>
@@ -24441,7 +24441,7 @@
       </c>
       <c r="L356" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M356" s="8" t="inlineStr"/>
@@ -24630,7 +24630,7 @@
       </c>
       <c r="L359" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M359" s="8" t="inlineStr"/>
@@ -24756,7 +24756,7 @@
       </c>
       <c r="L361" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M361" s="8" t="inlineStr"/>
@@ -25827,7 +25827,7 @@
       </c>
       <c r="L378" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M378" s="8" t="inlineStr"/>
@@ -25890,7 +25890,7 @@
       </c>
       <c r="L379" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M379" s="8" t="inlineStr"/>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="L380" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M380" s="8" t="inlineStr"/>
@@ -26016,7 +26016,7 @@
       </c>
       <c r="L381" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M381" s="8" t="inlineStr"/>
@@ -26205,7 +26205,7 @@
       </c>
       <c r="L384" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M384" s="8" t="inlineStr"/>
@@ -26331,7 +26331,7 @@
       </c>
       <c r="L386" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M386" s="8" t="inlineStr"/>
@@ -26520,7 +26520,7 @@
       </c>
       <c r="L389" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M389" s="8" t="inlineStr"/>
@@ -26583,7 +26583,7 @@
       </c>
       <c r="L390" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M390" s="8" t="inlineStr"/>
@@ -26646,7 +26646,7 @@
       </c>
       <c r="L391" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M391" s="8" t="inlineStr"/>
@@ -26709,7 +26709,7 @@
       </c>
       <c r="L392" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M392" s="8" t="inlineStr"/>
@@ -26772,7 +26772,7 @@
       </c>
       <c r="L393" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M393" s="8" t="inlineStr"/>
@@ -26835,7 +26835,7 @@
       </c>
       <c r="L394" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M394" s="8" t="inlineStr"/>
@@ -26898,7 +26898,7 @@
       </c>
       <c r="L395" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M395" s="8" t="inlineStr"/>
@@ -27039,17 +27039,17 @@
       </c>
       <c r="B398" s="8" t="inlineStr">
         <is>
-          <t>T-6214</t>
+          <t>T-6059</t>
         </is>
       </c>
       <c r="C398" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-177</t>
         </is>
       </c>
       <c r="D398" s="8" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Registrar si la predicción se cumplió</t>
         </is>
       </c>
       <c r="E398" s="8" t="inlineStr">
@@ -27069,7 +27069,7 @@
       </c>
       <c r="H398" s="9" t="inlineStr">
         <is>
-          <t>Modelo: revisar Modelo_Monitoreo — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
+          <t>Modelo: revisar Prediccion — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
         </is>
       </c>
       <c r="I398" s="8" t="inlineStr">
@@ -27078,7 +27078,7 @@
         </is>
       </c>
       <c r="J398" s="8" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K398" s="8" t="inlineStr">
         <is>
@@ -27087,7 +27087,7 @@
       </c>
       <c r="L398" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M398" s="8" t="inlineStr"/>
@@ -27102,17 +27102,17 @@
       </c>
       <c r="B399" s="8" t="inlineStr">
         <is>
-          <t>T-6215</t>
+          <t>T-6060</t>
         </is>
       </c>
       <c r="C399" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-177</t>
         </is>
       </c>
       <c r="D399" s="8" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Registrar si la predicción se cumplió</t>
         </is>
       </c>
       <c r="E399" s="8" t="inlineStr">
@@ -27132,7 +27132,7 @@
       </c>
       <c r="H399" s="9" t="inlineStr">
         <is>
-          <t>SP SEL_MODELO_MONITOREO: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
+          <t>SP INS_PREDICCION_RESULTADO: alta transaccional con las validaciones de negocio de la historia. Devuelve el id creado por OUTPUT.</t>
         </is>
       </c>
       <c r="I399" s="8" t="inlineStr">
@@ -27141,7 +27141,7 @@
         </is>
       </c>
       <c r="J399" s="8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K399" s="8" t="inlineStr">
         <is>
@@ -27150,7 +27150,7 @@
       </c>
       <c r="L399" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M399" s="8" t="inlineStr"/>
@@ -27165,17 +27165,17 @@
       </c>
       <c r="B400" s="8" t="inlineStr">
         <is>
-          <t>T-6216</t>
+          <t>T-6061</t>
         </is>
       </c>
       <c r="C400" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-177</t>
         </is>
       </c>
       <c r="D400" s="8" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Registrar si la predicción se cumplió</t>
         </is>
       </c>
       <c r="E400" s="8" t="inlineStr">
@@ -27195,7 +27195,7 @@
       </c>
       <c r="H400" s="9" t="inlineStr">
         <is>
-          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Modelo_Monitoreo crezca.</t>
+          <t>SP SEL_PREDICCION_RESULTADO: consulta por id y por filtros, para la ficha y el listado.</t>
         </is>
       </c>
       <c r="I400" s="8" t="inlineStr">
@@ -27204,7 +27204,7 @@
         </is>
       </c>
       <c r="J400" s="8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K400" s="8" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
       </c>
       <c r="L400" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M400" s="8" t="inlineStr"/>
@@ -27228,17 +27228,17 @@
       </c>
       <c r="B401" s="8" t="inlineStr">
         <is>
-          <t>T-6217</t>
+          <t>T-6062</t>
         </is>
       </c>
       <c r="C401" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-177</t>
         </is>
       </c>
       <c r="D401" s="8" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Registrar si la predicción se cumplió</t>
         </is>
       </c>
       <c r="E401" s="8" t="inlineStr">
@@ -27258,7 +27258,7 @@
       </c>
       <c r="H401" s="9" t="inlineStr">
         <is>
-          <t>Datos de prueba en Modelo_Monitoreo para poder ejercitar los criterios de aceptación.</t>
+          <t>SP UPD_PREDICCION_RESULTADO: corrección del registro mientras esté en un estado que lo permita.</t>
         </is>
       </c>
       <c r="I401" s="8" t="inlineStr">
@@ -27267,7 +27267,7 @@
         </is>
       </c>
       <c r="J401" s="8" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="K401" s="8" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
       </c>
       <c r="L401" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M401" s="8" t="inlineStr"/>
@@ -27291,17 +27291,17 @@
       </c>
       <c r="B402" s="8" t="inlineStr">
         <is>
-          <t>T-6220</t>
+          <t>T-6063</t>
         </is>
       </c>
       <c r="C402" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-177</t>
         </is>
       </c>
       <c r="D402" s="8" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Registrar si la predicción se cumplió</t>
         </is>
       </c>
       <c r="E402" s="8" t="inlineStr">
@@ -27321,16 +27321,16 @@
       </c>
       <c r="H402" s="9" t="inlineStr">
         <is>
-          <t>Pantalla ModeloMonitoreo.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
+          <t>Datos de prueba en Prediccion para poder ejercitar los criterios de aceptación.</t>
         </is>
       </c>
       <c r="I402" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J402" s="8" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="K402" s="8" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
       </c>
       <c r="L402" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M402" s="8" t="inlineStr"/>
@@ -27354,17 +27354,17 @@
       </c>
       <c r="B403" s="8" t="inlineStr">
         <is>
-          <t>T-6221</t>
+          <t>T-6067</t>
         </is>
       </c>
       <c r="C403" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-177</t>
         </is>
       </c>
       <c r="D403" s="8" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Registrar si la predicción se cumplió</t>
         </is>
       </c>
       <c r="E403" s="8" t="inlineStr">
@@ -27384,16 +27384,16 @@
       </c>
       <c r="H403" s="9" t="inlineStr">
         <is>
-          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
+          <t>Ficha PrediccionResultado.aspx: formulario de alta con sus validaciones.</t>
         </is>
       </c>
       <c r="I403" s="8" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="J403" s="8" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K403" s="8" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
       </c>
       <c r="L403" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M403" s="8" t="inlineStr"/>
@@ -27417,17 +27417,17 @@
       </c>
       <c r="B404" s="8" t="inlineStr">
         <is>
-          <t>T-6222</t>
+          <t>T-6068</t>
         </is>
       </c>
       <c r="C404" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-177</t>
         </is>
       </c>
       <c r="D404" s="8" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Registrar si la predicción se cumplió</t>
         </is>
       </c>
       <c r="E404" s="8" t="inlineStr">
@@ -27447,16 +27447,16 @@
       </c>
       <c r="H404" s="9" t="inlineStr">
         <is>
-          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
+          <t>Listado PrediccionResultados.aspx con el estado de cada registro.</t>
         </is>
       </c>
       <c r="I404" s="8" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="J404" s="8" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="K404" s="8" t="inlineStr">
         <is>
@@ -27480,17 +27480,17 @@
       </c>
       <c r="B405" s="8" t="inlineStr">
         <is>
-          <t>T-6223</t>
+          <t>T-6069</t>
         </is>
       </c>
       <c r="C405" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-177</t>
         </is>
       </c>
       <c r="D405" s="8" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Registrar si la predicción se cumplió</t>
         </is>
       </c>
       <c r="E405" s="8" t="inlineStr">
@@ -27510,12 +27510,12 @@
       </c>
       <c r="H405" s="9" t="inlineStr">
         <is>
-          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
+          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
         </is>
       </c>
       <c r="I405" s="8" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="J405" s="8" t="n">
@@ -27543,17 +27543,17 @@
       </c>
       <c r="B406" s="8" t="inlineStr">
         <is>
-          <t>T-6224</t>
+          <t>T-6070</t>
         </is>
       </c>
       <c r="C406" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-177</t>
         </is>
       </c>
       <c r="D406" s="8" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Registrar si la predicción se cumplió</t>
         </is>
       </c>
       <c r="E406" s="8" t="inlineStr">
@@ -27573,16 +27573,16 @@
       </c>
       <c r="H406" s="9" t="inlineStr">
         <is>
-          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
+          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
         </is>
       </c>
       <c r="I406" s="8" t="inlineStr">
         <is>
-          <t>Validación</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="J406" s="8" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="K406" s="8" t="inlineStr">
         <is>
@@ -27606,22 +27606,22 @@
       </c>
       <c r="B407" s="8" t="inlineStr">
         <is>
-          <t>T-6072</t>
+          <t>T-6071</t>
         </is>
       </c>
       <c r="C407" s="8" t="inlineStr">
         <is>
-          <t>HU-181</t>
+          <t>HU-177</t>
         </is>
       </c>
       <c r="D407" s="8" t="inlineStr">
         <is>
-          <t>Consultar el cumplimiento del plan de mantenimiento</t>
+          <t>Registrar si la predicción se cumplió</t>
         </is>
       </c>
       <c r="E407" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-17</t>
         </is>
       </c>
       <c r="F407" s="8" t="inlineStr">
@@ -27636,25 +27636,25 @@
       </c>
       <c r="H407" s="9" t="inlineStr">
         <is>
-          <t>Modelo: CREAR la tabla Indicador_Valor — todavía no existe. Columnas, PK, FK a sus padres y columna ind_uuid con índice UNIQUE para que la sincronización no duplique.</t>
+          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
         </is>
       </c>
       <c r="I407" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="J407" s="8" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="K407" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L407" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M407" s="8" t="inlineStr"/>
@@ -27669,22 +27669,22 @@
       </c>
       <c r="B408" s="8" t="inlineStr">
         <is>
-          <t>T-6073</t>
+          <t>T-6214</t>
         </is>
       </c>
       <c r="C408" s="8" t="inlineStr">
         <is>
-          <t>HU-181</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D408" s="8" t="inlineStr">
         <is>
-          <t>Consultar el cumplimiento del plan de mantenimiento</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E408" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-17</t>
         </is>
       </c>
       <c r="F408" s="8" t="inlineStr">
@@ -27699,7 +27699,7 @@
       </c>
       <c r="H408" s="9" t="inlineStr">
         <is>
-          <t>SP SEL_INDICADOR_CUMPLIMIENTO: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
+          <t>Modelo: revisar Modelo_Monitoreo — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
         </is>
       </c>
       <c r="I408" s="8" t="inlineStr">
@@ -27708,16 +27708,16 @@
         </is>
       </c>
       <c r="J408" s="8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K408" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L408" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M408" s="8" t="inlineStr"/>
@@ -27732,22 +27732,22 @@
       </c>
       <c r="B409" s="8" t="inlineStr">
         <is>
-          <t>T-6074</t>
+          <t>T-6215</t>
         </is>
       </c>
       <c r="C409" s="8" t="inlineStr">
         <is>
-          <t>HU-181</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D409" s="8" t="inlineStr">
         <is>
-          <t>Consultar el cumplimiento del plan de mantenimiento</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E409" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-17</t>
         </is>
       </c>
       <c r="F409" s="8" t="inlineStr">
@@ -27762,7 +27762,7 @@
       </c>
       <c r="H409" s="9" t="inlineStr">
         <is>
-          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Indicador_Valor crezca.</t>
+          <t>SP SEL_MODELO_MONITOREO: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
         </is>
       </c>
       <c r="I409" s="8" t="inlineStr">
@@ -27771,16 +27771,16 @@
         </is>
       </c>
       <c r="J409" s="8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K409" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L409" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M409" s="8" t="inlineStr"/>
@@ -27795,22 +27795,22 @@
       </c>
       <c r="B410" s="8" t="inlineStr">
         <is>
-          <t>T-6075</t>
+          <t>T-6216</t>
         </is>
       </c>
       <c r="C410" s="8" t="inlineStr">
         <is>
-          <t>HU-181</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D410" s="8" t="inlineStr">
         <is>
-          <t>Consultar el cumplimiento del plan de mantenimiento</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E410" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-17</t>
         </is>
       </c>
       <c r="F410" s="8" t="inlineStr">
@@ -27825,7 +27825,7 @@
       </c>
       <c r="H410" s="9" t="inlineStr">
         <is>
-          <t>Datos de prueba en Indicador_Valor para poder ejercitar los criterios de aceptación.</t>
+          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Modelo_Monitoreo crezca.</t>
         </is>
       </c>
       <c r="I410" s="8" t="inlineStr">
@@ -27834,16 +27834,16 @@
         </is>
       </c>
       <c r="J410" s="8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K410" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L410" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M410" s="8" t="inlineStr"/>
@@ -27858,22 +27858,22 @@
       </c>
       <c r="B411" s="8" t="inlineStr">
         <is>
-          <t>T-6078</t>
+          <t>T-6217</t>
         </is>
       </c>
       <c r="C411" s="8" t="inlineStr">
         <is>
-          <t>HU-181</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D411" s="8" t="inlineStr">
         <is>
-          <t>Consultar el cumplimiento del plan de mantenimiento</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E411" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-17</t>
         </is>
       </c>
       <c r="F411" s="8" t="inlineStr">
@@ -27888,25 +27888,25 @@
       </c>
       <c r="H411" s="9" t="inlineStr">
         <is>
-          <t>Pantalla IndicadorCumplimiento.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
+          <t>Datos de prueba en Modelo_Monitoreo para poder ejercitar los criterios de aceptación.</t>
         </is>
       </c>
       <c r="I411" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J411" s="8" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="K411" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L411" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M411" s="8" t="inlineStr"/>
@@ -27921,22 +27921,22 @@
       </c>
       <c r="B412" s="8" t="inlineStr">
         <is>
-          <t>T-6079</t>
+          <t>T-6220</t>
         </is>
       </c>
       <c r="C412" s="8" t="inlineStr">
         <is>
-          <t>HU-181</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D412" s="8" t="inlineStr">
         <is>
-          <t>Consultar el cumplimiento del plan de mantenimiento</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E412" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-17</t>
         </is>
       </c>
       <c r="F412" s="8" t="inlineStr">
@@ -27951,25 +27951,25 @@
       </c>
       <c r="H412" s="9" t="inlineStr">
         <is>
-          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
+          <t>Pantalla ModeloMonitoreo.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
         </is>
       </c>
       <c r="I412" s="8" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="J412" s="8" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="K412" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L412" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M412" s="8" t="inlineStr"/>
@@ -27984,22 +27984,22 @@
       </c>
       <c r="B413" s="8" t="inlineStr">
         <is>
-          <t>T-6080</t>
+          <t>T-6221</t>
         </is>
       </c>
       <c r="C413" s="8" t="inlineStr">
         <is>
-          <t>HU-181</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D413" s="8" t="inlineStr">
         <is>
-          <t>Consultar el cumplimiento del plan de mantenimiento</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E413" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-17</t>
         </is>
       </c>
       <c r="F413" s="8" t="inlineStr">
@@ -28014,12 +28014,12 @@
       </c>
       <c r="H413" s="9" t="inlineStr">
         <is>
-          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
+          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
         </is>
       </c>
       <c r="I413" s="8" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="J413" s="8" t="n">
@@ -28027,7 +28027,7 @@
       </c>
       <c r="K413" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L413" s="8" t="inlineStr">
@@ -28047,22 +28047,22 @@
       </c>
       <c r="B414" s="8" t="inlineStr">
         <is>
-          <t>T-6081</t>
+          <t>T-6222</t>
         </is>
       </c>
       <c r="C414" s="8" t="inlineStr">
         <is>
-          <t>HU-181</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D414" s="8" t="inlineStr">
         <is>
-          <t>Consultar el cumplimiento del plan de mantenimiento</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E414" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-17</t>
         </is>
       </c>
       <c r="F414" s="8" t="inlineStr">
@@ -28077,20 +28077,20 @@
       </c>
       <c r="H414" s="9" t="inlineStr">
         <is>
-          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
+          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
         </is>
       </c>
       <c r="I414" s="8" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="J414" s="8" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="K414" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L414" s="8" t="inlineStr">
@@ -28110,22 +28110,22 @@
       </c>
       <c r="B415" s="8" t="inlineStr">
         <is>
-          <t>T-6116</t>
+          <t>T-6223</t>
         </is>
       </c>
       <c r="C415" s="8" t="inlineStr">
         <is>
-          <t>HU-184</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D415" s="8" t="inlineStr">
         <is>
-          <t>Consultar la bandeja de alertas</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E415" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-17</t>
         </is>
       </c>
       <c r="F415" s="8" t="inlineStr">
@@ -28135,30 +28135,30 @@
       </c>
       <c r="G415" s="8" t="inlineStr">
         <is>
-          <t>Web y App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H415" s="9" t="inlineStr">
         <is>
-          <t>Modelo: revisar Alerta — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
+          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
         </is>
       </c>
       <c r="I415" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="J415" s="8" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="K415" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L415" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M415" s="8" t="inlineStr"/>
@@ -28173,22 +28173,22 @@
       </c>
       <c r="B416" s="8" t="inlineStr">
         <is>
-          <t>T-6117</t>
+          <t>T-6224</t>
         </is>
       </c>
       <c r="C416" s="8" t="inlineStr">
         <is>
-          <t>HU-184</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D416" s="8" t="inlineStr">
         <is>
-          <t>Consultar la bandeja de alertas</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E416" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-17</t>
         </is>
       </c>
       <c r="F416" s="8" t="inlineStr">
@@ -28198,30 +28198,30 @@
       </c>
       <c r="G416" s="8" t="inlineStr">
         <is>
-          <t>Web y App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H416" s="9" t="inlineStr">
         <is>
-          <t>SP SEL_ALERTA: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
+          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
         </is>
       </c>
       <c r="I416" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Validación</t>
         </is>
       </c>
       <c r="J416" s="8" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="K416" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="L416" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M416" s="8" t="inlineStr"/>
@@ -28236,17 +28236,17 @@
       </c>
       <c r="B417" s="8" t="inlineStr">
         <is>
-          <t>T-6118</t>
+          <t>T-6035</t>
         </is>
       </c>
       <c r="C417" s="8" t="inlineStr">
         <is>
-          <t>HU-184</t>
+          <t>HU-180</t>
         </is>
       </c>
       <c r="D417" s="8" t="inlineStr">
         <is>
-          <t>Consultar la bandeja de alertas</t>
+          <t>Consultar el tablero de indicadores</t>
         </is>
       </c>
       <c r="E417" s="8" t="inlineStr">
@@ -28261,12 +28261,12 @@
       </c>
       <c r="G417" s="8" t="inlineStr">
         <is>
-          <t>Web y App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H417" s="9" t="inlineStr">
         <is>
-          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Alerta crezca.</t>
+          <t>Modelo: CREAR la tabla Indicador_Valor — todavía no existe. Columnas, PK, FK a sus padres y columna ind_uuid con índice UNIQUE para que la sincronización no duplique.</t>
         </is>
       </c>
       <c r="I417" s="8" t="inlineStr">
@@ -28275,16 +28275,16 @@
         </is>
       </c>
       <c r="J417" s="8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K417" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L417" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M417" s="8" t="inlineStr"/>
@@ -28299,17 +28299,17 @@
       </c>
       <c r="B418" s="8" t="inlineStr">
         <is>
-          <t>T-6119</t>
+          <t>T-6036</t>
         </is>
       </c>
       <c r="C418" s="8" t="inlineStr">
         <is>
-          <t>HU-184</t>
+          <t>HU-180</t>
         </is>
       </c>
       <c r="D418" s="8" t="inlineStr">
         <is>
-          <t>Consultar la bandeja de alertas</t>
+          <t>Consultar el tablero de indicadores</t>
         </is>
       </c>
       <c r="E418" s="8" t="inlineStr">
@@ -28324,12 +28324,12 @@
       </c>
       <c r="G418" s="8" t="inlineStr">
         <is>
-          <t>Web y App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H418" s="9" t="inlineStr">
         <is>
-          <t>Datos de prueba en Alerta para poder ejercitar los criterios de aceptación.</t>
+          <t>SP SEL_INDICADOR_TABLERO: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
         </is>
       </c>
       <c r="I418" s="8" t="inlineStr">
@@ -28338,16 +28338,16 @@
         </is>
       </c>
       <c r="J418" s="8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K418" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L418" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M418" s="8" t="inlineStr"/>
@@ -28362,17 +28362,17 @@
       </c>
       <c r="B419" s="8" t="inlineStr">
         <is>
-          <t>T-6120</t>
+          <t>T-6037</t>
         </is>
       </c>
       <c r="C419" s="8" t="inlineStr">
         <is>
-          <t>HU-184</t>
+          <t>HU-180</t>
         </is>
       </c>
       <c r="D419" s="8" t="inlineStr">
         <is>
-          <t>Consultar la bandeja de alertas</t>
+          <t>Consultar el tablero de indicadores</t>
         </is>
       </c>
       <c r="E419" s="8" t="inlineStr">
@@ -28387,25 +28387,25 @@
       </c>
       <c r="G419" s="8" t="inlineStr">
         <is>
-          <t>Web y App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H419" s="9" t="inlineStr">
         <is>
-          <t>GET /api/alertas — consulta con filtros y paginación.</t>
+          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Indicador_Valor crezca.</t>
         </is>
       </c>
       <c r="I419" s="8" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J419" s="8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K419" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L419" s="8" t="inlineStr">
@@ -28425,17 +28425,17 @@
       </c>
       <c r="B420" s="8" t="inlineStr">
         <is>
-          <t>T-6121</t>
+          <t>T-6038</t>
         </is>
       </c>
       <c r="C420" s="8" t="inlineStr">
         <is>
-          <t>HU-184</t>
+          <t>HU-180</t>
         </is>
       </c>
       <c r="D420" s="8" t="inlineStr">
         <is>
-          <t>Consultar la bandeja de alertas</t>
+          <t>Consultar el tablero de indicadores</t>
         </is>
       </c>
       <c r="E420" s="8" t="inlineStr">
@@ -28450,17 +28450,17 @@
       </c>
       <c r="G420" s="8" t="inlineStr">
         <is>
-          <t>Web y App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H420" s="9" t="inlineStr">
         <is>
-          <t>Caché corta de la respuesta cuando el dato no cambia por petición.</t>
+          <t>Datos de prueba en Indicador_Valor para poder ejercitar los criterios de aceptación.</t>
         </is>
       </c>
       <c r="I420" s="8" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J420" s="8" t="n">
@@ -28468,7 +28468,7 @@
       </c>
       <c r="K420" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L420" s="8" t="inlineStr">
@@ -28488,17 +28488,17 @@
       </c>
       <c r="B421" s="8" t="inlineStr">
         <is>
-          <t>T-6122</t>
+          <t>T-6041</t>
         </is>
       </c>
       <c r="C421" s="8" t="inlineStr">
         <is>
-          <t>HU-184</t>
+          <t>HU-180</t>
         </is>
       </c>
       <c r="D421" s="8" t="inlineStr">
         <is>
-          <t>Consultar la bandeja de alertas</t>
+          <t>Consultar el tablero de indicadores</t>
         </is>
       </c>
       <c r="E421" s="8" t="inlineStr">
@@ -28513,12 +28513,12 @@
       </c>
       <c r="G421" s="8" t="inlineStr">
         <is>
-          <t>Web y App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H421" s="9" t="inlineStr">
         <is>
-          <t>Pantalla Alerta.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
+          <t>Pantalla IndicadorTablero.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
         </is>
       </c>
       <c r="I421" s="8" t="inlineStr">
@@ -28527,16 +28527,16 @@
         </is>
       </c>
       <c r="J421" s="8" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="K421" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L421" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M421" s="8" t="inlineStr"/>
@@ -28551,17 +28551,17 @@
       </c>
       <c r="B422" s="8" t="inlineStr">
         <is>
-          <t>T-6123</t>
+          <t>T-6042</t>
         </is>
       </c>
       <c r="C422" s="8" t="inlineStr">
         <is>
-          <t>HU-184</t>
+          <t>HU-180</t>
         </is>
       </c>
       <c r="D422" s="8" t="inlineStr">
         <is>
-          <t>Consultar la bandeja de alertas</t>
+          <t>Consultar el tablero de indicadores</t>
         </is>
       </c>
       <c r="E422" s="8" t="inlineStr">
@@ -28576,25 +28576,25 @@
       </c>
       <c r="G422" s="8" t="inlineStr">
         <is>
-          <t>Web y App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H422" s="9" t="inlineStr">
         <is>
-          <t>Consumo del endpoint desde la app cuando corresponda.</t>
+          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
         </is>
       </c>
       <c r="I422" s="8" t="inlineStr">
         <is>
-          <t>Móvil</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="J422" s="8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K422" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L422" s="8" t="inlineStr">
@@ -28614,17 +28614,17 @@
       </c>
       <c r="B423" s="8" t="inlineStr">
         <is>
-          <t>T-6124</t>
+          <t>T-6043</t>
         </is>
       </c>
       <c r="C423" s="8" t="inlineStr">
         <is>
-          <t>HU-184</t>
+          <t>HU-180</t>
         </is>
       </c>
       <c r="D423" s="8" t="inlineStr">
         <is>
-          <t>Consultar la bandeja de alertas</t>
+          <t>Consultar el tablero de indicadores</t>
         </is>
       </c>
       <c r="E423" s="8" t="inlineStr">
@@ -28639,30 +28639,30 @@
       </c>
       <c r="G423" s="8" t="inlineStr">
         <is>
-          <t>Web y App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H423" s="9" t="inlineStr">
         <is>
-          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
+          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
         </is>
       </c>
       <c r="I423" s="8" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="J423" s="8" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="K423" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L423" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M423" s="8" t="inlineStr"/>
@@ -28677,17 +28677,17 @@
       </c>
       <c r="B424" s="8" t="inlineStr">
         <is>
-          <t>T-6125</t>
+          <t>T-6044</t>
         </is>
       </c>
       <c r="C424" s="8" t="inlineStr">
         <is>
-          <t>HU-184</t>
+          <t>HU-180</t>
         </is>
       </c>
       <c r="D424" s="8" t="inlineStr">
         <is>
-          <t>Consultar la bandeja de alertas</t>
+          <t>Consultar el tablero de indicadores</t>
         </is>
       </c>
       <c r="E424" s="8" t="inlineStr">
@@ -28702,25 +28702,25 @@
       </c>
       <c r="G424" s="8" t="inlineStr">
         <is>
-          <t>Web y App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H424" s="9" t="inlineStr">
         <is>
-          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
+          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
         </is>
       </c>
       <c r="I424" s="8" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="J424" s="8" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="K424" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L424" s="8" t="inlineStr">
@@ -28740,17 +28740,17 @@
       </c>
       <c r="B425" s="8" t="inlineStr">
         <is>
-          <t>T-6126</t>
+          <t>T-6045</t>
         </is>
       </c>
       <c r="C425" s="8" t="inlineStr">
         <is>
-          <t>HU-184</t>
+          <t>HU-180</t>
         </is>
       </c>
       <c r="D425" s="8" t="inlineStr">
         <is>
-          <t>Consultar la bandeja de alertas</t>
+          <t>Consultar el tablero de indicadores</t>
         </is>
       </c>
       <c r="E425" s="8" t="inlineStr">
@@ -28765,17 +28765,17 @@
       </c>
       <c r="G425" s="8" t="inlineStr">
         <is>
-          <t>Web y App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H425" s="9" t="inlineStr">
         <is>
-          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
+          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
         </is>
       </c>
       <c r="I425" s="8" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>Validación</t>
         </is>
       </c>
       <c r="J425" s="8" t="n">
@@ -28783,7 +28783,7 @@
       </c>
       <c r="K425" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L425" s="8" t="inlineStr">
@@ -28803,17 +28803,17 @@
       </c>
       <c r="B426" s="8" t="inlineStr">
         <is>
-          <t>T-6192</t>
+          <t>T-6072</t>
         </is>
       </c>
       <c r="C426" s="8" t="inlineStr">
         <is>
-          <t>HU-185</t>
+          <t>HU-181</t>
         </is>
       </c>
       <c r="D426" s="8" t="inlineStr">
         <is>
-          <t>Exportar e imprimir reportes</t>
+          <t>Consultar el cumplimiento del plan de mantenimiento</t>
         </is>
       </c>
       <c r="E426" s="8" t="inlineStr">
@@ -28851,7 +28851,7 @@
       </c>
       <c r="L426" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M426" s="8" t="inlineStr"/>
@@ -28866,17 +28866,17 @@
       </c>
       <c r="B427" s="8" t="inlineStr">
         <is>
-          <t>T-6193</t>
+          <t>T-6073</t>
         </is>
       </c>
       <c r="C427" s="8" t="inlineStr">
         <is>
-          <t>HU-185</t>
+          <t>HU-181</t>
         </is>
       </c>
       <c r="D427" s="8" t="inlineStr">
         <is>
-          <t>Exportar e imprimir reportes</t>
+          <t>Consultar el cumplimiento del plan de mantenimiento</t>
         </is>
       </c>
       <c r="E427" s="8" t="inlineStr">
@@ -28896,7 +28896,7 @@
       </c>
       <c r="H427" s="9" t="inlineStr">
         <is>
-          <t>SP INDICADOR_EXPORTAR: el proceso completo dentro de una transacción, con SET XACT_ABORT ON para que un error no deje datos a medias.</t>
+          <t>SP SEL_INDICADOR_CUMPLIMIENTO: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
         </is>
       </c>
       <c r="I427" s="8" t="inlineStr">
@@ -28905,7 +28905,7 @@
         </is>
       </c>
       <c r="J427" s="8" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K427" s="8" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
       </c>
       <c r="L427" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M427" s="8" t="inlineStr"/>
@@ -28929,17 +28929,17 @@
       </c>
       <c r="B428" s="8" t="inlineStr">
         <is>
-          <t>T-6194</t>
+          <t>T-6074</t>
         </is>
       </c>
       <c r="C428" s="8" t="inlineStr">
         <is>
-          <t>HU-185</t>
+          <t>HU-181</t>
         </is>
       </c>
       <c r="D428" s="8" t="inlineStr">
         <is>
-          <t>Exportar e imprimir reportes</t>
+          <t>Consultar el cumplimiento del plan de mantenimiento</t>
         </is>
       </c>
       <c r="E428" s="8" t="inlineStr">
@@ -28959,7 +28959,7 @@
       </c>
       <c r="H428" s="9" t="inlineStr">
         <is>
-          <t>Reglas de negocio de la historia en el SP, no en la pantalla: la API y la web tienen que obtener el mismo resultado.</t>
+          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Indicador_Valor crezca.</t>
         </is>
       </c>
       <c r="I428" s="8" t="inlineStr">
@@ -28977,7 +28977,7 @@
       </c>
       <c r="L428" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M428" s="8" t="inlineStr"/>
@@ -28992,17 +28992,17 @@
       </c>
       <c r="B429" s="8" t="inlineStr">
         <is>
-          <t>T-6195</t>
+          <t>T-6075</t>
         </is>
       </c>
       <c r="C429" s="8" t="inlineStr">
         <is>
-          <t>HU-185</t>
+          <t>HU-181</t>
         </is>
       </c>
       <c r="D429" s="8" t="inlineStr">
         <is>
-          <t>Exportar e imprimir reportes</t>
+          <t>Consultar el cumplimiento del plan de mantenimiento</t>
         </is>
       </c>
       <c r="E429" s="8" t="inlineStr">
@@ -29022,7 +29022,7 @@
       </c>
       <c r="H429" s="9" t="inlineStr">
         <is>
-          <t>SP SEL_INDICADOR_EXPORTAR: consultar el resultado del proceso.</t>
+          <t>Datos de prueba en Indicador_Valor para poder ejercitar los criterios de aceptación.</t>
         </is>
       </c>
       <c r="I429" s="8" t="inlineStr">
@@ -29040,7 +29040,7 @@
       </c>
       <c r="L429" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M429" s="8" t="inlineStr"/>
@@ -29055,17 +29055,17 @@
       </c>
       <c r="B430" s="8" t="inlineStr">
         <is>
-          <t>T-6196</t>
+          <t>T-6078</t>
         </is>
       </c>
       <c r="C430" s="8" t="inlineStr">
         <is>
-          <t>HU-185</t>
+          <t>HU-181</t>
         </is>
       </c>
       <c r="D430" s="8" t="inlineStr">
         <is>
-          <t>Exportar e imprimir reportes</t>
+          <t>Consultar el cumplimiento del plan de mantenimiento</t>
         </is>
       </c>
       <c r="E430" s="8" t="inlineStr">
@@ -29085,16 +29085,16 @@
       </c>
       <c r="H430" s="9" t="inlineStr">
         <is>
-          <t>Datos de prueba en Indicador_Valor para poder ejercitar los criterios de aceptación.</t>
+          <t>Pantalla IndicadorCumplimiento.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
         </is>
       </c>
       <c r="I430" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="J430" s="8" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="K430" s="8" t="inlineStr">
         <is>
@@ -29103,7 +29103,7 @@
       </c>
       <c r="L430" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M430" s="8" t="inlineStr"/>
@@ -29118,17 +29118,17 @@
       </c>
       <c r="B431" s="8" t="inlineStr">
         <is>
-          <t>T-6199</t>
+          <t>T-6079</t>
         </is>
       </c>
       <c r="C431" s="8" t="inlineStr">
         <is>
-          <t>HU-185</t>
+          <t>HU-181</t>
         </is>
       </c>
       <c r="D431" s="8" t="inlineStr">
         <is>
-          <t>Exportar e imprimir reportes</t>
+          <t>Consultar el cumplimiento del plan de mantenimiento</t>
         </is>
       </c>
       <c r="E431" s="8" t="inlineStr">
@@ -29148,16 +29148,16 @@
       </c>
       <c r="H431" s="9" t="inlineStr">
         <is>
-          <t>Pantalla IndicadorExportar.aspx: disparar el proceso, mostrar el resultado y dejar constancia de quién lo ejecutó.</t>
+          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
         </is>
       </c>
       <c r="I431" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="J431" s="8" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="K431" s="8" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
       </c>
       <c r="L431" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M431" s="8" t="inlineStr"/>
@@ -29181,17 +29181,17 @@
       </c>
       <c r="B432" s="8" t="inlineStr">
         <is>
-          <t>T-6200</t>
+          <t>T-6080</t>
         </is>
       </c>
       <c r="C432" s="8" t="inlineStr">
         <is>
-          <t>HU-185</t>
+          <t>HU-181</t>
         </is>
       </c>
       <c r="D432" s="8" t="inlineStr">
         <is>
-          <t>Exportar e imprimir reportes</t>
+          <t>Consultar el cumplimiento del plan de mantenimiento</t>
         </is>
       </c>
       <c r="E432" s="8" t="inlineStr">
@@ -29211,16 +29211,16 @@
       </c>
       <c r="H432" s="9" t="inlineStr">
         <is>
-          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
+          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
         </is>
       </c>
       <c r="I432" s="8" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="J432" s="8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K432" s="8" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
       </c>
       <c r="L432" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M432" s="8" t="inlineStr"/>
@@ -29244,17 +29244,17 @@
       </c>
       <c r="B433" s="8" t="inlineStr">
         <is>
-          <t>T-6201</t>
+          <t>T-6081</t>
         </is>
       </c>
       <c r="C433" s="8" t="inlineStr">
         <is>
-          <t>HU-185</t>
+          <t>HU-181</t>
         </is>
       </c>
       <c r="D433" s="8" t="inlineStr">
         <is>
-          <t>Exportar e imprimir reportes</t>
+          <t>Consultar el cumplimiento del plan de mantenimiento</t>
         </is>
       </c>
       <c r="E433" s="8" t="inlineStr">
@@ -29274,16 +29274,16 @@
       </c>
       <c r="H433" s="9" t="inlineStr">
         <is>
-          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
+          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
         </is>
       </c>
       <c r="I433" s="8" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="J433" s="8" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="K433" s="8" t="inlineStr">
         <is>
@@ -29307,17 +29307,17 @@
       </c>
       <c r="B434" s="8" t="inlineStr">
         <is>
-          <t>T-6202</t>
+          <t>T-6082</t>
         </is>
       </c>
       <c r="C434" s="8" t="inlineStr">
         <is>
-          <t>HU-185</t>
+          <t>HU-182</t>
         </is>
       </c>
       <c r="D434" s="8" t="inlineStr">
         <is>
-          <t>Exportar e imprimir reportes</t>
+          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
         </is>
       </c>
       <c r="E434" s="8" t="inlineStr">
@@ -29337,20 +29337,20 @@
       </c>
       <c r="H434" s="9" t="inlineStr">
         <is>
-          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
+          <t>Modelo: CREAR la tabla Indicador_Valor — todavía no existe. Columnas, PK, FK a sus padres y columna ind_uuid con índice UNIQUE para que la sincronización no duplique.</t>
         </is>
       </c>
       <c r="I434" s="8" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J434" s="8" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="K434" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L434" s="8" t="inlineStr">
@@ -29370,46 +29370,46 @@
       </c>
       <c r="B435" s="8" t="inlineStr">
         <is>
-          <t>T-2142</t>
+          <t>T-6083</t>
         </is>
       </c>
       <c r="C435" s="8" t="inlineStr">
         <is>
-          <t>HU-193</t>
+          <t>HU-182</t>
         </is>
       </c>
       <c r="D435" s="8" t="inlineStr">
         <is>
-          <t>Bloquear el acceso por suscripción vencida</t>
+          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
         </is>
       </c>
       <c r="E435" s="8" t="inlineStr">
         <is>
-          <t>EP-19</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F435" s="8" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
+          <t>Sprint 6</t>
         </is>
       </c>
       <c r="G435" s="8" t="inlineStr">
         <is>
-          <t>Web y App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="H435" s="9" t="inlineStr">
         <is>
-          <t>Consumo del endpoint desde la app cuando corresponda.</t>
+          <t>SP SEL_INDICADOR_DISPONIBILIDAD: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
         </is>
       </c>
       <c r="I435" s="8" t="inlineStr">
         <is>
-          <t>Móvil</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J435" s="8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K435" s="8" t="inlineStr">
         <is>
@@ -29421,11 +29421,7 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="M435" s="8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
+      <c r="M435" s="8" t="inlineStr"/>
       <c r="N435" s="8" t="inlineStr"/>
       <c r="O435" s="8" t="inlineStr"/>
     </row>
@@ -29437,22 +29433,22 @@
       </c>
       <c r="B436" s="8" t="inlineStr">
         <is>
-          <t>T-6127</t>
+          <t>T-6084</t>
         </is>
       </c>
       <c r="C436" s="8" t="inlineStr">
         <is>
-          <t>HU-201</t>
+          <t>HU-182</t>
         </is>
       </c>
       <c r="D436" s="8" t="inlineStr">
         <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
+          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
         </is>
       </c>
       <c r="E436" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F436" s="8" t="inlineStr">
@@ -29467,7 +29463,7 @@
       </c>
       <c r="H436" s="9" t="inlineStr">
         <is>
-          <t>Modelo: revisar Importacion_Carga_Celda — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
+          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Indicador_Valor crezca.</t>
         </is>
       </c>
       <c r="I436" s="8" t="inlineStr">
@@ -29480,12 +29476,12 @@
       </c>
       <c r="K436" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L436" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M436" s="8" t="inlineStr"/>
@@ -29500,22 +29496,22 @@
       </c>
       <c r="B437" s="8" t="inlineStr">
         <is>
-          <t>T-6128</t>
+          <t>T-6085</t>
         </is>
       </c>
       <c r="C437" s="8" t="inlineStr">
         <is>
-          <t>HU-201</t>
+          <t>HU-182</t>
         </is>
       </c>
       <c r="D437" s="8" t="inlineStr">
         <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
+          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
         </is>
       </c>
       <c r="E437" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F437" s="8" t="inlineStr">
@@ -29530,7 +29526,7 @@
       </c>
       <c r="H437" s="9" t="inlineStr">
         <is>
-          <t>SP IMPORTACION_CELDA: el proceso completo dentro de una transacción, con SET XACT_ABORT ON para que un error no deje datos a medias.</t>
+          <t>Datos de prueba en Indicador_Valor para poder ejercitar los criterios de aceptación.</t>
         </is>
       </c>
       <c r="I437" s="8" t="inlineStr">
@@ -29543,12 +29539,12 @@
       </c>
       <c r="K437" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L437" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M437" s="8" t="inlineStr"/>
@@ -29563,22 +29559,22 @@
       </c>
       <c r="B438" s="8" t="inlineStr">
         <is>
-          <t>T-6129</t>
+          <t>T-6088</t>
         </is>
       </c>
       <c r="C438" s="8" t="inlineStr">
         <is>
-          <t>HU-201</t>
+          <t>HU-182</t>
         </is>
       </c>
       <c r="D438" s="8" t="inlineStr">
         <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
+          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
         </is>
       </c>
       <c r="E438" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F438" s="8" t="inlineStr">
@@ -29593,25 +29589,25 @@
       </c>
       <c r="H438" s="9" t="inlineStr">
         <is>
-          <t>Reglas de negocio de la historia en el SP, no en la pantalla: la API y la web tienen que obtener el mismo resultado.</t>
+          <t>Pantalla IndicadorDisponibilidad.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
         </is>
       </c>
       <c r="I438" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="J438" s="8" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="K438" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L438" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M438" s="8" t="inlineStr"/>
@@ -29626,22 +29622,22 @@
       </c>
       <c r="B439" s="8" t="inlineStr">
         <is>
-          <t>T-6130</t>
+          <t>T-6089</t>
         </is>
       </c>
       <c r="C439" s="8" t="inlineStr">
         <is>
-          <t>HU-201</t>
+          <t>HU-182</t>
         </is>
       </c>
       <c r="D439" s="8" t="inlineStr">
         <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
+          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
         </is>
       </c>
       <c r="E439" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F439" s="8" t="inlineStr">
@@ -29656,25 +29652,25 @@
       </c>
       <c r="H439" s="9" t="inlineStr">
         <is>
-          <t>SP SEL_IMPORTACION_CELDA: consultar el resultado del proceso.</t>
+          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
         </is>
       </c>
       <c r="I439" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="J439" s="8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K439" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L439" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M439" s="8" t="inlineStr"/>
@@ -29689,22 +29685,22 @@
       </c>
       <c r="B440" s="8" t="inlineStr">
         <is>
-          <t>T-6131</t>
+          <t>T-6090</t>
         </is>
       </c>
       <c r="C440" s="8" t="inlineStr">
         <is>
-          <t>HU-201</t>
+          <t>HU-182</t>
         </is>
       </c>
       <c r="D440" s="8" t="inlineStr">
         <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
+          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
         </is>
       </c>
       <c r="E440" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F440" s="8" t="inlineStr">
@@ -29719,25 +29715,25 @@
       </c>
       <c r="H440" s="9" t="inlineStr">
         <is>
-          <t>Datos de prueba en Importacion_Carga_Celda para poder ejercitar los criterios de aceptación.</t>
+          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
         </is>
       </c>
       <c r="I440" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="J440" s="8" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="K440" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L440" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M440" s="8" t="inlineStr"/>
@@ -29752,22 +29748,22 @@
       </c>
       <c r="B441" s="8" t="inlineStr">
         <is>
-          <t>T-6134</t>
+          <t>T-6091</t>
         </is>
       </c>
       <c r="C441" s="8" t="inlineStr">
         <is>
-          <t>HU-201</t>
+          <t>HU-182</t>
         </is>
       </c>
       <c r="D441" s="8" t="inlineStr">
         <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
+          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
         </is>
       </c>
       <c r="E441" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F441" s="8" t="inlineStr">
@@ -29782,25 +29778,25 @@
       </c>
       <c r="H441" s="9" t="inlineStr">
         <is>
-          <t>Pantalla ImportacionCelda.aspx: disparar el proceso, mostrar el resultado y dejar constancia de quién lo ejecutó.</t>
+          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
         </is>
       </c>
       <c r="I441" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="J441" s="8" t="n">
-        <v>2.25</v>
+        <v>0.5</v>
       </c>
       <c r="K441" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L441" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M441" s="8" t="inlineStr"/>
@@ -29815,22 +29811,22 @@
       </c>
       <c r="B442" s="8" t="inlineStr">
         <is>
-          <t>T-6135</t>
+          <t>T-6092</t>
         </is>
       </c>
       <c r="C442" s="8" t="inlineStr">
         <is>
-          <t>HU-201</t>
+          <t>HU-182</t>
         </is>
       </c>
       <c r="D442" s="8" t="inlineStr">
         <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
+          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
         </is>
       </c>
       <c r="E442" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F442" s="8" t="inlineStr">
@@ -29845,25 +29841,25 @@
       </c>
       <c r="H442" s="9" t="inlineStr">
         <is>
-          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
+          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
         </is>
       </c>
       <c r="I442" s="8" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Validación</t>
         </is>
       </c>
       <c r="J442" s="8" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="K442" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L442" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M442" s="8" t="inlineStr"/>
@@ -29878,22 +29874,22 @@
       </c>
       <c r="B443" s="8" t="inlineStr">
         <is>
-          <t>T-6136</t>
+          <t>T-6093</t>
         </is>
       </c>
       <c r="C443" s="8" t="inlineStr">
         <is>
-          <t>HU-201</t>
+          <t>HU-183</t>
         </is>
       </c>
       <c r="D443" s="8" t="inlineStr">
         <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
+          <t>Consultar los costos de mantenimiento</t>
         </is>
       </c>
       <c r="E443" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F443" s="8" t="inlineStr">
@@ -29908,20 +29904,20 @@
       </c>
       <c r="H443" s="9" t="inlineStr">
         <is>
-          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
+          <t>Modelo: CREAR la tabla Indicador_Valor — todavía no existe. Columnas, PK, FK a sus padres y columna ind_uuid con índice UNIQUE para que la sincronización no duplique.</t>
         </is>
       </c>
       <c r="I443" s="8" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J443" s="8" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="K443" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L443" s="8" t="inlineStr">
@@ -29941,22 +29937,22 @@
       </c>
       <c r="B444" s="8" t="inlineStr">
         <is>
-          <t>T-6137</t>
+          <t>T-6094</t>
         </is>
       </c>
       <c r="C444" s="8" t="inlineStr">
         <is>
-          <t>HU-201</t>
+          <t>HU-183</t>
         </is>
       </c>
       <c r="D444" s="8" t="inlineStr">
         <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
+          <t>Consultar los costos de mantenimiento</t>
         </is>
       </c>
       <c r="E444" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F444" s="8" t="inlineStr">
@@ -29971,20 +29967,20 @@
       </c>
       <c r="H444" s="9" t="inlineStr">
         <is>
-          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
+          <t>SP SEL_INDICADOR_COSTO: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
         </is>
       </c>
       <c r="I444" s="8" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J444" s="8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K444" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L444" s="8" t="inlineStr">
@@ -30004,22 +30000,22 @@
       </c>
       <c r="B445" s="8" t="inlineStr">
         <is>
-          <t>T-6138</t>
+          <t>T-6095</t>
         </is>
       </c>
       <c r="C445" s="8" t="inlineStr">
         <is>
-          <t>HU-201</t>
+          <t>HU-183</t>
         </is>
       </c>
       <c r="D445" s="8" t="inlineStr">
         <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
+          <t>Consultar los costos de mantenimiento</t>
         </is>
       </c>
       <c r="E445" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F445" s="8" t="inlineStr">
@@ -30034,20 +30030,20 @@
       </c>
       <c r="H445" s="9" t="inlineStr">
         <is>
-          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
+          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Indicador_Valor crezca.</t>
         </is>
       </c>
       <c r="I445" s="8" t="inlineStr">
         <is>
-          <t>Validación</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J445" s="8" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="K445" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L445" s="8" t="inlineStr">
@@ -30067,22 +30063,22 @@
       </c>
       <c r="B446" s="8" t="inlineStr">
         <is>
-          <t>T-6139</t>
+          <t>T-6096</t>
         </is>
       </c>
       <c r="C446" s="8" t="inlineStr">
         <is>
-          <t>HU-202</t>
+          <t>HU-183</t>
         </is>
       </c>
       <c r="D446" s="8" t="inlineStr">
         <is>
-          <t>Importar el plan anual desde una planilla</t>
+          <t>Consultar los costos de mantenimiento</t>
         </is>
       </c>
       <c r="E446" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F446" s="8" t="inlineStr">
@@ -30097,7 +30093,7 @@
       </c>
       <c r="H446" s="9" t="inlineStr">
         <is>
-          <t>Modelo: revisar Importacion_Carga — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
+          <t>Datos de prueba en Indicador_Valor para poder ejercitar los criterios de aceptación.</t>
         </is>
       </c>
       <c r="I446" s="8" t="inlineStr">
@@ -30106,16 +30102,16 @@
         </is>
       </c>
       <c r="J446" s="8" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="K446" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L446" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M446" s="8" t="inlineStr"/>
@@ -30130,22 +30126,22 @@
       </c>
       <c r="B447" s="8" t="inlineStr">
         <is>
-          <t>T-6140</t>
+          <t>T-6099</t>
         </is>
       </c>
       <c r="C447" s="8" t="inlineStr">
         <is>
-          <t>HU-202</t>
+          <t>HU-183</t>
         </is>
       </c>
       <c r="D447" s="8" t="inlineStr">
         <is>
-          <t>Importar el plan anual desde una planilla</t>
+          <t>Consultar los costos de mantenimiento</t>
         </is>
       </c>
       <c r="E447" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F447" s="8" t="inlineStr">
@@ -30160,25 +30156,25 @@
       </c>
       <c r="H447" s="9" t="inlineStr">
         <is>
-          <t>SP IMPORTACION_PLAN: el proceso completo dentro de una transacción, con SET XACT_ABORT ON para que un error no deje datos a medias.</t>
+          <t>Pantalla IndicadorCosto.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
         </is>
       </c>
       <c r="I447" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="J447" s="8" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="K447" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L447" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M447" s="8" t="inlineStr"/>
@@ -30193,22 +30189,22 @@
       </c>
       <c r="B448" s="8" t="inlineStr">
         <is>
-          <t>T-6141</t>
+          <t>T-6100</t>
         </is>
       </c>
       <c r="C448" s="8" t="inlineStr">
         <is>
-          <t>HU-202</t>
+          <t>HU-183</t>
         </is>
       </c>
       <c r="D448" s="8" t="inlineStr">
         <is>
-          <t>Importar el plan anual desde una planilla</t>
+          <t>Consultar los costos de mantenimiento</t>
         </is>
       </c>
       <c r="E448" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F448" s="8" t="inlineStr">
@@ -30223,25 +30219,25 @@
       </c>
       <c r="H448" s="9" t="inlineStr">
         <is>
-          <t>Reglas de negocio de la historia en el SP, no en la pantalla: la API y la web tienen que obtener el mismo resultado.</t>
+          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
         </is>
       </c>
       <c r="I448" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="J448" s="8" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="K448" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L448" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M448" s="8" t="inlineStr"/>
@@ -30256,22 +30252,22 @@
       </c>
       <c r="B449" s="8" t="inlineStr">
         <is>
-          <t>T-6142</t>
+          <t>T-6101</t>
         </is>
       </c>
       <c r="C449" s="8" t="inlineStr">
         <is>
-          <t>HU-202</t>
+          <t>HU-183</t>
         </is>
       </c>
       <c r="D449" s="8" t="inlineStr">
         <is>
-          <t>Importar el plan anual desde una planilla</t>
+          <t>Consultar los costos de mantenimiento</t>
         </is>
       </c>
       <c r="E449" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F449" s="8" t="inlineStr">
@@ -30286,12 +30282,12 @@
       </c>
       <c r="H449" s="9" t="inlineStr">
         <is>
-          <t>SP SEL_IMPORTACION_PLAN: consultar el resultado del proceso.</t>
+          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
         </is>
       </c>
       <c r="I449" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="J449" s="8" t="n">
@@ -30299,12 +30295,12 @@
       </c>
       <c r="K449" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L449" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M449" s="8" t="inlineStr"/>
@@ -30319,22 +30315,22 @@
       </c>
       <c r="B450" s="8" t="inlineStr">
         <is>
-          <t>T-6143</t>
+          <t>T-6102</t>
         </is>
       </c>
       <c r="C450" s="8" t="inlineStr">
         <is>
-          <t>HU-202</t>
+          <t>HU-183</t>
         </is>
       </c>
       <c r="D450" s="8" t="inlineStr">
         <is>
-          <t>Importar el plan anual desde una planilla</t>
+          <t>Consultar los costos de mantenimiento</t>
         </is>
       </c>
       <c r="E450" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F450" s="8" t="inlineStr">
@@ -30349,25 +30345,25 @@
       </c>
       <c r="H450" s="9" t="inlineStr">
         <is>
-          <t>Datos de prueba en Importacion_Carga para poder ejercitar los criterios de aceptación.</t>
+          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
         </is>
       </c>
       <c r="I450" s="8" t="inlineStr">
         <is>
-          <t>Base de datos</t>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="J450" s="8" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="K450" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L450" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M450" s="8" t="inlineStr"/>
@@ -30382,22 +30378,22 @@
       </c>
       <c r="B451" s="8" t="inlineStr">
         <is>
-          <t>T-6146</t>
+          <t>T-6103</t>
         </is>
       </c>
       <c r="C451" s="8" t="inlineStr">
         <is>
-          <t>HU-202</t>
+          <t>HU-183</t>
         </is>
       </c>
       <c r="D451" s="8" t="inlineStr">
         <is>
-          <t>Importar el plan anual desde una planilla</t>
+          <t>Consultar los costos de mantenimiento</t>
         </is>
       </c>
       <c r="E451" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F451" s="8" t="inlineStr">
@@ -30412,25 +30408,25 @@
       </c>
       <c r="H451" s="9" t="inlineStr">
         <is>
-          <t>Pantalla ImportacionPlan.aspx: disparar el proceso, mostrar el resultado y dejar constancia de quién lo ejecutó.</t>
+          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
         </is>
       </c>
       <c r="I451" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Validación</t>
         </is>
       </c>
       <c r="J451" s="8" t="n">
-        <v>4</v>
+        <v>0.25</v>
       </c>
       <c r="K451" s="8" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="L451" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M451" s="8" t="inlineStr"/>
@@ -30445,22 +30441,22 @@
       </c>
       <c r="B452" s="8" t="inlineStr">
         <is>
-          <t>T-6147</t>
+          <t>T-6116</t>
         </is>
       </c>
       <c r="C452" s="8" t="inlineStr">
         <is>
-          <t>HU-202</t>
+          <t>HU-184</t>
         </is>
       </c>
       <c r="D452" s="8" t="inlineStr">
         <is>
-          <t>Importar el plan anual desde una planilla</t>
+          <t>Consultar la bandeja de alertas</t>
         </is>
       </c>
       <c r="E452" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F452" s="8" t="inlineStr">
@@ -30470,21 +30466,21 @@
       </c>
       <c r="G452" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Web y App</t>
         </is>
       </c>
       <c r="H452" s="9" t="inlineStr">
         <is>
-          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
+          <t>Modelo: revisar Alerta — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
         </is>
       </c>
       <c r="I452" s="8" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J452" s="8" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="K452" s="8" t="inlineStr">
         <is>
@@ -30493,7 +30489,7 @@
       </c>
       <c r="L452" s="8" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="M452" s="8" t="inlineStr"/>
@@ -30508,22 +30504,22 @@
       </c>
       <c r="B453" s="8" t="inlineStr">
         <is>
-          <t>T-6148</t>
+          <t>T-6117</t>
         </is>
       </c>
       <c r="C453" s="8" t="inlineStr">
         <is>
-          <t>HU-202</t>
+          <t>HU-184</t>
         </is>
       </c>
       <c r="D453" s="8" t="inlineStr">
         <is>
-          <t>Importar el plan anual desde una planilla</t>
+          <t>Consultar la bandeja de alertas</t>
         </is>
       </c>
       <c r="E453" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F453" s="8" t="inlineStr">
@@ -30533,21 +30529,21 @@
       </c>
       <c r="G453" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Web y App</t>
         </is>
       </c>
       <c r="H453" s="9" t="inlineStr">
         <is>
-          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
+          <t>SP SEL_ALERTA: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
         </is>
       </c>
       <c r="I453" s="8" t="inlineStr">
         <is>
-          <t>Pruebas</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J453" s="8" t="n">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
       <c r="K453" s="8" t="inlineStr">
         <is>
@@ -30571,22 +30567,22 @@
       </c>
       <c r="B454" s="8" t="inlineStr">
         <is>
-          <t>T-6149</t>
+          <t>T-6118</t>
         </is>
       </c>
       <c r="C454" s="8" t="inlineStr">
         <is>
-          <t>HU-202</t>
+          <t>HU-184</t>
         </is>
       </c>
       <c r="D454" s="8" t="inlineStr">
         <is>
-          <t>Importar el plan anual desde una planilla</t>
+          <t>Consultar la bandeja de alertas</t>
         </is>
       </c>
       <c r="E454" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F454" s="8" t="inlineStr">
@@ -30596,21 +30592,21 @@
       </c>
       <c r="G454" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Web y App</t>
         </is>
       </c>
       <c r="H454" s="9" t="inlineStr">
         <is>
-          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
+          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Alerta crezca.</t>
         </is>
       </c>
       <c r="I454" s="8" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J454" s="8" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="K454" s="8" t="inlineStr">
         <is>
@@ -30634,22 +30630,22 @@
       </c>
       <c r="B455" s="8" t="inlineStr">
         <is>
-          <t>T-6150</t>
+          <t>T-6119</t>
         </is>
       </c>
       <c r="C455" s="8" t="inlineStr">
         <is>
-          <t>HU-202</t>
+          <t>HU-184</t>
         </is>
       </c>
       <c r="D455" s="8" t="inlineStr">
         <is>
-          <t>Importar el plan anual desde una planilla</t>
+          <t>Consultar la bandeja de alertas</t>
         </is>
       </c>
       <c r="E455" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F455" s="8" t="inlineStr">
@@ -30659,17 +30655,17 @@
       </c>
       <c r="G455" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Web y App</t>
         </is>
       </c>
       <c r="H455" s="9" t="inlineStr">
         <is>
-          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
+          <t>Datos de prueba en Alerta para poder ejercitar los criterios de aceptación.</t>
         </is>
       </c>
       <c r="I455" s="8" t="inlineStr">
         <is>
-          <t>Validación</t>
+          <t>Base de datos</t>
         </is>
       </c>
       <c r="J455" s="8" t="n">
@@ -30689,8 +30685,3477 @@
       <c r="N455" s="8" t="inlineStr"/>
       <c r="O455" s="8" t="inlineStr"/>
     </row>
+    <row r="456">
+      <c r="A456" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B456" s="8" t="inlineStr">
+        <is>
+          <t>T-6120</t>
+        </is>
+      </c>
+      <c r="C456" s="8" t="inlineStr">
+        <is>
+          <t>HU-184</t>
+        </is>
+      </c>
+      <c r="D456" s="8" t="inlineStr">
+        <is>
+          <t>Consultar la bandeja de alertas</t>
+        </is>
+      </c>
+      <c r="E456" s="8" t="inlineStr">
+        <is>
+          <t>EP-18</t>
+        </is>
+      </c>
+      <c r="F456" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G456" s="8" t="inlineStr">
+        <is>
+          <t>Web y App</t>
+        </is>
+      </c>
+      <c r="H456" s="9" t="inlineStr">
+        <is>
+          <t>GET /api/alertas — consulta con filtros y paginación.</t>
+        </is>
+      </c>
+      <c r="I456" s="8" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="J456" s="8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K456" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L456" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M456" s="8" t="inlineStr"/>
+      <c r="N456" s="8" t="inlineStr"/>
+      <c r="O456" s="8" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B457" s="8" t="inlineStr">
+        <is>
+          <t>T-6121</t>
+        </is>
+      </c>
+      <c r="C457" s="8" t="inlineStr">
+        <is>
+          <t>HU-184</t>
+        </is>
+      </c>
+      <c r="D457" s="8" t="inlineStr">
+        <is>
+          <t>Consultar la bandeja de alertas</t>
+        </is>
+      </c>
+      <c r="E457" s="8" t="inlineStr">
+        <is>
+          <t>EP-18</t>
+        </is>
+      </c>
+      <c r="F457" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G457" s="8" t="inlineStr">
+        <is>
+          <t>Web y App</t>
+        </is>
+      </c>
+      <c r="H457" s="9" t="inlineStr">
+        <is>
+          <t>Caché corta de la respuesta cuando el dato no cambia por petición.</t>
+        </is>
+      </c>
+      <c r="I457" s="8" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="J457" s="8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K457" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L457" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M457" s="8" t="inlineStr"/>
+      <c r="N457" s="8" t="inlineStr"/>
+      <c r="O457" s="8" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B458" s="8" t="inlineStr">
+        <is>
+          <t>T-6122</t>
+        </is>
+      </c>
+      <c r="C458" s="8" t="inlineStr">
+        <is>
+          <t>HU-184</t>
+        </is>
+      </c>
+      <c r="D458" s="8" t="inlineStr">
+        <is>
+          <t>Consultar la bandeja de alertas</t>
+        </is>
+      </c>
+      <c r="E458" s="8" t="inlineStr">
+        <is>
+          <t>EP-18</t>
+        </is>
+      </c>
+      <c r="F458" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G458" s="8" t="inlineStr">
+        <is>
+          <t>Web y App</t>
+        </is>
+      </c>
+      <c r="H458" s="9" t="inlineStr">
+        <is>
+          <t>Pantalla Alerta.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
+        </is>
+      </c>
+      <c r="I458" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="J458" s="8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K458" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L458" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M458" s="8" t="inlineStr"/>
+      <c r="N458" s="8" t="inlineStr"/>
+      <c r="O458" s="8" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B459" s="8" t="inlineStr">
+        <is>
+          <t>T-6123</t>
+        </is>
+      </c>
+      <c r="C459" s="8" t="inlineStr">
+        <is>
+          <t>HU-184</t>
+        </is>
+      </c>
+      <c r="D459" s="8" t="inlineStr">
+        <is>
+          <t>Consultar la bandeja de alertas</t>
+        </is>
+      </c>
+      <c r="E459" s="8" t="inlineStr">
+        <is>
+          <t>EP-18</t>
+        </is>
+      </c>
+      <c r="F459" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G459" s="8" t="inlineStr">
+        <is>
+          <t>Web y App</t>
+        </is>
+      </c>
+      <c r="H459" s="9" t="inlineStr">
+        <is>
+          <t>Consumo del endpoint desde la app cuando corresponda.</t>
+        </is>
+      </c>
+      <c r="I459" s="8" t="inlineStr">
+        <is>
+          <t>Móvil</t>
+        </is>
+      </c>
+      <c r="J459" s="8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K459" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L459" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M459" s="8" t="inlineStr"/>
+      <c r="N459" s="8" t="inlineStr"/>
+      <c r="O459" s="8" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B460" s="8" t="inlineStr">
+        <is>
+          <t>T-6124</t>
+        </is>
+      </c>
+      <c r="C460" s="8" t="inlineStr">
+        <is>
+          <t>HU-184</t>
+        </is>
+      </c>
+      <c r="D460" s="8" t="inlineStr">
+        <is>
+          <t>Consultar la bandeja de alertas</t>
+        </is>
+      </c>
+      <c r="E460" s="8" t="inlineStr">
+        <is>
+          <t>EP-18</t>
+        </is>
+      </c>
+      <c r="F460" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G460" s="8" t="inlineStr">
+        <is>
+          <t>Web y App</t>
+        </is>
+      </c>
+      <c r="H460" s="9" t="inlineStr">
+        <is>
+          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
+        </is>
+      </c>
+      <c r="I460" s="8" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="J460" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K460" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L460" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M460" s="8" t="inlineStr"/>
+      <c r="N460" s="8" t="inlineStr"/>
+      <c r="O460" s="8" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B461" s="8" t="inlineStr">
+        <is>
+          <t>T-6125</t>
+        </is>
+      </c>
+      <c r="C461" s="8" t="inlineStr">
+        <is>
+          <t>HU-184</t>
+        </is>
+      </c>
+      <c r="D461" s="8" t="inlineStr">
+        <is>
+          <t>Consultar la bandeja de alertas</t>
+        </is>
+      </c>
+      <c r="E461" s="8" t="inlineStr">
+        <is>
+          <t>EP-18</t>
+        </is>
+      </c>
+      <c r="F461" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G461" s="8" t="inlineStr">
+        <is>
+          <t>Web y App</t>
+        </is>
+      </c>
+      <c r="H461" s="9" t="inlineStr">
+        <is>
+          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
+        </is>
+      </c>
+      <c r="I461" s="8" t="inlineStr">
+        <is>
+          <t>Pruebas</t>
+        </is>
+      </c>
+      <c r="J461" s="8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K461" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L461" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M461" s="8" t="inlineStr"/>
+      <c r="N461" s="8" t="inlineStr"/>
+      <c r="O461" s="8" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B462" s="8" t="inlineStr">
+        <is>
+          <t>T-6126</t>
+        </is>
+      </c>
+      <c r="C462" s="8" t="inlineStr">
+        <is>
+          <t>HU-184</t>
+        </is>
+      </c>
+      <c r="D462" s="8" t="inlineStr">
+        <is>
+          <t>Consultar la bandeja de alertas</t>
+        </is>
+      </c>
+      <c r="E462" s="8" t="inlineStr">
+        <is>
+          <t>EP-18</t>
+        </is>
+      </c>
+      <c r="F462" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G462" s="8" t="inlineStr">
+        <is>
+          <t>Web y App</t>
+        </is>
+      </c>
+      <c r="H462" s="9" t="inlineStr">
+        <is>
+          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
+        </is>
+      </c>
+      <c r="I462" s="8" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="J462" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K462" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L462" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M462" s="8" t="inlineStr"/>
+      <c r="N462" s="8" t="inlineStr"/>
+      <c r="O462" s="8" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B463" s="8" t="inlineStr">
+        <is>
+          <t>T-6192</t>
+        </is>
+      </c>
+      <c r="C463" s="8" t="inlineStr">
+        <is>
+          <t>HU-185</t>
+        </is>
+      </c>
+      <c r="D463" s="8" t="inlineStr">
+        <is>
+          <t>Exportar e imprimir reportes</t>
+        </is>
+      </c>
+      <c r="E463" s="8" t="inlineStr">
+        <is>
+          <t>EP-18</t>
+        </is>
+      </c>
+      <c r="F463" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G463" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H463" s="9" t="inlineStr">
+        <is>
+          <t>Modelo: CREAR la tabla Indicador_Valor — todavía no existe. Columnas, PK, FK a sus padres y columna ind_uuid con índice UNIQUE para que la sincronización no duplique.</t>
+        </is>
+      </c>
+      <c r="I463" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J463" s="8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K463" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L463" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M463" s="8" t="inlineStr"/>
+      <c r="N463" s="8" t="inlineStr"/>
+      <c r="O463" s="8" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B464" s="8" t="inlineStr">
+        <is>
+          <t>T-6193</t>
+        </is>
+      </c>
+      <c r="C464" s="8" t="inlineStr">
+        <is>
+          <t>HU-185</t>
+        </is>
+      </c>
+      <c r="D464" s="8" t="inlineStr">
+        <is>
+          <t>Exportar e imprimir reportes</t>
+        </is>
+      </c>
+      <c r="E464" s="8" t="inlineStr">
+        <is>
+          <t>EP-18</t>
+        </is>
+      </c>
+      <c r="F464" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G464" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H464" s="9" t="inlineStr">
+        <is>
+          <t>SP INDICADOR_EXPORTAR: el proceso completo dentro de una transacción, con SET XACT_ABORT ON para que un error no deje datos a medias.</t>
+        </is>
+      </c>
+      <c r="I464" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J464" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K464" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L464" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M464" s="8" t="inlineStr"/>
+      <c r="N464" s="8" t="inlineStr"/>
+      <c r="O464" s="8" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B465" s="8" t="inlineStr">
+        <is>
+          <t>T-6194</t>
+        </is>
+      </c>
+      <c r="C465" s="8" t="inlineStr">
+        <is>
+          <t>HU-185</t>
+        </is>
+      </c>
+      <c r="D465" s="8" t="inlineStr">
+        <is>
+          <t>Exportar e imprimir reportes</t>
+        </is>
+      </c>
+      <c r="E465" s="8" t="inlineStr">
+        <is>
+          <t>EP-18</t>
+        </is>
+      </c>
+      <c r="F465" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G465" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H465" s="9" t="inlineStr">
+        <is>
+          <t>Reglas de negocio de la historia en el SP, no en la pantalla: la API y la web tienen que obtener el mismo resultado.</t>
+        </is>
+      </c>
+      <c r="I465" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J465" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K465" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L465" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M465" s="8" t="inlineStr"/>
+      <c r="N465" s="8" t="inlineStr"/>
+      <c r="O465" s="8" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B466" s="8" t="inlineStr">
+        <is>
+          <t>T-6195</t>
+        </is>
+      </c>
+      <c r="C466" s="8" t="inlineStr">
+        <is>
+          <t>HU-185</t>
+        </is>
+      </c>
+      <c r="D466" s="8" t="inlineStr">
+        <is>
+          <t>Exportar e imprimir reportes</t>
+        </is>
+      </c>
+      <c r="E466" s="8" t="inlineStr">
+        <is>
+          <t>EP-18</t>
+        </is>
+      </c>
+      <c r="F466" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G466" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H466" s="9" t="inlineStr">
+        <is>
+          <t>SP SEL_INDICADOR_EXPORTAR: consultar el resultado del proceso.</t>
+        </is>
+      </c>
+      <c r="I466" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J466" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K466" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L466" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M466" s="8" t="inlineStr"/>
+      <c r="N466" s="8" t="inlineStr"/>
+      <c r="O466" s="8" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B467" s="8" t="inlineStr">
+        <is>
+          <t>T-6196</t>
+        </is>
+      </c>
+      <c r="C467" s="8" t="inlineStr">
+        <is>
+          <t>HU-185</t>
+        </is>
+      </c>
+      <c r="D467" s="8" t="inlineStr">
+        <is>
+          <t>Exportar e imprimir reportes</t>
+        </is>
+      </c>
+      <c r="E467" s="8" t="inlineStr">
+        <is>
+          <t>EP-18</t>
+        </is>
+      </c>
+      <c r="F467" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G467" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H467" s="9" t="inlineStr">
+        <is>
+          <t>Datos de prueba en Indicador_Valor para poder ejercitar los criterios de aceptación.</t>
+        </is>
+      </c>
+      <c r="I467" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J467" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K467" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L467" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M467" s="8" t="inlineStr"/>
+      <c r="N467" s="8" t="inlineStr"/>
+      <c r="O467" s="8" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B468" s="8" t="inlineStr">
+        <is>
+          <t>T-6199</t>
+        </is>
+      </c>
+      <c r="C468" s="8" t="inlineStr">
+        <is>
+          <t>HU-185</t>
+        </is>
+      </c>
+      <c r="D468" s="8" t="inlineStr">
+        <is>
+          <t>Exportar e imprimir reportes</t>
+        </is>
+      </c>
+      <c r="E468" s="8" t="inlineStr">
+        <is>
+          <t>EP-18</t>
+        </is>
+      </c>
+      <c r="F468" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G468" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H468" s="9" t="inlineStr">
+        <is>
+          <t>Pantalla IndicadorExportar.aspx: disparar el proceso, mostrar el resultado y dejar constancia de quién lo ejecutó.</t>
+        </is>
+      </c>
+      <c r="I468" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="J468" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K468" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L468" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M468" s="8" t="inlineStr"/>
+      <c r="N468" s="8" t="inlineStr"/>
+      <c r="O468" s="8" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B469" s="8" t="inlineStr">
+        <is>
+          <t>T-6200</t>
+        </is>
+      </c>
+      <c r="C469" s="8" t="inlineStr">
+        <is>
+          <t>HU-185</t>
+        </is>
+      </c>
+      <c r="D469" s="8" t="inlineStr">
+        <is>
+          <t>Exportar e imprimir reportes</t>
+        </is>
+      </c>
+      <c r="E469" s="8" t="inlineStr">
+        <is>
+          <t>EP-18</t>
+        </is>
+      </c>
+      <c r="F469" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G469" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H469" s="9" t="inlineStr">
+        <is>
+          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
+        </is>
+      </c>
+      <c r="I469" s="8" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="J469" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K469" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L469" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M469" s="8" t="inlineStr"/>
+      <c r="N469" s="8" t="inlineStr"/>
+      <c r="O469" s="8" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B470" s="8" t="inlineStr">
+        <is>
+          <t>T-6201</t>
+        </is>
+      </c>
+      <c r="C470" s="8" t="inlineStr">
+        <is>
+          <t>HU-185</t>
+        </is>
+      </c>
+      <c r="D470" s="8" t="inlineStr">
+        <is>
+          <t>Exportar e imprimir reportes</t>
+        </is>
+      </c>
+      <c r="E470" s="8" t="inlineStr">
+        <is>
+          <t>EP-18</t>
+        </is>
+      </c>
+      <c r="F470" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G470" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H470" s="9" t="inlineStr">
+        <is>
+          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
+        </is>
+      </c>
+      <c r="I470" s="8" t="inlineStr">
+        <is>
+          <t>Pruebas</t>
+        </is>
+      </c>
+      <c r="J470" s="8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K470" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L470" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M470" s="8" t="inlineStr"/>
+      <c r="N470" s="8" t="inlineStr"/>
+      <c r="O470" s="8" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B471" s="8" t="inlineStr">
+        <is>
+          <t>T-6202</t>
+        </is>
+      </c>
+      <c r="C471" s="8" t="inlineStr">
+        <is>
+          <t>HU-185</t>
+        </is>
+      </c>
+      <c r="D471" s="8" t="inlineStr">
+        <is>
+          <t>Exportar e imprimir reportes</t>
+        </is>
+      </c>
+      <c r="E471" s="8" t="inlineStr">
+        <is>
+          <t>EP-18</t>
+        </is>
+      </c>
+      <c r="F471" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G471" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H471" s="9" t="inlineStr">
+        <is>
+          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
+        </is>
+      </c>
+      <c r="I471" s="8" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="J471" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K471" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L471" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M471" s="8" t="inlineStr"/>
+      <c r="N471" s="8" t="inlineStr"/>
+      <c r="O471" s="8" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B472" s="8" t="inlineStr">
+        <is>
+          <t>T-2142</t>
+        </is>
+      </c>
+      <c r="C472" s="8" t="inlineStr">
+        <is>
+          <t>HU-193</t>
+        </is>
+      </c>
+      <c r="D472" s="8" t="inlineStr">
+        <is>
+          <t>Bloquear el acceso por suscripción vencida</t>
+        </is>
+      </c>
+      <c r="E472" s="8" t="inlineStr">
+        <is>
+          <t>EP-19</t>
+        </is>
+      </c>
+      <c r="F472" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="G472" s="8" t="inlineStr">
+        <is>
+          <t>Web y App</t>
+        </is>
+      </c>
+      <c r="H472" s="9" t="inlineStr">
+        <is>
+          <t>Consumo del endpoint desde la app cuando corresponda.</t>
+        </is>
+      </c>
+      <c r="I472" s="8" t="inlineStr">
+        <is>
+          <t>Móvil</t>
+        </is>
+      </c>
+      <c r="J472" s="8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K472" s="8" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="L472" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M472" s="8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N472" s="8" t="inlineStr"/>
+      <c r="O472" s="8" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B473" s="8" t="inlineStr">
+        <is>
+          <t>T-6104</t>
+        </is>
+      </c>
+      <c r="C473" s="8" t="inlineStr">
+        <is>
+          <t>HU-200</t>
+        </is>
+      </c>
+      <c r="D473" s="8" t="inlineStr">
+        <is>
+          <t>Importar activos desde una planilla</t>
+        </is>
+      </c>
+      <c r="E473" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F473" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G473" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H473" s="9" t="inlineStr">
+        <is>
+          <t>Modelo: revisar Importacion_Carga — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
+        </is>
+      </c>
+      <c r="I473" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J473" s="8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K473" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L473" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M473" s="8" t="inlineStr"/>
+      <c r="N473" s="8" t="inlineStr"/>
+      <c r="O473" s="8" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B474" s="8" t="inlineStr">
+        <is>
+          <t>T-6105</t>
+        </is>
+      </c>
+      <c r="C474" s="8" t="inlineStr">
+        <is>
+          <t>HU-200</t>
+        </is>
+      </c>
+      <c r="D474" s="8" t="inlineStr">
+        <is>
+          <t>Importar activos desde una planilla</t>
+        </is>
+      </c>
+      <c r="E474" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F474" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G474" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H474" s="9" t="inlineStr">
+        <is>
+          <t>SP IMPORTACION_ACTIVO: el proceso completo dentro de una transacción, con SET XACT_ABORT ON para que un error no deje datos a medias.</t>
+        </is>
+      </c>
+      <c r="I474" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J474" s="8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K474" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L474" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M474" s="8" t="inlineStr"/>
+      <c r="N474" s="8" t="inlineStr"/>
+      <c r="O474" s="8" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B475" s="8" t="inlineStr">
+        <is>
+          <t>T-6106</t>
+        </is>
+      </c>
+      <c r="C475" s="8" t="inlineStr">
+        <is>
+          <t>HU-200</t>
+        </is>
+      </c>
+      <c r="D475" s="8" t="inlineStr">
+        <is>
+          <t>Importar activos desde una planilla</t>
+        </is>
+      </c>
+      <c r="E475" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F475" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G475" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H475" s="9" t="inlineStr">
+        <is>
+          <t>Reglas de negocio de la historia en el SP, no en la pantalla: la API y la web tienen que obtener el mismo resultado.</t>
+        </is>
+      </c>
+      <c r="I475" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J475" s="8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K475" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L475" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M475" s="8" t="inlineStr"/>
+      <c r="N475" s="8" t="inlineStr"/>
+      <c r="O475" s="8" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B476" s="8" t="inlineStr">
+        <is>
+          <t>T-6107</t>
+        </is>
+      </c>
+      <c r="C476" s="8" t="inlineStr">
+        <is>
+          <t>HU-200</t>
+        </is>
+      </c>
+      <c r="D476" s="8" t="inlineStr">
+        <is>
+          <t>Importar activos desde una planilla</t>
+        </is>
+      </c>
+      <c r="E476" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F476" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G476" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H476" s="9" t="inlineStr">
+        <is>
+          <t>SP SEL_IMPORTACION_ACTIVO: consultar el resultado del proceso.</t>
+        </is>
+      </c>
+      <c r="I476" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J476" s="8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K476" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L476" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M476" s="8" t="inlineStr"/>
+      <c r="N476" s="8" t="inlineStr"/>
+      <c r="O476" s="8" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B477" s="8" t="inlineStr">
+        <is>
+          <t>T-6108</t>
+        </is>
+      </c>
+      <c r="C477" s="8" t="inlineStr">
+        <is>
+          <t>HU-200</t>
+        </is>
+      </c>
+      <c r="D477" s="8" t="inlineStr">
+        <is>
+          <t>Importar activos desde una planilla</t>
+        </is>
+      </c>
+      <c r="E477" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F477" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G477" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H477" s="9" t="inlineStr">
+        <is>
+          <t>Datos de prueba en Importacion_Carga para poder ejercitar los criterios de aceptación.</t>
+        </is>
+      </c>
+      <c r="I477" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J477" s="8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K477" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L477" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M477" s="8" t="inlineStr"/>
+      <c r="N477" s="8" t="inlineStr"/>
+      <c r="O477" s="8" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B478" s="8" t="inlineStr">
+        <is>
+          <t>T-6111</t>
+        </is>
+      </c>
+      <c r="C478" s="8" t="inlineStr">
+        <is>
+          <t>HU-200</t>
+        </is>
+      </c>
+      <c r="D478" s="8" t="inlineStr">
+        <is>
+          <t>Importar activos desde una planilla</t>
+        </is>
+      </c>
+      <c r="E478" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F478" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G478" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H478" s="9" t="inlineStr">
+        <is>
+          <t>Pantalla ImportacionActivo.aspx: disparar el proceso, mostrar el resultado y dejar constancia de quién lo ejecutó.</t>
+        </is>
+      </c>
+      <c r="I478" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="J478" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K478" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L478" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M478" s="8" t="inlineStr"/>
+      <c r="N478" s="8" t="inlineStr"/>
+      <c r="O478" s="8" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B479" s="8" t="inlineStr">
+        <is>
+          <t>T-6112</t>
+        </is>
+      </c>
+      <c r="C479" s="8" t="inlineStr">
+        <is>
+          <t>HU-200</t>
+        </is>
+      </c>
+      <c r="D479" s="8" t="inlineStr">
+        <is>
+          <t>Importar activos desde una planilla</t>
+        </is>
+      </c>
+      <c r="E479" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F479" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G479" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H479" s="9" t="inlineStr">
+        <is>
+          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
+        </is>
+      </c>
+      <c r="I479" s="8" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="J479" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K479" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L479" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M479" s="8" t="inlineStr"/>
+      <c r="N479" s="8" t="inlineStr"/>
+      <c r="O479" s="8" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B480" s="8" t="inlineStr">
+        <is>
+          <t>T-6113</t>
+        </is>
+      </c>
+      <c r="C480" s="8" t="inlineStr">
+        <is>
+          <t>HU-200</t>
+        </is>
+      </c>
+      <c r="D480" s="8" t="inlineStr">
+        <is>
+          <t>Importar activos desde una planilla</t>
+        </is>
+      </c>
+      <c r="E480" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F480" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G480" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H480" s="9" t="inlineStr">
+        <is>
+          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
+        </is>
+      </c>
+      <c r="I480" s="8" t="inlineStr">
+        <is>
+          <t>Pruebas</t>
+        </is>
+      </c>
+      <c r="J480" s="8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K480" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L480" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M480" s="8" t="inlineStr"/>
+      <c r="N480" s="8" t="inlineStr"/>
+      <c r="O480" s="8" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B481" s="8" t="inlineStr">
+        <is>
+          <t>T-6114</t>
+        </is>
+      </c>
+      <c r="C481" s="8" t="inlineStr">
+        <is>
+          <t>HU-200</t>
+        </is>
+      </c>
+      <c r="D481" s="8" t="inlineStr">
+        <is>
+          <t>Importar activos desde una planilla</t>
+        </is>
+      </c>
+      <c r="E481" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F481" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G481" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H481" s="9" t="inlineStr">
+        <is>
+          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
+        </is>
+      </c>
+      <c r="I481" s="8" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="J481" s="8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K481" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L481" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M481" s="8" t="inlineStr"/>
+      <c r="N481" s="8" t="inlineStr"/>
+      <c r="O481" s="8" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B482" s="8" t="inlineStr">
+        <is>
+          <t>T-6115</t>
+        </is>
+      </c>
+      <c r="C482" s="8" t="inlineStr">
+        <is>
+          <t>HU-200</t>
+        </is>
+      </c>
+      <c r="D482" s="8" t="inlineStr">
+        <is>
+          <t>Importar activos desde una planilla</t>
+        </is>
+      </c>
+      <c r="E482" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F482" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G482" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H482" s="9" t="inlineStr">
+        <is>
+          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
+        </is>
+      </c>
+      <c r="I482" s="8" t="inlineStr">
+        <is>
+          <t>Validación</t>
+        </is>
+      </c>
+      <c r="J482" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K482" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L482" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M482" s="8" t="inlineStr"/>
+      <c r="N482" s="8" t="inlineStr"/>
+      <c r="O482" s="8" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B483" s="8" t="inlineStr">
+        <is>
+          <t>T-6127</t>
+        </is>
+      </c>
+      <c r="C483" s="8" t="inlineStr">
+        <is>
+          <t>HU-201</t>
+        </is>
+      </c>
+      <c r="D483" s="8" t="inlineStr">
+        <is>
+          <t>Resolver las celdas ambiguas de una importación</t>
+        </is>
+      </c>
+      <c r="E483" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F483" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G483" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H483" s="9" t="inlineStr">
+        <is>
+          <t>Modelo: revisar Importacion_Carga_Celda — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
+        </is>
+      </c>
+      <c r="I483" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J483" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K483" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L483" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M483" s="8" t="inlineStr"/>
+      <c r="N483" s="8" t="inlineStr"/>
+      <c r="O483" s="8" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B484" s="8" t="inlineStr">
+        <is>
+          <t>T-6128</t>
+        </is>
+      </c>
+      <c r="C484" s="8" t="inlineStr">
+        <is>
+          <t>HU-201</t>
+        </is>
+      </c>
+      <c r="D484" s="8" t="inlineStr">
+        <is>
+          <t>Resolver las celdas ambiguas de una importación</t>
+        </is>
+      </c>
+      <c r="E484" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F484" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G484" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H484" s="9" t="inlineStr">
+        <is>
+          <t>SP IMPORTACION_CELDA: el proceso completo dentro de una transacción, con SET XACT_ABORT ON para que un error no deje datos a medias.</t>
+        </is>
+      </c>
+      <c r="I484" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J484" s="8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K484" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L484" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M484" s="8" t="inlineStr"/>
+      <c r="N484" s="8" t="inlineStr"/>
+      <c r="O484" s="8" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B485" s="8" t="inlineStr">
+        <is>
+          <t>T-6129</t>
+        </is>
+      </c>
+      <c r="C485" s="8" t="inlineStr">
+        <is>
+          <t>HU-201</t>
+        </is>
+      </c>
+      <c r="D485" s="8" t="inlineStr">
+        <is>
+          <t>Resolver las celdas ambiguas de una importación</t>
+        </is>
+      </c>
+      <c r="E485" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F485" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G485" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H485" s="9" t="inlineStr">
+        <is>
+          <t>Reglas de negocio de la historia en el SP, no en la pantalla: la API y la web tienen que obtener el mismo resultado.</t>
+        </is>
+      </c>
+      <c r="I485" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J485" s="8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K485" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L485" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M485" s="8" t="inlineStr"/>
+      <c r="N485" s="8" t="inlineStr"/>
+      <c r="O485" s="8" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B486" s="8" t="inlineStr">
+        <is>
+          <t>T-6130</t>
+        </is>
+      </c>
+      <c r="C486" s="8" t="inlineStr">
+        <is>
+          <t>HU-201</t>
+        </is>
+      </c>
+      <c r="D486" s="8" t="inlineStr">
+        <is>
+          <t>Resolver las celdas ambiguas de una importación</t>
+        </is>
+      </c>
+      <c r="E486" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F486" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G486" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H486" s="9" t="inlineStr">
+        <is>
+          <t>SP SEL_IMPORTACION_CELDA: consultar el resultado del proceso.</t>
+        </is>
+      </c>
+      <c r="I486" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J486" s="8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K486" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L486" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M486" s="8" t="inlineStr"/>
+      <c r="N486" s="8" t="inlineStr"/>
+      <c r="O486" s="8" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B487" s="8" t="inlineStr">
+        <is>
+          <t>T-6131</t>
+        </is>
+      </c>
+      <c r="C487" s="8" t="inlineStr">
+        <is>
+          <t>HU-201</t>
+        </is>
+      </c>
+      <c r="D487" s="8" t="inlineStr">
+        <is>
+          <t>Resolver las celdas ambiguas de una importación</t>
+        </is>
+      </c>
+      <c r="E487" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F487" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G487" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H487" s="9" t="inlineStr">
+        <is>
+          <t>Datos de prueba en Importacion_Carga_Celda para poder ejercitar los criterios de aceptación.</t>
+        </is>
+      </c>
+      <c r="I487" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J487" s="8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K487" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L487" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M487" s="8" t="inlineStr"/>
+      <c r="N487" s="8" t="inlineStr"/>
+      <c r="O487" s="8" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B488" s="8" t="inlineStr">
+        <is>
+          <t>T-6134</t>
+        </is>
+      </c>
+      <c r="C488" s="8" t="inlineStr">
+        <is>
+          <t>HU-201</t>
+        </is>
+      </c>
+      <c r="D488" s="8" t="inlineStr">
+        <is>
+          <t>Resolver las celdas ambiguas de una importación</t>
+        </is>
+      </c>
+      <c r="E488" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F488" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G488" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H488" s="9" t="inlineStr">
+        <is>
+          <t>Pantalla ImportacionCelda.aspx: disparar el proceso, mostrar el resultado y dejar constancia de quién lo ejecutó.</t>
+        </is>
+      </c>
+      <c r="I488" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="J488" s="8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K488" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L488" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M488" s="8" t="inlineStr"/>
+      <c r="N488" s="8" t="inlineStr"/>
+      <c r="O488" s="8" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B489" s="8" t="inlineStr">
+        <is>
+          <t>T-6135</t>
+        </is>
+      </c>
+      <c r="C489" s="8" t="inlineStr">
+        <is>
+          <t>HU-201</t>
+        </is>
+      </c>
+      <c r="D489" s="8" t="inlineStr">
+        <is>
+          <t>Resolver las celdas ambiguas de una importación</t>
+        </is>
+      </c>
+      <c r="E489" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F489" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G489" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H489" s="9" t="inlineStr">
+        <is>
+          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
+        </is>
+      </c>
+      <c r="I489" s="8" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="J489" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K489" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L489" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M489" s="8" t="inlineStr"/>
+      <c r="N489" s="8" t="inlineStr"/>
+      <c r="O489" s="8" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B490" s="8" t="inlineStr">
+        <is>
+          <t>T-6136</t>
+        </is>
+      </c>
+      <c r="C490" s="8" t="inlineStr">
+        <is>
+          <t>HU-201</t>
+        </is>
+      </c>
+      <c r="D490" s="8" t="inlineStr">
+        <is>
+          <t>Resolver las celdas ambiguas de una importación</t>
+        </is>
+      </c>
+      <c r="E490" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F490" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G490" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H490" s="9" t="inlineStr">
+        <is>
+          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
+        </is>
+      </c>
+      <c r="I490" s="8" t="inlineStr">
+        <is>
+          <t>Pruebas</t>
+        </is>
+      </c>
+      <c r="J490" s="8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K490" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L490" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M490" s="8" t="inlineStr"/>
+      <c r="N490" s="8" t="inlineStr"/>
+      <c r="O490" s="8" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B491" s="8" t="inlineStr">
+        <is>
+          <t>T-6137</t>
+        </is>
+      </c>
+      <c r="C491" s="8" t="inlineStr">
+        <is>
+          <t>HU-201</t>
+        </is>
+      </c>
+      <c r="D491" s="8" t="inlineStr">
+        <is>
+          <t>Resolver las celdas ambiguas de una importación</t>
+        </is>
+      </c>
+      <c r="E491" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F491" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G491" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H491" s="9" t="inlineStr">
+        <is>
+          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
+        </is>
+      </c>
+      <c r="I491" s="8" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="J491" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K491" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L491" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M491" s="8" t="inlineStr"/>
+      <c r="N491" s="8" t="inlineStr"/>
+      <c r="O491" s="8" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B492" s="8" t="inlineStr">
+        <is>
+          <t>T-6138</t>
+        </is>
+      </c>
+      <c r="C492" s="8" t="inlineStr">
+        <is>
+          <t>HU-201</t>
+        </is>
+      </c>
+      <c r="D492" s="8" t="inlineStr">
+        <is>
+          <t>Resolver las celdas ambiguas de una importación</t>
+        </is>
+      </c>
+      <c r="E492" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F492" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G492" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H492" s="9" t="inlineStr">
+        <is>
+          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
+        </is>
+      </c>
+      <c r="I492" s="8" t="inlineStr">
+        <is>
+          <t>Validación</t>
+        </is>
+      </c>
+      <c r="J492" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K492" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L492" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M492" s="8" t="inlineStr"/>
+      <c r="N492" s="8" t="inlineStr"/>
+      <c r="O492" s="8" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B493" s="8" t="inlineStr">
+        <is>
+          <t>T-6139</t>
+        </is>
+      </c>
+      <c r="C493" s="8" t="inlineStr">
+        <is>
+          <t>HU-202</t>
+        </is>
+      </c>
+      <c r="D493" s="8" t="inlineStr">
+        <is>
+          <t>Importar el plan anual desde una planilla</t>
+        </is>
+      </c>
+      <c r="E493" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F493" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G493" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H493" s="9" t="inlineStr">
+        <is>
+          <t>Modelo: revisar Importacion_Carga — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
+        </is>
+      </c>
+      <c r="I493" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J493" s="8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K493" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L493" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M493" s="8" t="inlineStr"/>
+      <c r="N493" s="8" t="inlineStr"/>
+      <c r="O493" s="8" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B494" s="8" t="inlineStr">
+        <is>
+          <t>T-6140</t>
+        </is>
+      </c>
+      <c r="C494" s="8" t="inlineStr">
+        <is>
+          <t>HU-202</t>
+        </is>
+      </c>
+      <c r="D494" s="8" t="inlineStr">
+        <is>
+          <t>Importar el plan anual desde una planilla</t>
+        </is>
+      </c>
+      <c r="E494" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F494" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G494" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H494" s="9" t="inlineStr">
+        <is>
+          <t>SP IMPORTACION_PLAN: el proceso completo dentro de una transacción, con SET XACT_ABORT ON para que un error no deje datos a medias.</t>
+        </is>
+      </c>
+      <c r="I494" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J494" s="8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K494" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L494" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M494" s="8" t="inlineStr"/>
+      <c r="N494" s="8" t="inlineStr"/>
+      <c r="O494" s="8" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B495" s="8" t="inlineStr">
+        <is>
+          <t>T-6141</t>
+        </is>
+      </c>
+      <c r="C495" s="8" t="inlineStr">
+        <is>
+          <t>HU-202</t>
+        </is>
+      </c>
+      <c r="D495" s="8" t="inlineStr">
+        <is>
+          <t>Importar el plan anual desde una planilla</t>
+        </is>
+      </c>
+      <c r="E495" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F495" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G495" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H495" s="9" t="inlineStr">
+        <is>
+          <t>Reglas de negocio de la historia en el SP, no en la pantalla: la API y la web tienen que obtener el mismo resultado.</t>
+        </is>
+      </c>
+      <c r="I495" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J495" s="8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K495" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L495" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M495" s="8" t="inlineStr"/>
+      <c r="N495" s="8" t="inlineStr"/>
+      <c r="O495" s="8" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B496" s="8" t="inlineStr">
+        <is>
+          <t>T-6142</t>
+        </is>
+      </c>
+      <c r="C496" s="8" t="inlineStr">
+        <is>
+          <t>HU-202</t>
+        </is>
+      </c>
+      <c r="D496" s="8" t="inlineStr">
+        <is>
+          <t>Importar el plan anual desde una planilla</t>
+        </is>
+      </c>
+      <c r="E496" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F496" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G496" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H496" s="9" t="inlineStr">
+        <is>
+          <t>SP SEL_IMPORTACION_PLAN: consultar el resultado del proceso.</t>
+        </is>
+      </c>
+      <c r="I496" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J496" s="8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K496" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L496" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M496" s="8" t="inlineStr"/>
+      <c r="N496" s="8" t="inlineStr"/>
+      <c r="O496" s="8" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B497" s="8" t="inlineStr">
+        <is>
+          <t>T-6143</t>
+        </is>
+      </c>
+      <c r="C497" s="8" t="inlineStr">
+        <is>
+          <t>HU-202</t>
+        </is>
+      </c>
+      <c r="D497" s="8" t="inlineStr">
+        <is>
+          <t>Importar el plan anual desde una planilla</t>
+        </is>
+      </c>
+      <c r="E497" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F497" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G497" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H497" s="9" t="inlineStr">
+        <is>
+          <t>Datos de prueba en Importacion_Carga para poder ejercitar los criterios de aceptación.</t>
+        </is>
+      </c>
+      <c r="I497" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J497" s="8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K497" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L497" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M497" s="8" t="inlineStr"/>
+      <c r="N497" s="8" t="inlineStr"/>
+      <c r="O497" s="8" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B498" s="8" t="inlineStr">
+        <is>
+          <t>T-6146</t>
+        </is>
+      </c>
+      <c r="C498" s="8" t="inlineStr">
+        <is>
+          <t>HU-202</t>
+        </is>
+      </c>
+      <c r="D498" s="8" t="inlineStr">
+        <is>
+          <t>Importar el plan anual desde una planilla</t>
+        </is>
+      </c>
+      <c r="E498" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F498" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G498" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H498" s="9" t="inlineStr">
+        <is>
+          <t>Pantalla ImportacionPlan.aspx: disparar el proceso, mostrar el resultado y dejar constancia de quién lo ejecutó.</t>
+        </is>
+      </c>
+      <c r="I498" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="J498" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K498" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L498" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M498" s="8" t="inlineStr"/>
+      <c r="N498" s="8" t="inlineStr"/>
+      <c r="O498" s="8" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B499" s="8" t="inlineStr">
+        <is>
+          <t>T-6147</t>
+        </is>
+      </c>
+      <c r="C499" s="8" t="inlineStr">
+        <is>
+          <t>HU-202</t>
+        </is>
+      </c>
+      <c r="D499" s="8" t="inlineStr">
+        <is>
+          <t>Importar el plan anual desde una planilla</t>
+        </is>
+      </c>
+      <c r="E499" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F499" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G499" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H499" s="9" t="inlineStr">
+        <is>
+          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
+        </is>
+      </c>
+      <c r="I499" s="8" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="J499" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K499" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L499" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M499" s="8" t="inlineStr"/>
+      <c r="N499" s="8" t="inlineStr"/>
+      <c r="O499" s="8" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B500" s="8" t="inlineStr">
+        <is>
+          <t>T-6148</t>
+        </is>
+      </c>
+      <c r="C500" s="8" t="inlineStr">
+        <is>
+          <t>HU-202</t>
+        </is>
+      </c>
+      <c r="D500" s="8" t="inlineStr">
+        <is>
+          <t>Importar el plan anual desde una planilla</t>
+        </is>
+      </c>
+      <c r="E500" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F500" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G500" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H500" s="9" t="inlineStr">
+        <is>
+          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
+        </is>
+      </c>
+      <c r="I500" s="8" t="inlineStr">
+        <is>
+          <t>Pruebas</t>
+        </is>
+      </c>
+      <c r="J500" s="8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K500" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L500" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M500" s="8" t="inlineStr"/>
+      <c r="N500" s="8" t="inlineStr"/>
+      <c r="O500" s="8" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B501" s="8" t="inlineStr">
+        <is>
+          <t>T-6149</t>
+        </is>
+      </c>
+      <c r="C501" s="8" t="inlineStr">
+        <is>
+          <t>HU-202</t>
+        </is>
+      </c>
+      <c r="D501" s="8" t="inlineStr">
+        <is>
+          <t>Importar el plan anual desde una planilla</t>
+        </is>
+      </c>
+      <c r="E501" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F501" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G501" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H501" s="9" t="inlineStr">
+        <is>
+          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
+        </is>
+      </c>
+      <c r="I501" s="8" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="J501" s="8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K501" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L501" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M501" s="8" t="inlineStr"/>
+      <c r="N501" s="8" t="inlineStr"/>
+      <c r="O501" s="8" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B502" s="8" t="inlineStr">
+        <is>
+          <t>T-6150</t>
+        </is>
+      </c>
+      <c r="C502" s="8" t="inlineStr">
+        <is>
+          <t>HU-202</t>
+        </is>
+      </c>
+      <c r="D502" s="8" t="inlineStr">
+        <is>
+          <t>Importar el plan anual desde una planilla</t>
+        </is>
+      </c>
+      <c r="E502" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F502" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G502" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H502" s="9" t="inlineStr">
+        <is>
+          <t>Validación funcional con la Product Owner sobre la pantalla terminada.</t>
+        </is>
+      </c>
+      <c r="I502" s="8" t="inlineStr">
+        <is>
+          <t>Validación</t>
+        </is>
+      </c>
+      <c r="J502" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K502" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L502" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M502" s="8" t="inlineStr"/>
+      <c r="N502" s="8" t="inlineStr"/>
+      <c r="O502" s="8" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B503" s="8" t="inlineStr">
+        <is>
+          <t>T-6225</t>
+        </is>
+      </c>
+      <c r="C503" s="8" t="inlineStr">
+        <is>
+          <t>HU-203</t>
+        </is>
+      </c>
+      <c r="D503" s="8" t="inlineStr">
+        <is>
+          <t>Consultar el historial de importaciones</t>
+        </is>
+      </c>
+      <c r="E503" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F503" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G503" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H503" s="9" t="inlineStr">
+        <is>
+          <t>Modelo: revisar Importacion_Carga — columnas, FK e índices. Confirmar el índice único del código dentro del cliente.</t>
+        </is>
+      </c>
+      <c r="I503" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J503" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K503" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L503" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M503" s="8" t="inlineStr"/>
+      <c r="N503" s="8" t="inlineStr"/>
+      <c r="O503" s="8" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B504" s="8" t="inlineStr">
+        <is>
+          <t>T-6226</t>
+        </is>
+      </c>
+      <c r="C504" s="8" t="inlineStr">
+        <is>
+          <t>HU-203</t>
+        </is>
+      </c>
+      <c r="D504" s="8" t="inlineStr">
+        <is>
+          <t>Consultar el historial de importaciones</t>
+        </is>
+      </c>
+      <c r="E504" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F504" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G504" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H504" s="9" t="inlineStr">
+        <is>
+          <t>SP SEL_IMPORTACION_HISTORIAL: consulta con filtros, ordenamiento y paginación. Sin SQL armado por concatenación: todo por parámetros.</t>
+        </is>
+      </c>
+      <c r="I504" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J504" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K504" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L504" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M504" s="8" t="inlineStr"/>
+      <c r="N504" s="8" t="inlineStr"/>
+      <c r="O504" s="8" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B505" s="8" t="inlineStr">
+        <is>
+          <t>T-6227</t>
+        </is>
+      </c>
+      <c r="C505" s="8" t="inlineStr">
+        <is>
+          <t>HU-203</t>
+        </is>
+      </c>
+      <c r="D505" s="8" t="inlineStr">
+        <is>
+          <t>Consultar el historial de importaciones</t>
+        </is>
+      </c>
+      <c r="E505" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F505" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G505" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H505" s="9" t="inlineStr">
+        <is>
+          <t>Índices de apoyo para que la consulta no haga scan cuando la tabla Importacion_Carga crezca.</t>
+        </is>
+      </c>
+      <c r="I505" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J505" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K505" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L505" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M505" s="8" t="inlineStr"/>
+      <c r="N505" s="8" t="inlineStr"/>
+      <c r="O505" s="8" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B506" s="8" t="inlineStr">
+        <is>
+          <t>T-6228</t>
+        </is>
+      </c>
+      <c r="C506" s="8" t="inlineStr">
+        <is>
+          <t>HU-203</t>
+        </is>
+      </c>
+      <c r="D506" s="8" t="inlineStr">
+        <is>
+          <t>Consultar el historial de importaciones</t>
+        </is>
+      </c>
+      <c r="E506" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F506" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G506" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H506" s="9" t="inlineStr">
+        <is>
+          <t>Datos de prueba en Importacion_Carga para poder ejercitar los criterios de aceptación.</t>
+        </is>
+      </c>
+      <c r="I506" s="8" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="J506" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K506" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L506" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M506" s="8" t="inlineStr"/>
+      <c r="N506" s="8" t="inlineStr"/>
+      <c r="O506" s="8" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B507" s="8" t="inlineStr">
+        <is>
+          <t>T-6231</t>
+        </is>
+      </c>
+      <c r="C507" s="8" t="inlineStr">
+        <is>
+          <t>HU-203</t>
+        </is>
+      </c>
+      <c r="D507" s="8" t="inlineStr">
+        <is>
+          <t>Consultar el historial de importaciones</t>
+        </is>
+      </c>
+      <c r="E507" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F507" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G507" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H507" s="9" t="inlineStr">
+        <is>
+          <t>Pantalla ImportacionHistorial.aspx de solo lectura: filtros arriba, grilla y exportación.</t>
+        </is>
+      </c>
+      <c r="I507" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="J507" s="8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K507" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L507" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M507" s="8" t="inlineStr"/>
+      <c r="N507" s="8" t="inlineStr"/>
+      <c r="O507" s="8" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B508" s="8" t="inlineStr">
+        <is>
+          <t>T-6232</t>
+        </is>
+      </c>
+      <c r="C508" s="8" t="inlineStr">
+        <is>
+          <t>HU-203</t>
+        </is>
+      </c>
+      <c r="D508" s="8" t="inlineStr">
+        <is>
+          <t>Consultar el historial de importaciones</t>
+        </is>
+      </c>
+      <c r="E508" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F508" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G508" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H508" s="9" t="inlineStr">
+        <is>
+          <t>Permiso en el servidor: la acción se valida con Token.Puede / ExigirPagina, no escondiendo el botón. Y filtrar por cliente en sesión para que no se vea lo de otra empresa.</t>
+        </is>
+      </c>
+      <c r="I508" s="8" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="J508" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K508" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L508" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M508" s="8" t="inlineStr"/>
+      <c r="N508" s="8" t="inlineStr"/>
+      <c r="O508" s="8" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B509" s="8" t="inlineStr">
+        <is>
+          <t>T-6233</t>
+        </is>
+      </c>
+      <c r="C509" s="8" t="inlineStr">
+        <is>
+          <t>HU-203</t>
+        </is>
+      </c>
+      <c r="D509" s="8" t="inlineStr">
+        <is>
+          <t>Consultar el historial de importaciones</t>
+        </is>
+      </c>
+      <c r="E509" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F509" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G509" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H509" s="9" t="inlineStr">
+        <is>
+          <t>Escribir y ejecutar un caso de prueba por cada criterio de aceptación de la historia, y dejar el resultado en la hoja Criterios de aceptación.</t>
+        </is>
+      </c>
+      <c r="I509" s="8" t="inlineStr">
+        <is>
+          <t>Pruebas</t>
+        </is>
+      </c>
+      <c r="J509" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K509" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L509" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M509" s="8" t="inlineStr"/>
+      <c r="N509" s="8" t="inlineStr"/>
+      <c r="O509" s="8" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B510" s="8" t="inlineStr">
+        <is>
+          <t>T-6234</t>
+        </is>
+      </c>
+      <c r="C510" s="8" t="inlineStr">
+        <is>
+          <t>HU-203</t>
+        </is>
+      </c>
+      <c r="D510" s="8" t="inlineStr">
+        <is>
+          <t>Consultar el historial de importaciones</t>
+        </is>
+      </c>
+      <c r="E510" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F510" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G510" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="H510" s="9" t="inlineStr">
+        <is>
+          <t>Documentar el endpoint en Swagger y anotar en el MD de estado las decisiones que un tercero no podría deducir del código.</t>
+        </is>
+      </c>
+      <c r="I510" s="8" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="J510" s="8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K510" s="8" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
+      <c r="L510" s="8" t="inlineStr">
+        <is>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="M510" s="8" t="inlineStr"/>
+      <c r="N510" s="8" t="inlineStr"/>
+      <c r="O510" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O455"/>
+  <autoFilter ref="A1:O510"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -30782,7 +34247,7 @@
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="n">
-        <v>117.8</v>
+        <v>145.5</v>
       </c>
       <c r="I6" s="6">
         <f>SUM(C6:H6)</f>
@@ -30801,7 +34266,7 @@
       <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="n">
-        <v>117</v>
+        <v>135.8</v>
       </c>
       <c r="I7" s="6">
         <f>SUM(C7:H7)</f>
@@ -30820,7 +34285,7 @@
       <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="n">
-        <v>118.5</v>
+        <v>124.2</v>
       </c>
       <c r="I8" s="6">
         <f>SUM(C8:H8)</f>
@@ -30838,7 +34303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J69"/>
+  <dimension ref="B2:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="2" max="2"/>
@@ -33299,12 +36764,12 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>HU-178</t>
+          <t>HU-177</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Monitorear la salud del modelo en producción</t>
+          <t>Registrar si la predicción se cumplió</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
@@ -33318,17 +36783,17 @@
         </is>
       </c>
       <c r="G64" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I64" s="8" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>Base de datos (4) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1) · Validación (1)</t>
+          <t>Base de datos (5) · Web (2) · Seguridad (1) · Pruebas (1) · Documentación (1)</t>
         </is>
       </c>
     </row>
@@ -33340,17 +36805,17 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>HU-181</t>
+          <t>HU-178</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Consultar el cumplimiento del plan de mantenimiento</t>
+          <t>Monitorear la salud del modelo en producción</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>EP-18</t>
+          <t>EP-17</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
@@ -33359,17 +36824,17 @@
         </is>
       </c>
       <c r="G65" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I65" s="8" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J65" s="9" t="inlineStr">
         <is>
-          <t>Base de datos (4) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1)</t>
+          <t>Base de datos (4) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1) · Validación (1)</t>
         </is>
       </c>
     </row>
@@ -33381,12 +36846,12 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>HU-184</t>
+          <t>HU-180</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Consultar la bandeja de alertas</t>
+          <t>Consultar el tablero de indicadores</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
@@ -33396,21 +36861,21 @@
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>Web y App</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="G66" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I66" s="8" t="n">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>Base de datos (4) · API (2) · Web (1) · Móvil (1) · Seguridad (1) · Pruebas (1) · Documentación (1)</t>
+          <t>Base de datos (4) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1) · Validación (1)</t>
         </is>
       </c>
     </row>
@@ -33422,12 +36887,12 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>HU-185</t>
+          <t>HU-181</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Exportar e imprimir reportes</t>
+          <t>Consultar el cumplimiento del plan de mantenimiento</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -33444,14 +36909,14 @@
         <v>5</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I67" s="8" t="n">
         <v>5.8</v>
       </c>
       <c r="J67" s="9" t="inlineStr">
         <is>
-          <t>Base de datos (5) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1)</t>
+          <t>Base de datos (4) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1)</t>
         </is>
       </c>
     </row>
@@ -33463,17 +36928,17 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>HU-201</t>
+          <t>HU-182</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Resolver las celdas ambiguas de una importación</t>
+          <t>Consultar disponibilidad y confiabilidad de los equipos</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>EP-20</t>
+          <t>EP-18</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
@@ -33485,14 +36950,14 @@
         <v>8</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I68" s="8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>Base de datos (5) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1) · Validación (1)</t>
+          <t>Base de datos (4) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1) · Validación (1)</t>
         </is>
       </c>
     </row>
@@ -33504,41 +36969,287 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
+          <t>HU-183</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>Consultar los costos de mantenimiento</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>EP-18</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H69" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I69" s="8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t>Base de datos (4) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1) · Validación (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>HU-184</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>Consultar la bandeja de alertas</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>EP-18</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>Web y App</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H70" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="I70" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J70" s="9" t="inlineStr">
+        <is>
+          <t>Base de datos (4) · API (2) · Web (1) · Móvil (1) · Seguridad (1) · Pruebas (1) · Documentación (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>HU-185</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>Exportar e imprimir reportes</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>EP-18</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H71" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I71" s="8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t>Base de datos (5) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>HU-200</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>Importar activos desde una planilla</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H72" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I72" s="8" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
+          <t>Base de datos (5) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1) · Validación (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>HU-201</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>Resolver las celdas ambiguas de una importación</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H73" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I73" s="8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J73" s="9" t="inlineStr">
+        <is>
+          <t>Base de datos (5) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1) · Validación (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
           <t>HU-202</t>
         </is>
       </c>
-      <c r="D69" s="9" t="inlineStr">
+      <c r="D74" s="9" t="inlineStr">
         <is>
           <t>Importar el plan anual desde una planilla</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
+      <c r="E74" s="8" t="inlineStr">
         <is>
           <t>EP-20</t>
         </is>
       </c>
-      <c r="F69" s="8" t="inlineStr">
+      <c r="F74" s="8" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="G69" s="8" t="n">
+      <c r="G74" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="H69" s="8" t="n">
+      <c r="H74" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="I69" s="8" t="n">
+      <c r="I74" s="8" t="n">
         <v>15.2</v>
       </c>
-      <c r="J69" s="9" t="inlineStr">
+      <c r="J74" s="9" t="inlineStr">
         <is>
           <t>Base de datos (5) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1) · Validación (1)</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>HU-203</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>Consultar el historial de importaciones</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>EP-20</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H75" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I75" s="8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J75" s="9" t="inlineStr">
+        <is>
+          <t>Base de datos (4) · Web (1) · Seguridad (1) · Pruebas (1) · Documentación (1)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B5:J69"/>
+  <autoFilter ref="B5:J75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>